--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -559,129 +559,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>34.39628482972136</v>
+        <v>29.67748825288338</v>
       </c>
       <c r="C2" t="n">
-        <v>45.47112462006078</v>
+        <v>34.65710782001698</v>
       </c>
       <c r="D2" t="n">
-        <v>26.01873536299766</v>
+        <v>15.6585434568249</v>
       </c>
       <c r="E2" t="n">
-        <v>34.33255269320843</v>
+        <v>21.3692069305536</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.01857585139318885</v>
+        <v>0.1321016659547202</v>
       </c>
       <c r="G2" t="n">
-        <v>82.73684210526316</v>
+        <v>41.00487804878049</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7010343129207027</v>
+        <v>1.187084044011906</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>667</v>
+        <v>3556</v>
       </c>
       <c r="J2" t="n">
-        <v>76.46921430165466</v>
+        <v>17.80103767695105</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>17.95524410389091</v>
+        <v>13.02966034945308</v>
       </c>
       <c r="L2" t="n">
-        <v>29.16686408659448</v>
+        <v>20.27736210195506</v>
       </c>
       <c r="M2" t="n">
-        <v>28.47351571234393</v>
+        <v>20.97355268843126</v>
       </c>
       <c r="N2" t="n">
-        <v>60.44</v>
+        <v>73.37</v>
       </c>
       <c r="O2" t="n">
-        <v>5.74</v>
+        <v>3.9</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="R2" t="n">
-        <v>1258520.29</v>
+        <v>2126725.18</v>
       </c>
       <c r="S2" t="n">
-        <v>4270</v>
+        <v>35495</v>
       </c>
       <c r="T2" t="n">
-        <v>85.75992272430739</v>
+        <v>84.54663657417515</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>36.30776794493609</v>
+        <v>34.39628482972136</v>
       </c>
       <c r="C3" t="n">
-        <v>33.00120254251846</v>
+        <v>45.47112462006078</v>
       </c>
       <c r="D3" t="n">
-        <v>11.93535353535353</v>
+        <v>26.01873536299766</v>
       </c>
       <c r="E3" t="n">
-        <v>15.92727272727273</v>
+        <v>34.33255269320843</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.4309242871189774</v>
+        <v>0.01857585139318885</v>
       </c>
       <c r="G3" t="n">
-        <v>8.043478260869565</v>
+        <v>82.73684210526316</v>
       </c>
       <c r="H3" t="n">
-        <v>1.727869310248534</v>
+        <v>0.7010343129207027</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>841</v>
+        <v>667</v>
       </c>
       <c r="J3" t="n">
-        <v>68.36335197744833</v>
+        <v>76.46921430165466</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>36.30691600183056</v>
+        <v>17.95524410389091</v>
       </c>
       <c r="L3" t="n">
-        <v>73.11367578503176</v>
+        <v>29.16686408659448</v>
       </c>
       <c r="M3" t="n">
-        <v>69.52182030724354</v>
+        <v>28.47351571234393</v>
       </c>
       <c r="N3" t="n">
-        <v>8.65</v>
+        <v>60.44</v>
       </c>
       <c r="O3" t="n">
-        <v>11.82</v>
+        <v>5.74</v>
       </c>
       <c r="P3" t="n">
-        <v>3.46</v>
+        <v>1.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="R3" t="n">
-        <v>571322.04</v>
+        <v>1258520.29</v>
       </c>
       <c r="S3" t="n">
-        <v>12375</v>
+        <v>4270</v>
       </c>
       <c r="T3" t="n">
-        <v>81.23496652577464</v>
+        <v>79.94074387215829</v>
       </c>
     </row>
     <row r="4">
@@ -739,263 +739,251 @@
         <v>50351</v>
       </c>
       <c r="T4" t="n">
-        <v>78.97373571732739</v>
+        <v>79.79697482700455</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>22.9043860525527</v>
+        <v>20.78030212917806</v>
       </c>
       <c r="C5" t="n">
-        <v>27.38467110326407</v>
+        <v>27.06792581636136</v>
       </c>
       <c r="D5" t="n">
-        <v>12.90931103415266</v>
+        <v>14.10805136073649</v>
       </c>
       <c r="E5" t="n">
-        <v>17.98293774812062</v>
+        <v>21.86869094726642</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1034568888000799</v>
+        <v>0.04543832520518615</v>
       </c>
       <c r="G5" t="n">
-        <v>31.93243243243243</v>
+        <v>54.33333333333334</v>
       </c>
       <c r="H5" t="n">
-        <v>1.289464130119082</v>
+        <v>1.025422325273269</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1752</v>
+        <v>955</v>
       </c>
       <c r="J5" t="n">
-        <v>42.13101535214459</v>
+        <v>19.2998469335665</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>30.32798083513346</v>
+        <v>11.83637017589811</v>
       </c>
       <c r="L5" t="n">
-        <v>24.775129058601</v>
+        <v>13.48774998597666</v>
       </c>
       <c r="M5" t="n">
-        <v>12.24383304425547</v>
+        <v>13.56415724960776</v>
       </c>
       <c r="N5" t="n">
-        <v>64.52</v>
+        <v>36.12</v>
       </c>
       <c r="O5" t="n">
-        <v>2.38</v>
+        <v>12.3</v>
       </c>
       <c r="P5" t="n">
-        <v>4.43</v>
+        <v>1.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>1347046.9</v>
+        <v>162274.18</v>
       </c>
       <c r="S5" t="n">
-        <v>35517</v>
+        <v>12383</v>
       </c>
       <c r="T5" t="n">
-        <v>68.09245734929726</v>
+        <v>78.17546048834996</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>29.67748825288338</v>
+        <v>117.7544910179641</v>
       </c>
       <c r="C6" t="n">
-        <v>34.65710782001698</v>
+        <v>143.527815468114</v>
       </c>
       <c r="D6" t="n">
-        <v>15.6585434568249</v>
+        <v>16.12281708616873</v>
       </c>
       <c r="E6" t="n">
-        <v>21.3692069305536</v>
+        <v>23.82963023694351</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.1321016659547202</v>
+        <v>0.1032934131736527</v>
       </c>
       <c r="G6" t="n">
-        <v>41.00487804878049</v>
+        <v>41.18620689655172</v>
       </c>
       <c r="H6" t="n">
-        <v>1.187084044011906</v>
+        <v>2.318160220469448</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3556</v>
+        <v>2938</v>
       </c>
       <c r="J6" t="n">
-        <v>17.80103767695105</v>
+        <v>18.28200866249903</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>13.02966034945308</v>
+        <v>14.54857371180267</v>
       </c>
       <c r="L6" t="n">
-        <v>20.27736210195506</v>
+        <v>14.85231951299384</v>
       </c>
       <c r="M6" t="n">
-        <v>20.97355268843126</v>
+        <v>15.43852585822143</v>
       </c>
       <c r="N6" t="n">
-        <v>73.37</v>
+        <v>54.96</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>14.34</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>3.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="R6" t="n">
-        <v>2126725.18</v>
+        <v>1677775.19</v>
       </c>
       <c r="S6" t="n">
-        <v>35495</v>
+        <v>24394</v>
       </c>
       <c r="T6" t="n">
-        <v>67.37697048318884</v>
+        <v>76.26865270052919</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>117.7544910179641</v>
+        <v>36.30776794493609</v>
       </c>
       <c r="C7" t="n">
-        <v>143.527815468114</v>
+        <v>33.00120254251846</v>
       </c>
       <c r="D7" t="n">
-        <v>16.12281708616873</v>
+        <v>11.93535353535353</v>
       </c>
       <c r="E7" t="n">
-        <v>23.82963023694351</v>
+        <v>15.92727272727273</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.1032934131736527</v>
+        <v>0.4309242871189774</v>
       </c>
       <c r="G7" t="n">
-        <v>41.18620689655172</v>
+        <v>8.043478260869565</v>
       </c>
       <c r="H7" t="n">
-        <v>2.318160220469448</v>
+        <v>1.727869310248534</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2938</v>
+        <v>841</v>
       </c>
       <c r="J7" t="n">
-        <v>18.28200866249903</v>
+        <v>68.36335197744833</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>14.54857371180267</v>
+        <v>36.30691600183056</v>
       </c>
       <c r="L7" t="n">
-        <v>14.85231951299384</v>
+        <v>73.11367578503176</v>
       </c>
       <c r="M7" t="n">
-        <v>15.43852585822143</v>
+        <v>69.52182030724354</v>
       </c>
       <c r="N7" t="n">
-        <v>54.96</v>
+        <v>8.65</v>
       </c>
       <c r="O7" t="n">
-        <v>14.34</v>
+        <v>11.82</v>
       </c>
       <c r="P7" t="n">
-        <v>3.85</v>
+        <v>3.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>1677775.19</v>
+        <v>571322.04</v>
       </c>
       <c r="S7" t="n">
-        <v>24394</v>
+        <v>12375</v>
       </c>
       <c r="T7" t="n">
-        <v>66.8729916012617</v>
+        <v>74.759015326533</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>50.94431367348518</v>
+        <v>17.69876929087712</v>
       </c>
       <c r="C8" t="n">
-        <v>62.9347274388387</v>
+        <v>23.27321565617805</v>
       </c>
       <c r="D8" t="n">
-        <v>19.13671215020777</v>
+        <v>12.22122302158273</v>
       </c>
       <c r="E8" t="n">
-        <v>26.69068839692312</v>
+        <v>13.9568345323741</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.0886406082507266</v>
+        <v>0.01816761086149639</v>
       </c>
       <c r="G8" t="n">
-        <v>87.09511568123393</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.655940662120545</v>
+        <v>0.8790861298865568</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>50429</v>
+        <v>1168</v>
       </c>
       <c r="J8" t="n">
-        <v>13.63286455550641</v>
+        <v>18.99870072744285</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>10.4636148017166</v>
+        <v>11.1933589020679</v>
       </c>
       <c r="L8" t="n">
-        <v>7.871172131953608</v>
+        <v>19.85339817550189</v>
       </c>
       <c r="M8" t="n">
-        <v>8.618771612987096</v>
-      </c>
-      <c r="N8" t="n">
-        <v>78.69</v>
-      </c>
-      <c r="O8" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.62</v>
+        <v>19.64385000375561</v>
       </c>
       <c r="Q8" t="n">
-        <v>58</v>
-      </c>
-      <c r="R8" t="n">
-        <v>461188.15</v>
+        <v>16</v>
       </c>
       <c r="S8" t="n">
-        <v>240893</v>
+        <v>22240</v>
       </c>
       <c r="T8" t="n">
-        <v>66.2679627617521</v>
+        <v>68.12570273895892</v>
       </c>
     </row>
     <row r="9">
@@ -1059,184 +1047,199 @@
         <v>26711</v>
       </c>
       <c r="T9" t="n">
-        <v>64.69131927823801</v>
+        <v>64.60059842643911</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>29.78800671841663</v>
+        <v>50.94431367348518</v>
       </c>
       <c r="C10" t="n">
-        <v>37.30292821974604</v>
+        <v>62.9347274388387</v>
       </c>
       <c r="D10" t="n">
-        <v>17.08075746730006</v>
+        <v>19.13671215020777</v>
       </c>
       <c r="E10" t="n">
-        <v>23.70339038198738</v>
+        <v>26.69068839692312</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.09486358890553362</v>
+        <v>0.0886406082507266</v>
       </c>
       <c r="G10" t="n">
-        <v>87.52340425531915</v>
+        <v>87.09511568123393</v>
       </c>
       <c r="H10" t="n">
-        <v>1.129760329363329</v>
+        <v>1.655940662120545</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20117</v>
+        <v>50429</v>
       </c>
       <c r="J10" t="n">
-        <v>15.21650079880636</v>
+        <v>13.63286455550641</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>13.19910093055623</v>
+        <v>10.4636148017166</v>
       </c>
       <c r="L10" t="n">
-        <v>11.23941998365794</v>
+        <v>7.871172131953608</v>
       </c>
       <c r="M10" t="n">
-        <v>12.47461131420948</v>
+        <v>8.618771612987096</v>
       </c>
       <c r="N10" t="n">
-        <v>35.99</v>
+        <v>78.69</v>
       </c>
       <c r="O10" t="n">
-        <v>8.970000000000001</v>
+        <v>6.08</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1</v>
+        <v>1.62</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>58</v>
       </c>
       <c r="R10" t="n">
-        <v>1112279.92</v>
+        <v>461188.15</v>
       </c>
       <c r="S10" t="n">
-        <v>153670</v>
+        <v>240893</v>
       </c>
       <c r="T10" t="n">
-        <v>63.88370700777556</v>
+        <v>61.31951778230892</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>15.09416181067115</v>
+        <v>19.74233736816026</v>
       </c>
       <c r="C11" t="n">
-        <v>16.56383979922618</v>
+        <v>23.8002379693284</v>
       </c>
       <c r="D11" t="n">
-        <v>19.81565870053818</v>
+        <v>19.9136053693192</v>
       </c>
       <c r="E11" t="n">
-        <v>26.84289749881436</v>
+        <v>28.32101674342223</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.05142381453500244</v>
+        <v>0.07085722375592836</v>
       </c>
       <c r="G11" t="n">
-        <v>58.33193277310924</v>
+        <v>51.70760233918129</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5684929901064378</v>
+        <v>0.7223053120165034</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11372</v>
+        <v>509</v>
       </c>
       <c r="J11" t="n">
-        <v>13.12675558948349</v>
+        <v>13.71726615103832</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>10.78116321985565</v>
+        <v>12.63964434957199</v>
       </c>
       <c r="L11" t="n">
-        <v>24.53682964293125</v>
+        <v>23.39250464543747</v>
       </c>
       <c r="M11" t="n">
-        <v>29.45936165164078</v>
+        <v>23.84240955838754</v>
       </c>
       <c r="N11" t="n">
-        <v>37.9</v>
+        <v>11.73</v>
       </c>
       <c r="O11" t="n">
-        <v>6.71</v>
+        <v>10.19</v>
       </c>
       <c r="P11" t="n">
-        <v>3.88</v>
+        <v>0.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>1339586.09</v>
+        <v>2441803.28</v>
       </c>
       <c r="S11" t="n">
-        <v>48497</v>
+        <v>28011</v>
       </c>
       <c r="T11" t="n">
-        <v>62.40707534502386</v>
+        <v>59.28443274332121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>17.69876929087712</v>
+        <v>15.7230643179025</v>
       </c>
       <c r="C12" t="n">
-        <v>23.27321565617805</v>
+        <v>20.87418300653595</v>
       </c>
       <c r="D12" t="n">
-        <v>12.22122302158273</v>
+        <v>9.366915605017816</v>
       </c>
       <c r="E12" t="n">
-        <v>13.9568345323741</v>
+        <v>87.42129155073948</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.01816761086149639</v>
+        <v>0.002867677181482999</v>
       </c>
       <c r="G12" t="n">
-        <v>67.15000000000001</v>
+        <v>160.0267857142857</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8790861298865568</v>
+        <v>0.3236083907247109</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1168</v>
+        <v>486</v>
       </c>
       <c r="J12" t="n">
-        <v>18.99870072744285</v>
+        <v>18.98796206427069</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>11.1933589020679</v>
+        <v>12.91184100336258</v>
       </c>
       <c r="L12" t="n">
-        <v>19.85339817550189</v>
+        <v>12.83917371819816</v>
       </c>
       <c r="M12" t="n">
-        <v>19.64385000375561</v>
+        <v>11.1392224868865</v>
+      </c>
+      <c r="N12" t="n">
+        <v>49</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1271789.21</v>
       </c>
       <c r="S12" t="n">
-        <v>22240</v>
+        <v>20487</v>
       </c>
       <c r="T12" t="n">
-        <v>60.95287318676066</v>
+        <v>59.23751631808607</v>
       </c>
     </row>
     <row r="13">
@@ -1300,135 +1303,135 @@
         <v>109913</v>
       </c>
       <c r="T13" t="n">
-        <v>59.9038594948709</v>
+        <v>57.51314363083295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>20.78030212917806</v>
+        <v>22.9043860525527</v>
       </c>
       <c r="C14" t="n">
-        <v>27.06792581636136</v>
+        <v>27.38467110326407</v>
       </c>
       <c r="D14" t="n">
-        <v>14.10805136073649</v>
+        <v>12.90931103415266</v>
       </c>
       <c r="E14" t="n">
-        <v>21.86869094726642</v>
+        <v>17.98293774812062</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.04543832520518615</v>
+        <v>0.1034568888000799</v>
       </c>
       <c r="G14" t="n">
-        <v>54.33333333333334</v>
+        <v>31.93243243243243</v>
       </c>
       <c r="H14" t="n">
-        <v>1.025422325273269</v>
+        <v>1.289464130119082</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>955</v>
+        <v>1752</v>
       </c>
       <c r="J14" t="n">
-        <v>19.2998469335665</v>
+        <v>42.13101535214459</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>11.83637017589811</v>
+        <v>30.32798083513346</v>
       </c>
       <c r="L14" t="n">
-        <v>13.48774998597666</v>
+        <v>24.775129058601</v>
       </c>
       <c r="M14" t="n">
-        <v>13.56415724960776</v>
+        <v>12.24383304425547</v>
       </c>
       <c r="N14" t="n">
-        <v>36.12</v>
+        <v>64.52</v>
       </c>
       <c r="O14" t="n">
-        <v>12.3</v>
+        <v>2.38</v>
       </c>
       <c r="P14" t="n">
-        <v>1.01</v>
+        <v>4.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="R14" t="n">
-        <v>162274.18</v>
+        <v>1347046.9</v>
       </c>
       <c r="S14" t="n">
-        <v>12383</v>
+        <v>35517</v>
       </c>
       <c r="T14" t="n">
-        <v>59.61651016619649</v>
+        <v>54.82910568425711</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>15.7230643179025</v>
+        <v>17.99027109750765</v>
       </c>
       <c r="C15" t="n">
-        <v>20.87418300653595</v>
+        <v>3.168808778744431</v>
       </c>
       <c r="D15" t="n">
-        <v>9.366915605017816</v>
+        <v>28.8880112339828</v>
       </c>
       <c r="E15" t="n">
-        <v>87.42129155073948</v>
+        <v>62.41380175029464</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.002867677181482999</v>
+        <v>6.445624336310825</v>
       </c>
       <c r="G15" t="n">
-        <v>160.0267857142857</v>
+        <v>1.300946133138182</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3236083907247109</v>
+        <v>0.06747535915921023</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>486</v>
+        <v>12547</v>
       </c>
       <c r="J15" t="n">
-        <v>18.98796206427069</v>
+        <v>21.39660074377121</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>12.91184100336258</v>
+        <v>17.25086850260209</v>
       </c>
       <c r="L15" t="n">
-        <v>12.83917371819816</v>
+        <v>51.94877118224903</v>
       </c>
       <c r="M15" t="n">
-        <v>11.1392224868865</v>
+        <v>55.18455739153598</v>
       </c>
       <c r="N15" t="n">
-        <v>49</v>
+        <v>25.76</v>
       </c>
       <c r="O15" t="n">
-        <v>7.86</v>
+        <v>6.2</v>
       </c>
       <c r="P15" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>1271789.21</v>
+        <v>1319221.86</v>
       </c>
       <c r="S15" t="n">
-        <v>20487</v>
+        <v>159516</v>
       </c>
       <c r="T15" t="n">
-        <v>58.37486301103623</v>
+        <v>54.25483366558786</v>
       </c>
     </row>
     <row r="16">
@@ -1492,391 +1495,388 @@
         <v>16536</v>
       </c>
       <c r="T16" t="n">
-        <v>58.08734076782807</v>
+        <v>52.44066966339204</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>19.74233736816026</v>
+        <v>15.09416181067115</v>
       </c>
       <c r="C17" t="n">
-        <v>23.8002379693284</v>
+        <v>16.56383979922618</v>
       </c>
       <c r="D17" t="n">
-        <v>19.9136053693192</v>
+        <v>19.81565870053818</v>
       </c>
       <c r="E17" t="n">
-        <v>28.32101674342223</v>
+        <v>26.84289749881436</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.07085722375592836</v>
+        <v>0.05142381453500244</v>
       </c>
       <c r="G17" t="n">
-        <v>51.70760233918129</v>
+        <v>58.33193277310924</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7223053120165034</v>
+        <v>0.5684929901064378</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>509</v>
+        <v>11372</v>
       </c>
       <c r="J17" t="n">
-        <v>13.71726615103832</v>
+        <v>13.12675558948349</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>12.63964434957199</v>
+        <v>10.78116321985565</v>
       </c>
       <c r="L17" t="n">
-        <v>23.39250464543747</v>
+        <v>24.53682964293125</v>
       </c>
       <c r="M17" t="n">
-        <v>23.84240955838754</v>
+        <v>29.45936165164078</v>
       </c>
       <c r="N17" t="n">
-        <v>11.73</v>
+        <v>37.9</v>
       </c>
       <c r="O17" t="n">
-        <v>10.19</v>
+        <v>6.71</v>
       </c>
       <c r="P17" t="n">
-        <v>0.09</v>
+        <v>3.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="R17" t="n">
-        <v>2441803.28</v>
+        <v>1339586.09</v>
       </c>
       <c r="S17" t="n">
-        <v>28011</v>
+        <v>48497</v>
       </c>
       <c r="T17" t="n">
-        <v>52.13287003379062</v>
+        <v>51.37713526020612</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>17.99027109750765</v>
+        <v>18.65921787709497</v>
       </c>
       <c r="C18" t="n">
-        <v>3.168808778744431</v>
+        <v>17.44208682110181</v>
       </c>
       <c r="D18" t="n">
-        <v>28.8880112339828</v>
+        <v>14.92737430167598</v>
       </c>
       <c r="E18" t="n">
-        <v>62.41380175029464</v>
+        <v>24.67039106145252</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>6.445624336310825</v>
+        <v>0.4349162011173184</v>
       </c>
       <c r="G18" t="n">
-        <v>1.300946133138182</v>
+        <v>10.5045045045045</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06747535915921023</v>
+        <v>0.6788531553398058</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>12547</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>21.39660074377121</v>
+        <v>38.18335427451367</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>17.25086850260209</v>
+        <v>21.08864867789759</v>
       </c>
       <c r="L18" t="n">
-        <v>51.94877118224903</v>
+        <v>23.8762916927858</v>
       </c>
       <c r="M18" t="n">
-        <v>55.18455739153598</v>
+        <v>24.57309396155174</v>
       </c>
       <c r="N18" t="n">
-        <v>25.76</v>
+        <v>56.96</v>
       </c>
       <c r="O18" t="n">
-        <v>6.2</v>
+        <v>5.76</v>
       </c>
       <c r="P18" t="n">
-        <v>3.43</v>
+        <v>0.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1319221.86</v>
+        <v>1535602.41</v>
       </c>
       <c r="S18" t="n">
-        <v>159516</v>
+        <v>4475</v>
       </c>
       <c r="T18" t="n">
-        <v>49.77499869166721</v>
+        <v>49.94497755046469</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>15.75038535195478</v>
+        <v>17.06727541291795</v>
       </c>
       <c r="C19" t="n">
-        <v>20.31834878432744</v>
+        <v>22.0258064516129</v>
       </c>
       <c r="D19" t="n">
-        <v>9.50809964894472</v>
+        <v>6.837009144701453</v>
       </c>
       <c r="E19" t="n">
-        <v>13.13003143989059</v>
+        <v>10.11834319526627</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.001389602503619973</v>
+        <v>0.040687525177924</v>
       </c>
       <c r="G19" t="n">
-        <v>117.9072164948454</v>
+        <v>25.35714285714286</v>
       </c>
       <c r="H19" t="n">
-        <v>1.230295566502463</v>
+        <v>1.495214348910158</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4936</v>
+        <v>335</v>
       </c>
       <c r="J19" t="n">
-        <v>26.32364432616601</v>
+        <v>21.14089015706202</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>10.51021511264258</v>
+        <v>13.03790793906312</v>
       </c>
       <c r="L19" t="n">
-        <v>12.00718203930038</v>
+        <v>10.03323122942004</v>
       </c>
       <c r="M19" t="n">
-        <v>11.1392224868865</v>
+        <v>8.997698704834534</v>
       </c>
       <c r="N19" t="n">
-        <v>20.78</v>
+        <v>45.41</v>
       </c>
       <c r="O19" t="n">
-        <v>8.26</v>
+        <v>14.08</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="R19" t="n">
-        <v>1503863.63</v>
+        <v>2521508.87</v>
       </c>
       <c r="S19" t="n">
-        <v>141858</v>
+        <v>18590</v>
       </c>
       <c r="T19" t="n">
-        <v>49.23865164943381</v>
+        <v>48.75439737462181</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>17.06727541291795</v>
+        <v>16.71605179468811</v>
       </c>
       <c r="C20" t="n">
-        <v>22.0258064516129</v>
+        <v>1.368070466573592</v>
       </c>
       <c r="D20" t="n">
-        <v>6.837009144701453</v>
+        <v>13.93516047014541</v>
       </c>
       <c r="E20" t="n">
-        <v>10.11834319526627</v>
+        <v>41.75390656810141</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.040687525177924</v>
+        <v>14.86741992554242</v>
       </c>
       <c r="G20" t="n">
-        <v>25.35714285714286</v>
+        <v>1.610661174334986</v>
       </c>
       <c r="H20" t="n">
-        <v>1.495214348910158</v>
+        <v>0.0719985042520674</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>335</v>
+        <v>13296</v>
       </c>
       <c r="J20" t="n">
-        <v>21.14089015706202</v>
+        <v>16.30293930023252</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>13.03790793906312</v>
+        <v>18.17561078322378</v>
       </c>
       <c r="L20" t="n">
-        <v>10.03323122942004</v>
+        <v>85.7752850068174</v>
       </c>
       <c r="M20" t="n">
-        <v>8.997698704834534</v>
+        <v>53.4206382524911</v>
       </c>
       <c r="N20" t="n">
-        <v>45.41</v>
+        <v>36.74</v>
       </c>
       <c r="O20" t="n">
-        <v>14.08</v>
+        <v>12.61</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>3.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="R20" t="n">
-        <v>2521508.87</v>
+        <v>496415.88</v>
       </c>
       <c r="S20" t="n">
-        <v>18590</v>
+        <v>110519</v>
       </c>
       <c r="T20" t="n">
-        <v>42.0191990677735</v>
+        <v>46.09979877526326</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>16.71605179468811</v>
+        <v>29.78800671841663</v>
       </c>
       <c r="C21" t="n">
-        <v>1.368070466573592</v>
+        <v>37.30292821974604</v>
       </c>
       <c r="D21" t="n">
-        <v>13.93516047014541</v>
+        <v>17.08075746730006</v>
       </c>
       <c r="E21" t="n">
-        <v>41.75390656810141</v>
+        <v>23.70339038198738</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>14.86741992554242</v>
+        <v>0.09486358890553362</v>
       </c>
       <c r="G21" t="n">
-        <v>1.610661174334986</v>
+        <v>87.52340425531915</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0719985042520674</v>
+        <v>1.129760329363329</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>13296</v>
+        <v>20117</v>
       </c>
       <c r="J21" t="n">
-        <v>16.30293930023252</v>
+        <v>15.21650079880636</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>18.17561078322378</v>
+        <v>13.19910093055623</v>
       </c>
       <c r="L21" t="n">
-        <v>85.7752850068174</v>
+        <v>11.23941998365794</v>
       </c>
       <c r="M21" t="n">
-        <v>53.4206382524911</v>
+        <v>12.47461131420948</v>
       </c>
       <c r="N21" t="n">
-        <v>36.74</v>
+        <v>35.99</v>
       </c>
       <c r="O21" t="n">
-        <v>12.61</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>19</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>496415.88</v>
+        <v>1112279.92</v>
       </c>
       <c r="S21" t="n">
-        <v>110519</v>
+        <v>153670</v>
       </c>
       <c r="T21" t="n">
-        <v>41.24609119135111</v>
+        <v>45.58342731354364</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>18.65921787709497</v>
+        <v>15.75038535195478</v>
       </c>
       <c r="C22" t="n">
-        <v>17.44208682110181</v>
+        <v>20.31834878432744</v>
       </c>
       <c r="D22" t="n">
-        <v>14.92737430167598</v>
+        <v>9.50809964894472</v>
       </c>
       <c r="E22" t="n">
-        <v>24.67039106145252</v>
+        <v>13.13003143989059</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.4349162011173184</v>
+        <v>0.001389602503619973</v>
       </c>
       <c r="G22" t="n">
-        <v>10.5045045045045</v>
+        <v>117.9072164948454</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6788531553398058</v>
+        <v>1.230295566502463</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>4936</v>
       </c>
       <c r="J22" t="n">
-        <v>38.18335427451367</v>
+        <v>26.32364432616601</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>21.08864867789759</v>
+        <v>10.51021511264258</v>
       </c>
       <c r="L22" t="n">
-        <v>23.8762916927858</v>
+        <v>12.00718203930038</v>
       </c>
       <c r="M22" t="n">
-        <v>24.57309396155174</v>
+        <v>11.1392224868865</v>
       </c>
       <c r="N22" t="n">
-        <v>56.96</v>
+        <v>20.78</v>
       </c>
       <c r="O22" t="n">
-        <v>5.76</v>
+        <v>8.26</v>
       </c>
       <c r="P22" t="n">
-        <v>0.51</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="R22" t="n">
-        <v>1535602.41</v>
+        <v>1503863.63</v>
       </c>
       <c r="S22" t="n">
-        <v>4475</v>
+        <v>141858</v>
       </c>
       <c r="T22" t="n">
-        <v>39.53403578159925</v>
+        <v>42.2423881483173</v>
       </c>
     </row>
   </sheetData>
@@ -2078,7 +2078,7 @@
         <v>776352</v>
       </c>
       <c r="T2" t="n">
-        <v>55.28378884950389</v>
+        <v>51.28288911006975</v>
       </c>
     </row>
     <row r="3">
@@ -2142,7 +2142,7 @@
         <v>26645</v>
       </c>
       <c r="T3" t="n">
-        <v>50.05123927590353</v>
+        <v>43.7068962147807</v>
       </c>
     </row>
     <row r="4">
@@ -2206,7 +2206,7 @@
         <v>20521</v>
       </c>
       <c r="T4" t="n">
-        <v>39.93760869022043</v>
+        <v>42.94800389990229</v>
       </c>
     </row>
     <row r="5">
@@ -2270,199 +2270,199 @@
         <v>118379</v>
       </c>
       <c r="T5" t="n">
-        <v>36.85487131369802</v>
+        <v>36.09489342813068</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.54654941693749</v>
+        <v>14.25227319776422</v>
       </c>
       <c r="C6" t="n">
-        <v>8.333875903379125</v>
+        <v>2.411546018687361</v>
       </c>
       <c r="D6" t="n">
-        <v>3.060025128683176</v>
+        <v>19.56369677362945</v>
       </c>
       <c r="E6" t="n">
-        <v>9.445547764763102</v>
+        <v>38.55469091544986</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7616899254444657</v>
+        <v>6.885742949503957</v>
       </c>
       <c r="G6" t="n">
-        <v>5.224737713970182</v>
+        <v>1.879527055815935</v>
       </c>
       <c r="H6" t="n">
-        <v>1.172420347359167</v>
+        <v>0.08884228106460039</v>
       </c>
       <c r="I6" t="n">
-        <v>925</v>
+        <v>-17468</v>
       </c>
       <c r="J6" t="n">
-        <v>19.82084189180693</v>
+        <v>16.41029009859514</v>
       </c>
       <c r="K6" t="n">
-        <v>9.211957132942761</v>
+        <v>15.49561308335803</v>
       </c>
       <c r="L6" t="n">
-        <v>7.557399109099472</v>
+        <v>22.07746495394836</v>
       </c>
       <c r="M6" t="n">
-        <v>5.922384104881218</v>
+        <v>15.89562187541786</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>9.539999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>2.38</v>
+        <v>3.7</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>2.18</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>146151.16</v>
+        <v>1807433.12</v>
       </c>
       <c r="S6" t="n">
-        <v>98692</v>
+        <v>45748</v>
       </c>
       <c r="T6" t="n">
-        <v>33.91957992781828</v>
+        <v>24.97145035706258</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18.53754343556428</v>
+        <v>11.54654941693749</v>
       </c>
       <c r="C7" t="n">
-        <v>9.13879785171331</v>
+        <v>8.333875903379125</v>
       </c>
       <c r="D7" t="n">
-        <v>8.822387437265419</v>
+        <v>3.060025128683176</v>
       </c>
       <c r="E7" t="n">
-        <v>17.89787025985418</v>
+        <v>9.445547764763102</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1.641441305333132</v>
+        <v>0.7616899254444657</v>
       </c>
       <c r="G7" t="n">
-        <v>3.764690170940171</v>
+        <v>5.224737713970182</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5925222177725139</v>
+        <v>1.172420347359167</v>
       </c>
       <c r="I7" t="n">
-        <v>-11245</v>
+        <v>925</v>
       </c>
       <c r="J7" t="n">
-        <v>23.2535428740343</v>
+        <v>19.82084189180693</v>
       </c>
       <c r="K7" t="n">
-        <v>5.838805854237616</v>
+        <v>9.211957132942761</v>
       </c>
       <c r="L7" t="n">
-        <v>15.31688706104797</v>
+        <v>7.557399109099472</v>
       </c>
       <c r="M7" t="n">
-        <v>16.17550991430385</v>
+        <v>5.922384104881218</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>14.22</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.38</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R7" t="n">
-        <v>4173085.48</v>
+        <v>146151.16</v>
       </c>
       <c r="S7" t="n">
-        <v>139078</v>
+        <v>98692</v>
       </c>
       <c r="T7" t="n">
-        <v>30.1618704592897</v>
+        <v>23.02128544550119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.25227319776422</v>
+        <v>18.53754343556428</v>
       </c>
       <c r="C8" t="n">
-        <v>2.411546018687361</v>
+        <v>9.13879785171331</v>
       </c>
       <c r="D8" t="n">
-        <v>19.56369677362945</v>
+        <v>8.822387437265419</v>
       </c>
       <c r="E8" t="n">
-        <v>38.55469091544986</v>
+        <v>17.89787025985418</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6.885742949503957</v>
+        <v>1.641441305333132</v>
       </c>
       <c r="G8" t="n">
-        <v>1.879527055815935</v>
+        <v>3.764690170940171</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08884228106460039</v>
+        <v>0.5925222177725139</v>
       </c>
       <c r="I8" t="n">
-        <v>-17468</v>
+        <v>-11245</v>
       </c>
       <c r="J8" t="n">
-        <v>16.41029009859514</v>
+        <v>23.2535428740343</v>
       </c>
       <c r="K8" t="n">
-        <v>15.49561308335803</v>
+        <v>5.838805854237616</v>
       </c>
       <c r="L8" t="n">
-        <v>22.07746495394836</v>
+        <v>15.31688706104797</v>
       </c>
       <c r="M8" t="n">
-        <v>15.89562187541786</v>
+        <v>16.17550991430385</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>8.99</v>
+        <v>14.22</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1.42</v>
+        <v>2.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R8" t="n">
-        <v>1807433.12</v>
+        <v>4173085.48</v>
       </c>
       <c r="S8" t="n">
-        <v>45748</v>
+        <v>139078</v>
       </c>
       <c r="T8" t="n">
-        <v>26.44635437536095</v>
+        <v>6.96190308800157</v>
       </c>
     </row>
   </sheetData>
@@ -2664,7 +2664,7 @@
         <v>4270</v>
       </c>
       <c r="T2" t="n">
-        <v>85.75992272430739</v>
+        <v>79.94074387215829</v>
       </c>
     </row>
     <row r="3">
@@ -2728,7 +2728,7 @@
         <v>12375</v>
       </c>
       <c r="T3" t="n">
-        <v>81.23496652577464</v>
+        <v>74.759015326533</v>
       </c>
     </row>
     <row r="4">
@@ -2786,7 +2786,7 @@
         <v>68904</v>
       </c>
       <c r="T4" t="n">
-        <v>69.54636475343268</v>
+        <v>74.17618738106648</v>
       </c>
     </row>
     <row r="5">
@@ -2850,263 +2850,263 @@
         <v>35517</v>
       </c>
       <c r="T5" t="n">
-        <v>68.09245734929726</v>
+        <v>54.82910568425711</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.2192057915469</v>
+        <v>17.99027109750765</v>
       </c>
       <c r="C6" t="n">
-        <v>18.55061995907066</v>
+        <v>3.168808778744431</v>
       </c>
       <c r="D6" t="n">
-        <v>6.843630099444054</v>
+        <v>28.8880112339828</v>
       </c>
       <c r="E6" t="n">
-        <v>10.35940803382664</v>
+        <v>62.41380175029464</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1.653145959757266</v>
+        <v>6.445624336310825</v>
       </c>
       <c r="G6" t="n">
-        <v>9.411954765751211</v>
+        <v>1.300946133138182</v>
       </c>
       <c r="H6" t="n">
-        <v>1.619298190002219</v>
+        <v>0.06747535915921023</v>
       </c>
       <c r="I6" t="n">
-        <v>1506</v>
+        <v>12547</v>
       </c>
       <c r="J6" t="n">
-        <v>33.14221885428872</v>
+        <v>21.39660074377121</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>20.89716395312024</v>
+        <v>17.25086850260209</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>20.27457629679304</v>
+        <v>51.94877118224903</v>
       </c>
       <c r="M6" t="n">
-        <v>19.50578386760935</v>
+        <v>55.18455739153598</v>
       </c>
       <c r="N6" t="n">
-        <v>10.13</v>
+        <v>25.76</v>
       </c>
       <c r="O6" t="n">
-        <v>10.51</v>
+        <v>6.2</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="R6" t="n">
-        <v>1793769.72</v>
+        <v>1319221.86</v>
       </c>
       <c r="S6" t="n">
-        <v>51084</v>
+        <v>159516</v>
       </c>
       <c r="T6" t="n">
-        <v>65.93993816050103</v>
+        <v>54.25483366558786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.56294790886726</v>
+        <v>37.2192057915469</v>
       </c>
       <c r="C7" t="n">
-        <v>17.9419388284085</v>
+        <v>18.55061995907066</v>
       </c>
       <c r="D7" t="n">
-        <v>4.993207190533383</v>
+        <v>6.843630099444054</v>
       </c>
       <c r="E7" t="n">
-        <v>8.084427730414067</v>
+        <v>10.35940803382664</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.03166114022890149</v>
+        <v>1.653145959757266</v>
       </c>
       <c r="G7" t="n">
-        <v>73.29310344827586</v>
+        <v>9.411954765751211</v>
       </c>
       <c r="H7" t="n">
-        <v>2.398875873795579</v>
+        <v>1.619298190002219</v>
       </c>
       <c r="I7" t="n">
-        <v>278</v>
+        <v>1506</v>
       </c>
       <c r="J7" t="n">
-        <v>28.1325519519273</v>
+        <v>33.14221885428872</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>20.48312440202782</v>
+        <v>20.89716395312024</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>22.96698996520703</v>
+        <v>20.27457629679304</v>
       </c>
       <c r="M7" t="n">
-        <v>22.74033782145131</v>
+        <v>19.50578386760935</v>
       </c>
       <c r="N7" t="n">
-        <v>72.53</v>
+        <v>10.13</v>
       </c>
       <c r="O7" t="n">
-        <v>11.71</v>
+        <v>10.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R7" t="n">
-        <v>3053088.97</v>
+        <v>1793769.72</v>
       </c>
       <c r="S7" t="n">
-        <v>50789</v>
+        <v>51084</v>
       </c>
       <c r="T7" t="n">
-        <v>59.54233552850971</v>
+        <v>50.35838701964626</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.0380853616381</v>
+        <v>18.65921787709497</v>
       </c>
       <c r="C8" t="n">
-        <v>1.390231951051347</v>
+        <v>17.44208682110181</v>
       </c>
       <c r="D8" t="n">
-        <v>24.0645524488647</v>
+        <v>14.92737430167598</v>
       </c>
       <c r="E8" t="n">
-        <v>99.50459748545694</v>
+        <v>24.67039106145252</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>8.378352548852153</v>
+        <v>0.4349162011173184</v>
       </c>
       <c r="G8" t="n">
-        <v>1.31948659270683</v>
+        <v>10.5045045045045</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05492885738906</v>
+        <v>0.6788531553398058</v>
       </c>
       <c r="I8" t="n">
-        <v>7906</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>19.10193873049559</v>
+        <v>38.18335427451367</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>19.06740855567788</v>
+        <v>21.08864867789759</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>23.24502393394037</v>
+        <v>23.8762916927858</v>
       </c>
       <c r="M8" t="n">
-        <v>20.11244339814313</v>
+        <v>24.57309396155174</v>
       </c>
       <c r="N8" t="n">
-        <v>9.81</v>
+        <v>56.96</v>
       </c>
       <c r="O8" t="n">
-        <v>3.91</v>
+        <v>5.76</v>
       </c>
       <c r="P8" t="n">
-        <v>2.82</v>
+        <v>0.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>2618348.58</v>
+        <v>1535602.41</v>
       </c>
       <c r="S8" t="n">
-        <v>26645</v>
+        <v>4475</v>
       </c>
       <c r="T8" t="n">
-        <v>50.05123927590353</v>
+        <v>49.94497755046469</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17.99027109750765</v>
+        <v>13.56294790886726</v>
       </c>
       <c r="C9" t="n">
-        <v>3.168808778744431</v>
+        <v>17.9419388284085</v>
       </c>
       <c r="D9" t="n">
-        <v>28.8880112339828</v>
+        <v>4.993207190533383</v>
       </c>
       <c r="E9" t="n">
-        <v>62.41380175029464</v>
+        <v>8.084427730414067</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>6.445624336310825</v>
+        <v>0.03166114022890149</v>
       </c>
       <c r="G9" t="n">
-        <v>1.300946133138182</v>
+        <v>73.29310344827586</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06747535915921023</v>
+        <v>2.398875873795579</v>
       </c>
       <c r="I9" t="n">
-        <v>12547</v>
+        <v>278</v>
       </c>
       <c r="J9" t="n">
-        <v>21.39660074377121</v>
+        <v>28.1325519519273</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>17.25086850260209</v>
+        <v>20.48312440202782</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>51.94877118224903</v>
+        <v>22.96698996520703</v>
       </c>
       <c r="M9" t="n">
-        <v>55.18455739153598</v>
+        <v>22.74033782145131</v>
       </c>
       <c r="N9" t="n">
-        <v>25.76</v>
+        <v>72.53</v>
       </c>
       <c r="O9" t="n">
-        <v>6.2</v>
+        <v>11.71</v>
       </c>
       <c r="P9" t="n">
-        <v>3.43</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1319221.86</v>
+        <v>3053088.97</v>
       </c>
       <c r="S9" t="n">
-        <v>159516</v>
+        <v>50789</v>
       </c>
       <c r="T9" t="n">
-        <v>49.77499869166721</v>
+        <v>49.2334625729186</v>
       </c>
     </row>
     <row r="10">
@@ -3170,455 +3170,455 @@
         <v>283649</v>
       </c>
       <c r="T10" t="n">
-        <v>48.88959773887582</v>
+        <v>47.16364601771759</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.534650424813185</v>
+        <v>16.71605179468811</v>
       </c>
       <c r="C11" t="n">
-        <v>4.719023623857606</v>
+        <v>1.368070466573592</v>
       </c>
       <c r="D11" t="n">
-        <v>3.458790097592848</v>
+        <v>13.93516047014541</v>
       </c>
       <c r="E11" t="n">
-        <v>11.79929683367731</v>
+        <v>41.75390656810141</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1.671358378544375</v>
+        <v>14.86741992554242</v>
       </c>
       <c r="G11" t="n">
-        <v>2.749286498353458</v>
+        <v>1.610661174334986</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6004321671876751</v>
+        <v>0.0719985042520674</v>
       </c>
       <c r="I11" t="n">
-        <v>-8455</v>
+        <v>13296</v>
       </c>
       <c r="J11" t="n">
-        <v>34.60338228109774</v>
+        <v>16.30293930023252</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>19.01541475308124</v>
+        <v>18.17561078322378</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>45.81058899665285</v>
+        <v>85.7752850068174</v>
       </c>
       <c r="M11" t="n">
-        <v>31.95079107728942</v>
+        <v>53.4206382524911</v>
       </c>
       <c r="N11" t="n">
-        <v>58.87</v>
+        <v>36.74</v>
       </c>
       <c r="O11" t="n">
-        <v>10.41</v>
+        <v>12.61</v>
       </c>
       <c r="P11" t="n">
-        <v>0.83</v>
+        <v>3.81</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="R11" t="n">
-        <v>187927.97</v>
+        <v>496415.88</v>
       </c>
       <c r="S11" t="n">
-        <v>96421</v>
+        <v>110519</v>
       </c>
       <c r="T11" t="n">
-        <v>46.93721822075608</v>
+        <v>46.09979877526326</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.8419213518306</v>
+        <v>13.0380853616381</v>
       </c>
       <c r="C12" t="n">
-        <v>5.218326568335486</v>
+        <v>1.390231951051347</v>
       </c>
       <c r="D12" t="n">
-        <v>26.28792839991269</v>
+        <v>24.0645524488647</v>
       </c>
       <c r="E12" t="n">
-        <v>29.28581823473769</v>
+        <v>99.50459748545694</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>3.824788776468134</v>
+        <v>8.378352548852153</v>
       </c>
       <c r="G12" t="n">
-        <v>2689.166666666667</v>
+        <v>1.31948659270683</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1463025160881669</v>
+        <v>0.05492885738906</v>
       </c>
       <c r="I12" t="n">
-        <v>-79931</v>
+        <v>7906</v>
       </c>
       <c r="J12" t="n">
-        <v>27.25940575809531</v>
+        <v>19.10193873049559</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>24.35264273954201</v>
+        <v>19.06740855567788</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>29.32313482597901</v>
+        <v>23.24502393394037</v>
       </c>
       <c r="M12" t="n">
-        <v>27.5561392815338</v>
+        <v>20.11244339814313</v>
       </c>
       <c r="N12" t="n">
-        <v>69.2</v>
+        <v>9.81</v>
       </c>
       <c r="O12" t="n">
-        <v>4.11</v>
+        <v>3.91</v>
       </c>
       <c r="P12" t="n">
-        <v>0.27</v>
+        <v>2.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="R12" t="n">
-        <v>2473271.58</v>
+        <v>2618348.58</v>
       </c>
       <c r="S12" t="n">
-        <v>54972</v>
+        <v>26645</v>
       </c>
       <c r="T12" t="n">
-        <v>41.62565089126185</v>
+        <v>43.7068962147807</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16.71605179468811</v>
+        <v>7.566793298872766</v>
       </c>
       <c r="C13" t="n">
-        <v>1.368070466573592</v>
+        <v>8.682297532507423</v>
       </c>
       <c r="D13" t="n">
-        <v>13.93516047014541</v>
+        <v>7.990266999868473</v>
       </c>
       <c r="E13" t="n">
-        <v>41.75390656810141</v>
+        <v>15.02038668946468</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>14.86741992554242</v>
+        <v>0.21654107242947</v>
       </c>
       <c r="G13" t="n">
-        <v>1.610661174334986</v>
+        <v>25.32183908045977</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0719985042520674</v>
+        <v>0.5454284586965099</v>
       </c>
       <c r="I13" t="n">
-        <v>13296</v>
+        <v>26</v>
       </c>
       <c r="J13" t="n">
-        <v>16.30293930023252</v>
+        <v>9.436125385661253</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>18.17561078322378</v>
+        <v>15.96086282879563</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>85.7752850068174</v>
+        <v>21.59956338772886</v>
       </c>
       <c r="M13" t="n">
-        <v>53.4206382524911</v>
+        <v>14.86983549970351</v>
       </c>
       <c r="N13" t="n">
-        <v>36.74</v>
+        <v>54.79</v>
       </c>
       <c r="O13" t="n">
-        <v>12.61</v>
+        <v>7.14</v>
       </c>
       <c r="P13" t="n">
-        <v>3.81</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="R13" t="n">
-        <v>496415.88</v>
+        <v>350543.35</v>
       </c>
       <c r="S13" t="n">
-        <v>110519</v>
+        <v>15206</v>
       </c>
       <c r="T13" t="n">
-        <v>41.24609119135111</v>
+        <v>43.51633606444935</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18.65921787709497</v>
+        <v>8.534650424813185</v>
       </c>
       <c r="C14" t="n">
-        <v>17.44208682110181</v>
+        <v>4.719023623857606</v>
       </c>
       <c r="D14" t="n">
-        <v>14.92737430167598</v>
+        <v>3.458790097592848</v>
       </c>
       <c r="E14" t="n">
-        <v>24.67039106145252</v>
+        <v>11.79929683367731</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.4349162011173184</v>
+        <v>1.671358378544375</v>
       </c>
       <c r="G14" t="n">
-        <v>10.5045045045045</v>
+        <v>2.749286498353458</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6788531553398058</v>
+        <v>0.6004321671876751</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-8455</v>
       </c>
       <c r="J14" t="n">
-        <v>38.18335427451367</v>
+        <v>34.60338228109774</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>21.08864867789759</v>
+        <v>19.01541475308124</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>23.8762916927858</v>
+        <v>45.81058899665285</v>
       </c>
       <c r="M14" t="n">
-        <v>24.57309396155174</v>
+        <v>31.95079107728942</v>
       </c>
       <c r="N14" t="n">
-        <v>56.96</v>
+        <v>58.87</v>
       </c>
       <c r="O14" t="n">
-        <v>5.76</v>
+        <v>10.41</v>
       </c>
       <c r="P14" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1535602.41</v>
+        <v>187927.97</v>
       </c>
       <c r="S14" t="n">
-        <v>4475</v>
+        <v>96421</v>
       </c>
       <c r="T14" t="n">
-        <v>39.53403578159925</v>
+        <v>43.08380814902782</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.566793298872766</v>
+        <v>18.8419213518306</v>
       </c>
       <c r="C15" t="n">
-        <v>8.682297532507423</v>
+        <v>5.218326568335486</v>
       </c>
       <c r="D15" t="n">
-        <v>7.990266999868473</v>
+        <v>26.28792839991269</v>
       </c>
       <c r="E15" t="n">
-        <v>15.02038668946468</v>
+        <v>29.28581823473769</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.21654107242947</v>
+        <v>3.824788776468134</v>
       </c>
       <c r="G15" t="n">
-        <v>25.32183908045977</v>
+        <v>2689.166666666667</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5454284586965099</v>
+        <v>0.1463025160881669</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>-79931</v>
       </c>
       <c r="J15" t="n">
-        <v>9.436125385661253</v>
+        <v>27.25940575809531</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>15.96086282879563</v>
+        <v>24.35264273954201</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>21.59956338772886</v>
+        <v>29.32313482597901</v>
       </c>
       <c r="M15" t="n">
-        <v>14.86983549970351</v>
+        <v>27.5561392815338</v>
       </c>
       <c r="N15" t="n">
-        <v>54.79</v>
+        <v>69.2</v>
       </c>
       <c r="O15" t="n">
-        <v>7.14</v>
+        <v>4.11</v>
       </c>
       <c r="P15" t="n">
-        <v>1.87</v>
+        <v>0.27</v>
       </c>
       <c r="Q15" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
-        <v>350543.35</v>
+        <v>2473271.58</v>
       </c>
       <c r="S15" t="n">
-        <v>15206</v>
+        <v>54972</v>
       </c>
       <c r="T15" t="n">
-        <v>38.49853226294994</v>
+        <v>42.97457272117435</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.7618637908999</v>
+        <v>25.85035141227954</v>
       </c>
       <c r="C16" t="n">
-        <v>1.639620355976648</v>
+        <v>6.12006493711007</v>
       </c>
       <c r="D16" t="n">
-        <v>15.93948250956673</v>
+        <v>14.12820930948886</v>
       </c>
       <c r="E16" t="n">
-        <v>37.4889127294537</v>
+        <v>37.04045949520755</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>12.14371872728943</v>
+        <v>4.789368120938867</v>
       </c>
       <c r="G16" t="n">
-        <v>1.896747724261721</v>
+        <v>2.197130112323319</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07153782236255685</v>
+        <v>0.2053943414307379</v>
       </c>
       <c r="I16" t="n">
-        <v>-7559</v>
+        <v>-79634</v>
       </c>
       <c r="J16" t="n">
-        <v>16.78883948962531</v>
+        <v>22.13149041552844</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>17.47729766589094</v>
+        <v>20.97274568418761</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>74.50588066551305</v>
+        <v>23.74781614270227</v>
       </c>
       <c r="M16" t="n">
-        <v>55.18455739153598</v>
+        <v>20.58909506066124</v>
       </c>
       <c r="N16" t="n">
-        <v>16.89</v>
+        <v>15.07</v>
       </c>
       <c r="O16" t="n">
-        <v>4.15</v>
+        <v>6.08</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>590971.02</v>
+        <v>1905112.17</v>
       </c>
       <c r="S16" t="n">
-        <v>118379</v>
+        <v>110382</v>
       </c>
       <c r="T16" t="n">
-        <v>36.85487131369802</v>
+        <v>38.40876341598192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25.85035141227954</v>
+        <v>15.7618637908999</v>
       </c>
       <c r="C17" t="n">
-        <v>6.12006493711007</v>
+        <v>1.639620355976648</v>
       </c>
       <c r="D17" t="n">
-        <v>14.12820930948886</v>
+        <v>15.93948250956673</v>
       </c>
       <c r="E17" t="n">
-        <v>37.04045949520755</v>
+        <v>37.4889127294537</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>4.789368120938867</v>
+        <v>12.14371872728943</v>
       </c>
       <c r="G17" t="n">
-        <v>2.197130112323319</v>
+        <v>1.896747724261721</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2053943414307379</v>
+        <v>0.07153782236255685</v>
       </c>
       <c r="I17" t="n">
-        <v>-79634</v>
+        <v>-7559</v>
       </c>
       <c r="J17" t="n">
-        <v>22.13149041552844</v>
+        <v>16.78883948962531</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>20.97274568418761</v>
+        <v>17.47729766589094</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>23.74781614270227</v>
+        <v>74.50588066551305</v>
       </c>
       <c r="M17" t="n">
-        <v>20.58909506066124</v>
+        <v>55.18455739153598</v>
       </c>
       <c r="N17" t="n">
-        <v>15.07</v>
+        <v>16.89</v>
       </c>
       <c r="O17" t="n">
-        <v>6.08</v>
+        <v>4.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="R17" t="n">
-        <v>1905112.17</v>
+        <v>590971.02</v>
       </c>
       <c r="S17" t="n">
-        <v>110382</v>
+        <v>118379</v>
       </c>
       <c r="T17" t="n">
-        <v>32.61569326725172</v>
+        <v>36.09489342813068</v>
       </c>
     </row>
     <row r="18">
@@ -3682,7 +3682,7 @@
         <v>36388</v>
       </c>
       <c r="T18" t="n">
-        <v>28.24447538501256</v>
+        <v>27.62899709111431</v>
       </c>
     </row>
     <row r="19">
@@ -3746,7 +3746,7 @@
         <v>19163</v>
       </c>
       <c r="T19" t="n">
-        <v>26.51794275934105</v>
+        <v>26.12030955422183</v>
       </c>
     </row>
     <row r="20">
@@ -3810,7 +3810,7 @@
         <v>45748</v>
       </c>
       <c r="T20" t="n">
-        <v>26.44635437536095</v>
+        <v>24.97145035706258</v>
       </c>
     </row>
   </sheetData>
@@ -3954,65 +3954,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.30776794493609</v>
+        <v>29.67748825288338</v>
       </c>
       <c r="C2" t="n">
-        <v>33.00120254251846</v>
+        <v>34.65710782001698</v>
       </c>
       <c r="D2" t="n">
-        <v>11.93535353535353</v>
+        <v>15.6585434568249</v>
       </c>
       <c r="E2" t="n">
-        <v>15.92727272727273</v>
+        <v>21.3692069305536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4309242871189774</v>
+        <v>0.1321016659547202</v>
       </c>
       <c r="G2" t="n">
-        <v>8.043478260869565</v>
+        <v>41.00487804878049</v>
       </c>
       <c r="H2" t="n">
-        <v>1.727869310248534</v>
+        <v>1.187084044011906</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>841</v>
+        <v>3556</v>
       </c>
       <c r="J2" t="n">
-        <v>68.36335197744833</v>
+        <v>17.80103767695105</v>
       </c>
       <c r="K2" t="n">
-        <v>36.30691600183056</v>
+        <v>13.02966034945308</v>
       </c>
       <c r="L2" t="n">
-        <v>73.11367578503176</v>
+        <v>20.27736210195506</v>
       </c>
       <c r="M2" t="n">
-        <v>69.52182030724354</v>
+        <v>20.97355268843126</v>
       </c>
       <c r="N2" t="n">
-        <v>8.65</v>
+        <v>73.37</v>
       </c>
       <c r="O2" t="n">
-        <v>11.82</v>
+        <v>3.9</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>3.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="R2" t="n">
-        <v>571322.04</v>
+        <v>2126725.18</v>
       </c>
       <c r="S2" t="n">
-        <v>12375</v>
+        <v>35495</v>
       </c>
       <c r="T2" t="n">
-        <v>81.23496652577464</v>
+        <v>84.54663657417515</v>
       </c>
     </row>
     <row r="3">
@@ -4070,1644 +4070,1644 @@
         <v>30381</v>
       </c>
       <c r="T3" t="n">
-        <v>76.26614180892425</v>
+        <v>80.11686765708708</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
-        </is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>117.7544910179641</v>
+      </c>
+      <c r="C4" t="n">
+        <v>143.527815468114</v>
       </c>
       <c r="D4" t="n">
-        <v>11.8527226285847</v>
+        <v>16.12281708616873</v>
       </c>
       <c r="E4" t="n">
-        <v>76.29890862649484</v>
+        <v>23.82963023694351</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01857923497267759</v>
+        <v>0.1032934131736527</v>
       </c>
       <c r="G4" t="n">
-        <v>22.61263972484953</v>
+        <v>41.18620689655172</v>
       </c>
       <c r="H4" t="n">
-        <v>56.38625204582652</v>
+        <v>2.318160220469448</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9424</v>
+        <v>2938</v>
       </c>
       <c r="J4" t="n">
-        <v>67.58091776468258</v>
+        <v>18.28200866249903</v>
       </c>
       <c r="K4" t="n">
-        <v>19.31335512580617</v>
+        <v>14.54857371180267</v>
       </c>
       <c r="L4" t="n">
-        <v>120.6925086746793</v>
+        <v>14.85231951299384</v>
       </c>
       <c r="M4" t="n">
-        <v>121.2356822276117</v>
+        <v>15.43852585822143</v>
       </c>
       <c r="N4" t="n">
-        <v>76.23</v>
+        <v>54.96</v>
       </c>
       <c r="O4" t="n">
-        <v>7.87</v>
+        <v>14.34</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>4.27</v>
+        <v>3.85</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="R4" t="n">
-        <v>1040632.92</v>
+        <v>1677775.19</v>
       </c>
       <c r="S4" t="n">
-        <v>68904</v>
+        <v>24394</v>
       </c>
       <c r="T4" t="n">
-        <v>69.54636475343268</v>
+        <v>76.26865270052919</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.9043860525527</v>
+        <v>13.57678765646027</v>
       </c>
       <c r="C5" t="n">
-        <v>27.38467110326407</v>
+        <v>13.79672251887314</v>
       </c>
       <c r="D5" t="n">
-        <v>12.90931103415266</v>
+        <v>432.7262044653349</v>
       </c>
       <c r="E5" t="n">
-        <v>17.98293774812062</v>
+        <v>91.77438307873091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1034568888000799</v>
+        <v>0.001161354544951794</v>
       </c>
       <c r="G5" t="n">
-        <v>31.93243243243243</v>
+        <v>3764.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.289464130119082</v>
+        <v>0.02611991835607188</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1752</v>
+        <v>1469</v>
       </c>
       <c r="J5" t="n">
-        <v>42.13101535214459</v>
+        <v>55.00574158769729</v>
       </c>
       <c r="K5" t="n">
-        <v>30.32798083513346</v>
+        <v>31.61229344896917</v>
       </c>
       <c r="L5" t="n">
-        <v>24.775129058601</v>
+        <v>19.2975590637313</v>
       </c>
       <c r="M5" t="n">
-        <v>12.24383304425547</v>
+        <v>18.96864732798973</v>
       </c>
       <c r="N5" t="n">
-        <v>64.52</v>
+        <v>37.73</v>
       </c>
       <c r="O5" t="n">
-        <v>2.38</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>4.43</v>
+        <v>3.37</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
-        <v>1347046.9</v>
+        <v>2191568.13</v>
       </c>
       <c r="S5" t="n">
-        <v>35517</v>
+        <v>1702</v>
       </c>
       <c r="T5" t="n">
-        <v>68.09245734929726</v>
+        <v>75.54487526078582</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.57678765646027</v>
+        <v>36.30776794493609</v>
       </c>
       <c r="C6" t="n">
-        <v>13.79672251887314</v>
+        <v>33.00120254251846</v>
       </c>
       <c r="D6" t="n">
-        <v>432.7262044653349</v>
+        <v>11.93535353535353</v>
       </c>
       <c r="E6" t="n">
-        <v>91.77438307873091</v>
+        <v>15.92727272727273</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001161354544951794</v>
+        <v>0.4309242871189774</v>
       </c>
       <c r="G6" t="n">
-        <v>3764.5</v>
+        <v>8.043478260869565</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02611991835607188</v>
+        <v>1.727869310248534</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1469</v>
+        <v>841</v>
       </c>
       <c r="J6" t="n">
-        <v>55.00574158769729</v>
+        <v>68.36335197744833</v>
       </c>
       <c r="K6" t="n">
-        <v>31.61229344896917</v>
+        <v>36.30691600183056</v>
       </c>
       <c r="L6" t="n">
-        <v>19.2975590637313</v>
+        <v>73.11367578503176</v>
       </c>
       <c r="M6" t="n">
-        <v>18.96864732798973</v>
+        <v>69.52182030724354</v>
       </c>
       <c r="N6" t="n">
-        <v>37.73</v>
+        <v>8.65</v>
       </c>
       <c r="O6" t="n">
-        <v>9.380000000000001</v>
+        <v>11.82</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>3.37</v>
+        <v>3.46</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>2191568.13</v>
+        <v>571322.04</v>
       </c>
       <c r="S6" t="n">
-        <v>1702</v>
+        <v>12375</v>
       </c>
       <c r="T6" t="n">
-        <v>67.8491262474583</v>
+        <v>74.759015326533</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>29.67748825288338</v>
-      </c>
-      <c r="C7" t="n">
-        <v>34.65710782001698</v>
+          <t>INDIGO</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6585434568249</v>
+        <v>11.8527226285847</v>
       </c>
       <c r="E7" t="n">
-        <v>21.3692069305536</v>
+        <v>76.29890862649484</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1321016659547202</v>
+        <v>0.01857923497267759</v>
       </c>
       <c r="G7" t="n">
-        <v>41.00487804878049</v>
+        <v>22.61263972484953</v>
       </c>
       <c r="H7" t="n">
-        <v>1.187084044011906</v>
+        <v>56.38625204582652</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>3556</v>
+        <v>9424</v>
       </c>
       <c r="J7" t="n">
-        <v>17.80103767695105</v>
+        <v>67.58091776468258</v>
       </c>
       <c r="K7" t="n">
-        <v>13.02966034945308</v>
+        <v>19.31335512580617</v>
       </c>
       <c r="L7" t="n">
-        <v>20.27736210195506</v>
+        <v>120.6925086746793</v>
       </c>
       <c r="M7" t="n">
-        <v>20.97355268843126</v>
+        <v>121.2356822276117</v>
       </c>
       <c r="N7" t="n">
-        <v>73.37</v>
+        <v>76.23</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>7.87</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>2.42</v>
+        <v>4.27</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2126725.18</v>
+        <v>1040632.92</v>
       </c>
       <c r="S7" t="n">
-        <v>35495</v>
+        <v>68904</v>
       </c>
       <c r="T7" t="n">
-        <v>67.37697048318884</v>
+        <v>74.17618738106648</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>117.7544910179641</v>
+        <v>45.16982956605826</v>
       </c>
       <c r="C8" t="n">
-        <v>143.527815468114</v>
+        <v>54.69059863534</v>
       </c>
       <c r="D8" t="n">
-        <v>16.12281708616873</v>
+        <v>26.25628846856468</v>
       </c>
       <c r="E8" t="n">
-        <v>23.82963023694351</v>
+        <v>66.29380849329698</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1032934131736527</v>
+        <v>0.0788468512027076</v>
       </c>
       <c r="G8" t="n">
-        <v>41.18620689655172</v>
+        <v>11.24178180085755</v>
       </c>
       <c r="H8" t="n">
-        <v>2.318160220469448</v>
+        <v>0.6018691588785047</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2938</v>
+        <v>13617</v>
       </c>
       <c r="J8" t="n">
-        <v>18.28200866249903</v>
+        <v>16.49395652851666</v>
       </c>
       <c r="K8" t="n">
-        <v>14.54857371180267</v>
+        <v>7.402890725901301</v>
       </c>
       <c r="L8" t="n">
-        <v>14.85231951299384</v>
+        <v>16.43231987118112</v>
       </c>
       <c r="M8" t="n">
-        <v>15.43852585822143</v>
+        <v>16.85151856943003</v>
       </c>
       <c r="N8" t="n">
-        <v>54.96</v>
+        <v>34.27</v>
       </c>
       <c r="O8" t="n">
-        <v>14.34</v>
+        <v>14.75</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>3.85</v>
+        <v>4.38</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="R8" t="n">
-        <v>1677775.19</v>
+        <v>454024.84</v>
       </c>
       <c r="S8" t="n">
-        <v>24394</v>
+        <v>142324</v>
       </c>
       <c r="T8" t="n">
-        <v>66.8729916012617</v>
+        <v>68.39225391955706</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45.16982956605826</v>
+        <v>49.44710986501021</v>
       </c>
       <c r="C9" t="n">
-        <v>54.69059863534</v>
+        <v>56.81656132548613</v>
       </c>
       <c r="D9" t="n">
-        <v>26.25628846856468</v>
+        <v>4.836600998148862</v>
       </c>
       <c r="E9" t="n">
-        <v>66.29380849329698</v>
+        <v>3.87474201090824</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0788468512027076</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>11.24178180085755</v>
+        <v>371.9375</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6018691588785047</v>
+        <v>0.1591344094587576</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>13617</v>
+        <v>853</v>
       </c>
       <c r="J9" t="n">
-        <v>16.49395652851666</v>
+        <v>6.981735429882496</v>
       </c>
       <c r="K9" t="n">
-        <v>7.402890725901301</v>
+        <v>8.15986061977938</v>
       </c>
       <c r="L9" t="n">
-        <v>16.43231987118112</v>
-      </c>
-      <c r="M9" t="n">
-        <v>16.85151856943003</v>
+        <v>73.17556747076097</v>
       </c>
       <c r="N9" t="n">
-        <v>34.27</v>
+        <v>30.67</v>
       </c>
       <c r="O9" t="n">
-        <v>14.75</v>
+        <v>8.1</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>4.38</v>
+        <v>3.77</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
-        <v>454024.84</v>
+        <v>183583.67</v>
       </c>
       <c r="S9" t="n">
-        <v>142324</v>
+        <v>845966</v>
       </c>
       <c r="T9" t="n">
-        <v>66.64461659726513</v>
+        <v>62.95324388299893</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37.2192057915469</v>
+        <v>26.61418410330778</v>
       </c>
       <c r="C10" t="n">
-        <v>18.55061995907066</v>
+        <v>32.51927187925115</v>
       </c>
       <c r="D10" t="n">
-        <v>6.843630099444054</v>
+        <v>17.17851571205706</v>
       </c>
       <c r="E10" t="n">
-        <v>10.35940803382664</v>
+        <v>19.53420993982616</v>
       </c>
       <c r="F10" t="n">
-        <v>1.653145959757266</v>
+        <v>0.06601754022512257</v>
       </c>
       <c r="G10" t="n">
-        <v>9.411954765751211</v>
+        <v>174.4166666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>1.619298190002219</v>
+        <v>1.140453436356242</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1506</v>
+        <v>6486</v>
       </c>
       <c r="J10" t="n">
-        <v>33.14221885428872</v>
+        <v>17.38465261667195</v>
       </c>
       <c r="K10" t="n">
-        <v>20.89716395312024</v>
+        <v>8.127604751021389</v>
       </c>
       <c r="L10" t="n">
-        <v>20.27457629679304</v>
+        <v>9.358917170384974</v>
       </c>
       <c r="M10" t="n">
-        <v>19.50578386760935</v>
+        <v>10.17727634846559</v>
       </c>
       <c r="N10" t="n">
-        <v>10.13</v>
+        <v>29.91</v>
       </c>
       <c r="O10" t="n">
-        <v>10.51</v>
+        <v>9.83</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>3.1</v>
+        <v>3.59</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R10" t="n">
-        <v>1793769.72</v>
+        <v>653817.3</v>
       </c>
       <c r="S10" t="n">
-        <v>51084</v>
+        <v>44870</v>
       </c>
       <c r="T10" t="n">
-        <v>65.93993816050103</v>
+        <v>59.33632474653394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26.61418410330778</v>
+        <v>15.7230643179025</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51927187925115</v>
+        <v>20.87418300653595</v>
       </c>
       <c r="D11" t="n">
-        <v>17.17851571205706</v>
+        <v>9.366915605017816</v>
       </c>
       <c r="E11" t="n">
-        <v>19.53420993982616</v>
+        <v>87.42129155073948</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06601754022512257</v>
+        <v>0.002867677181482999</v>
       </c>
       <c r="G11" t="n">
-        <v>174.4166666666667</v>
+        <v>160.0267857142857</v>
       </c>
       <c r="H11" t="n">
-        <v>1.140453436356242</v>
+        <v>0.3236083907247109</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6486</v>
+        <v>486</v>
       </c>
       <c r="J11" t="n">
-        <v>17.38465261667195</v>
+        <v>18.98796206427069</v>
       </c>
       <c r="K11" t="n">
-        <v>8.127604751021389</v>
+        <v>12.91184100336258</v>
       </c>
       <c r="L11" t="n">
-        <v>9.358917170384974</v>
+        <v>12.83917371819816</v>
       </c>
       <c r="M11" t="n">
-        <v>10.17727634846559</v>
+        <v>11.1392224868865</v>
       </c>
       <c r="N11" t="n">
-        <v>29.91</v>
+        <v>49</v>
       </c>
       <c r="O11" t="n">
-        <v>9.83</v>
+        <v>7.86</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>3.59</v>
+        <v>3.46</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>653817.3</v>
+        <v>1271789.21</v>
       </c>
       <c r="S11" t="n">
-        <v>44870</v>
+        <v>20487</v>
       </c>
       <c r="T11" t="n">
-        <v>64.21754306421302</v>
+        <v>59.23751631808607</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49.44710986501021</v>
+        <v>1.153456416595399</v>
       </c>
       <c r="C12" t="n">
-        <v>56.81656132548613</v>
+        <v>1.405707632934954</v>
       </c>
       <c r="D12" t="n">
-        <v>4.836600998148862</v>
+        <v>86.52291105121293</v>
       </c>
       <c r="E12" t="n">
-        <v>3.87474201090824</v>
+        <v>84.04312668463612</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>371.9375</v>
+        <v>198.8</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1591344094587576</v>
+        <v>0.0128052021565203</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>853</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6.981735429882496</v>
-      </c>
-      <c r="K12" t="n">
-        <v>8.15986061977938</v>
-      </c>
-      <c r="L12" t="n">
-        <v>73.17556747076097</v>
+        <v>763</v>
       </c>
       <c r="N12" t="n">
-        <v>30.67</v>
+        <v>34.24</v>
       </c>
       <c r="O12" t="n">
-        <v>8.1</v>
+        <v>9.91</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>3.77</v>
+        <v>3.09</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>183583.67</v>
+        <v>1401774.99</v>
       </c>
       <c r="S12" t="n">
-        <v>845966</v>
+        <v>1855</v>
       </c>
       <c r="T12" t="n">
-        <v>63.42665470127236</v>
+        <v>55.30519904723734</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15.09416181067115</v>
+        <v>22.9043860525527</v>
       </c>
       <c r="C13" t="n">
-        <v>16.56383979922618</v>
+        <v>27.38467110326407</v>
       </c>
       <c r="D13" t="n">
-        <v>19.81565870053818</v>
+        <v>12.90931103415266</v>
       </c>
       <c r="E13" t="n">
-        <v>26.84289749881436</v>
+        <v>17.98293774812062</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05142381453500244</v>
+        <v>0.1034568888000799</v>
       </c>
       <c r="G13" t="n">
-        <v>58.33193277310924</v>
+        <v>31.93243243243243</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5684929901064378</v>
+        <v>1.289464130119082</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>11372</v>
+        <v>1752</v>
       </c>
       <c r="J13" t="n">
-        <v>13.12675558948349</v>
+        <v>42.13101535214459</v>
       </c>
       <c r="K13" t="n">
-        <v>10.78116321985565</v>
+        <v>30.32798083513346</v>
       </c>
       <c r="L13" t="n">
-        <v>24.53682964293125</v>
+        <v>24.775129058601</v>
       </c>
       <c r="M13" t="n">
-        <v>29.45936165164078</v>
+        <v>12.24383304425547</v>
       </c>
       <c r="N13" t="n">
-        <v>37.9</v>
+        <v>64.52</v>
       </c>
       <c r="O13" t="n">
-        <v>6.71</v>
+        <v>2.38</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>3.88</v>
+        <v>4.43</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="R13" t="n">
-        <v>1339586.09</v>
+        <v>1347046.9</v>
       </c>
       <c r="S13" t="n">
-        <v>48497</v>
+        <v>35517</v>
       </c>
       <c r="T13" t="n">
-        <v>62.40707534502386</v>
+        <v>54.82910568425711</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>37.45613415294755</v>
+        <v>17.99027109750765</v>
       </c>
       <c r="C14" t="n">
-        <v>14.54625871578728</v>
+        <v>3.168808778744431</v>
       </c>
       <c r="D14" t="n">
-        <v>7.263066074788551</v>
+        <v>28.8880112339828</v>
       </c>
       <c r="E14" t="n">
-        <v>13.59538554282896</v>
+        <v>62.41380175029464</v>
       </c>
       <c r="F14" t="n">
-        <v>1.263124425916767</v>
+        <v>6.445624336310825</v>
       </c>
       <c r="G14" t="n">
-        <v>6.530242339274985</v>
+        <v>1.300946133138182</v>
       </c>
       <c r="H14" t="n">
-        <v>1.185123443593192</v>
+        <v>0.06747535915921023</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45133</v>
+        <v>12547</v>
       </c>
       <c r="J14" t="n">
-        <v>20.57936456937097</v>
+        <v>21.39660074377121</v>
       </c>
       <c r="K14" t="n">
-        <v>7.720159538623927</v>
+        <v>17.25086850260209</v>
+      </c>
+      <c r="L14" t="n">
+        <v>51.94877118224903</v>
+      </c>
+      <c r="M14" t="n">
+        <v>55.18455739153598</v>
       </c>
       <c r="N14" t="n">
-        <v>67.06999999999999</v>
+        <v>25.76</v>
       </c>
       <c r="O14" t="n">
-        <v>0.93</v>
+        <v>6.2</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>3.65</v>
+        <v>3.43</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="R14" t="n">
-        <v>1504106.64</v>
+        <v>1319221.86</v>
       </c>
       <c r="S14" t="n">
-        <v>437928</v>
+        <v>159516</v>
       </c>
       <c r="T14" t="n">
-        <v>58.76428095055527</v>
+        <v>54.25483366558786</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.7230643179025</v>
+        <v>22.17234691050152</v>
       </c>
       <c r="C15" t="n">
-        <v>20.87418300653595</v>
+        <v>28.17374350086655</v>
       </c>
       <c r="D15" t="n">
-        <v>9.366915605017816</v>
+        <v>24.19569424286405</v>
       </c>
       <c r="E15" t="n">
-        <v>87.42129155073948</v>
+        <v>26.17924528301887</v>
       </c>
       <c r="F15" t="n">
-        <v>0.002867677181482999</v>
+        <v>0.02321972845663619</v>
       </c>
       <c r="G15" t="n">
-        <v>160.0267857142857</v>
+        <v>114.7058823529412</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3236083907247109</v>
+        <v>0.7153796236210254</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>486</v>
+        <v>890</v>
       </c>
       <c r="J15" t="n">
-        <v>18.98796206427069</v>
+        <v>23.776441520116</v>
       </c>
       <c r="K15" t="n">
-        <v>12.91184100336258</v>
+        <v>11.03693649673969</v>
       </c>
       <c r="L15" t="n">
-        <v>12.83917371819816</v>
+        <v>12.6758416653777</v>
       </c>
       <c r="M15" t="n">
-        <v>11.1392224868865</v>
+        <v>12.50545162905032</v>
       </c>
       <c r="N15" t="n">
-        <v>49</v>
+        <v>15.62</v>
       </c>
       <c r="O15" t="n">
-        <v>7.86</v>
+        <v>13.61</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>3.46</v>
+        <v>4.41</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>1271789.21</v>
+        <v>222391.83</v>
       </c>
       <c r="S15" t="n">
-        <v>20487</v>
+        <v>16536</v>
       </c>
       <c r="T15" t="n">
-        <v>58.37486301103623</v>
+        <v>52.44066966339204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22.17234691050152</v>
+        <v>37.45613415294755</v>
       </c>
       <c r="C16" t="n">
-        <v>28.17374350086655</v>
+        <v>14.54625871578728</v>
       </c>
       <c r="D16" t="n">
-        <v>24.19569424286405</v>
+        <v>7.263066074788551</v>
       </c>
       <c r="E16" t="n">
-        <v>26.17924528301887</v>
+        <v>13.59538554282896</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02321972845663619</v>
+        <v>1.263124425916767</v>
       </c>
       <c r="G16" t="n">
-        <v>114.7058823529412</v>
+        <v>6.530242339274985</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7153796236210254</v>
+        <v>1.185123443593192</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>890</v>
+        <v>45133</v>
       </c>
       <c r="J16" t="n">
-        <v>23.776441520116</v>
+        <v>20.57936456937097</v>
       </c>
       <c r="K16" t="n">
-        <v>11.03693649673969</v>
-      </c>
-      <c r="L16" t="n">
-        <v>12.6758416653777</v>
-      </c>
-      <c r="M16" t="n">
-        <v>12.50545162905032</v>
+        <v>7.720159538623927</v>
       </c>
       <c r="N16" t="n">
-        <v>15.62</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>13.61</v>
+        <v>0.93</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>4.41</v>
+        <v>3.65</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="R16" t="n">
-        <v>222391.83</v>
+        <v>1504106.64</v>
       </c>
       <c r="S16" t="n">
-        <v>16536</v>
+        <v>437928</v>
       </c>
       <c r="T16" t="n">
-        <v>58.08734076782807</v>
+        <v>51.6052090535713</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.153456416595399</v>
+        <v>15.09416181067115</v>
       </c>
       <c r="C17" t="n">
-        <v>1.405707632934954</v>
+        <v>16.56383979922618</v>
       </c>
       <c r="D17" t="n">
-        <v>86.52291105121293</v>
+        <v>19.81565870053818</v>
       </c>
       <c r="E17" t="n">
-        <v>84.04312668463612</v>
+        <v>26.84289749881436</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.05142381453500244</v>
       </c>
       <c r="G17" t="n">
-        <v>198.8</v>
+        <v>58.33193277310924</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0128052021565203</v>
+        <v>0.5684929901064378</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>763</v>
+        <v>11372</v>
+      </c>
+      <c r="J17" t="n">
+        <v>13.12675558948349</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10.78116321985565</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24.53682964293125</v>
+      </c>
+      <c r="M17" t="n">
+        <v>29.45936165164078</v>
       </c>
       <c r="N17" t="n">
-        <v>34.24</v>
+        <v>37.9</v>
       </c>
       <c r="O17" t="n">
-        <v>9.91</v>
+        <v>6.71</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>3.09</v>
+        <v>3.88</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R17" t="n">
-        <v>1401774.99</v>
+        <v>1339586.09</v>
       </c>
       <c r="S17" t="n">
-        <v>1855</v>
+        <v>48497</v>
       </c>
       <c r="T17" t="n">
-        <v>56.61415948750577</v>
+        <v>51.37713526020612</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17.87001124549607</v>
+        <v>37.2192057915469</v>
       </c>
       <c r="C18" t="n">
-        <v>8.788485820888438</v>
+        <v>18.55061995907066</v>
       </c>
       <c r="D18" t="n">
-        <v>33.97028990249329</v>
+        <v>6.843630099444054</v>
       </c>
       <c r="E18" t="n">
-        <v>86.87476823070044</v>
+        <v>10.35940803382664</v>
       </c>
       <c r="F18" t="n">
-        <v>1.417345603929039</v>
+        <v>1.653145959757266</v>
       </c>
       <c r="G18" t="n">
-        <v>4.60298643565485</v>
+        <v>9.411954765751211</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1827659481160472</v>
+        <v>1.619298190002219</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24176</v>
+        <v>1506</v>
       </c>
       <c r="J18" t="n">
-        <v>4.965471644662767</v>
+        <v>33.14221885428872</v>
       </c>
       <c r="K18" t="n">
-        <v>5.510261937513361</v>
+        <v>20.89716395312024</v>
       </c>
       <c r="L18" t="n">
-        <v>9.189188268434778</v>
+        <v>20.27457629679304</v>
       </c>
       <c r="M18" t="n">
-        <v>9.096607850144967</v>
+        <v>19.50578386760935</v>
       </c>
       <c r="N18" t="n">
-        <v>64.39</v>
+        <v>10.13</v>
       </c>
       <c r="O18" t="n">
-        <v>5.1</v>
+        <v>10.51</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="R18" t="n">
-        <v>372584.24</v>
+        <v>1793769.72</v>
       </c>
       <c r="S18" t="n">
-        <v>45843</v>
+        <v>51084</v>
       </c>
       <c r="T18" t="n">
-        <v>55.81312913510921</v>
+        <v>50.35838701964626</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13.48039215686275</v>
+        <v>17.06727541291795</v>
       </c>
       <c r="C19" t="n">
-        <v>11.1011492379167</v>
+        <v>22.0258064516129</v>
       </c>
       <c r="D19" t="n">
-        <v>4.905818773282963</v>
+        <v>6.837009144701453</v>
       </c>
       <c r="E19" t="n">
-        <v>12.56099480560365</v>
+        <v>10.11834319526627</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7688869665513264</v>
+        <v>0.040687525177924</v>
       </c>
       <c r="G19" t="n">
-        <v>5.565701559020044</v>
+        <v>25.35714285714286</v>
       </c>
       <c r="H19" t="n">
-        <v>1.138394457054115</v>
+        <v>1.495214348910158</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>383</v>
+        <v>335</v>
       </c>
       <c r="J19" t="n">
-        <v>21.75273635187671</v>
+        <v>21.14089015706202</v>
       </c>
       <c r="K19" t="n">
-        <v>14.66004260219314</v>
+        <v>13.03790793906312</v>
       </c>
       <c r="L19" t="n">
-        <v>36.13077689773863</v>
+        <v>10.03323122942004</v>
       </c>
       <c r="M19" t="n">
-        <v>29.95061094416296</v>
+        <v>8.997698704834534</v>
       </c>
       <c r="N19" t="n">
-        <v>47.72</v>
+        <v>45.41</v>
       </c>
       <c r="O19" t="n">
-        <v>7.68</v>
+        <v>14.08</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="R19" t="n">
-        <v>1905622.43</v>
+        <v>2521508.87</v>
       </c>
       <c r="S19" t="n">
-        <v>19059</v>
+        <v>18590</v>
       </c>
       <c r="T19" t="n">
-        <v>51.34713033502982</v>
+        <v>48.75439737462181</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13.0380853616381</v>
+        <v>14.33974005030719</v>
       </c>
       <c r="C20" t="n">
-        <v>1.390231951051347</v>
+        <v>2.148461558534627</v>
       </c>
       <c r="D20" t="n">
-        <v>24.0645524488647</v>
+        <v>23.07288232992184</v>
       </c>
       <c r="E20" t="n">
-        <v>99.50459748545694</v>
+        <v>61.41252040373843</v>
       </c>
       <c r="F20" t="n">
-        <v>8.378352548852153</v>
+        <v>6.808786667718385</v>
       </c>
       <c r="G20" t="n">
-        <v>1.31948659270683</v>
+        <v>1.400768822479211</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05492885738906</v>
+        <v>0.07038097917866981</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7906</v>
+        <v>35669</v>
       </c>
       <c r="J20" t="n">
-        <v>19.10193873049559</v>
+        <v>30.18695614094877</v>
       </c>
       <c r="K20" t="n">
-        <v>19.06740855567788</v>
+        <v>21.95098428169122</v>
       </c>
       <c r="L20" t="n">
-        <v>23.24502393394037</v>
+        <v>23.86506357287907</v>
       </c>
       <c r="M20" t="n">
-        <v>20.11244339814313</v>
+        <v>15.42478808253083</v>
       </c>
       <c r="N20" t="n">
-        <v>9.81</v>
+        <v>49.42</v>
       </c>
       <c r="O20" t="n">
-        <v>3.91</v>
+        <v>4.4</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>2.82</v>
+        <v>4.33</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R20" t="n">
-        <v>2618348.58</v>
+        <v>808359.03</v>
       </c>
       <c r="S20" t="n">
-        <v>26645</v>
+        <v>283649</v>
       </c>
       <c r="T20" t="n">
-        <v>50.05123927590353</v>
+        <v>47.16364601771759</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.99027109750765</v>
+        <v>17.87001124549607</v>
       </c>
       <c r="C21" t="n">
-        <v>3.168808778744431</v>
+        <v>8.788485820888438</v>
       </c>
       <c r="D21" t="n">
-        <v>28.8880112339828</v>
+        <v>33.97028990249329</v>
       </c>
       <c r="E21" t="n">
-        <v>62.41380175029464</v>
+        <v>86.87476823070044</v>
       </c>
       <c r="F21" t="n">
-        <v>6.445624336310825</v>
+        <v>1.417345603929039</v>
       </c>
       <c r="G21" t="n">
-        <v>1.300946133138182</v>
+        <v>4.60298643565485</v>
       </c>
       <c r="H21" t="n">
-        <v>0.06747535915921023</v>
+        <v>0.1827659481160472</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>12547</v>
+        <v>24176</v>
       </c>
       <c r="J21" t="n">
-        <v>21.39660074377121</v>
+        <v>4.965471644662767</v>
       </c>
       <c r="K21" t="n">
-        <v>17.25086850260209</v>
+        <v>5.510261937513361</v>
       </c>
       <c r="L21" t="n">
-        <v>51.94877118224903</v>
+        <v>9.189188268434778</v>
       </c>
       <c r="M21" t="n">
-        <v>55.18455739153598</v>
+        <v>9.096607850144967</v>
       </c>
       <c r="N21" t="n">
-        <v>25.76</v>
+        <v>64.39</v>
       </c>
       <c r="O21" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>3.43</v>
+        <v>3.09</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="R21" t="n">
-        <v>1319221.86</v>
+        <v>372584.24</v>
       </c>
       <c r="S21" t="n">
-        <v>159516</v>
+        <v>45843</v>
       </c>
       <c r="T21" t="n">
-        <v>49.77499869166721</v>
+        <v>46.98257382219731</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14.33974005030719</v>
+        <v>16.71605179468811</v>
       </c>
       <c r="C22" t="n">
-        <v>2.148461558534627</v>
+        <v>1.368070466573592</v>
       </c>
       <c r="D22" t="n">
-        <v>23.07288232992184</v>
+        <v>13.93516047014541</v>
       </c>
       <c r="E22" t="n">
-        <v>61.41252040373843</v>
+        <v>41.75390656810141</v>
       </c>
       <c r="F22" t="n">
-        <v>6.808786667718385</v>
+        <v>14.86741992554242</v>
       </c>
       <c r="G22" t="n">
-        <v>1.400768822479211</v>
+        <v>1.610661174334986</v>
       </c>
       <c r="H22" t="n">
-        <v>0.07038097917866981</v>
+        <v>0.0719985042520674</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>35669</v>
+        <v>13296</v>
       </c>
       <c r="J22" t="n">
-        <v>30.18695614094877</v>
+        <v>16.30293930023252</v>
       </c>
       <c r="K22" t="n">
-        <v>21.95098428169122</v>
+        <v>18.17561078322378</v>
       </c>
       <c r="L22" t="n">
-        <v>23.86506357287907</v>
+        <v>85.7752850068174</v>
       </c>
       <c r="M22" t="n">
-        <v>15.42478808253083</v>
+        <v>53.4206382524911</v>
       </c>
       <c r="N22" t="n">
-        <v>49.42</v>
+        <v>36.74</v>
       </c>
       <c r="O22" t="n">
-        <v>4.4</v>
+        <v>12.61</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>4.33</v>
+        <v>3.81</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>808359.03</v>
+        <v>496415.88</v>
       </c>
       <c r="S22" t="n">
-        <v>283649</v>
+        <v>110519</v>
       </c>
       <c r="T22" t="n">
-        <v>48.88959773887582</v>
+        <v>46.09979877526326</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9.958650553699458</v>
+        <v>13.0380853616381</v>
       </c>
       <c r="C23" t="n">
-        <v>8.361624052274221</v>
+        <v>1.390231951051347</v>
       </c>
       <c r="D23" t="n">
-        <v>8.789365557299389</v>
+        <v>24.0645524488647</v>
       </c>
       <c r="E23" t="n">
-        <v>18.07459281612296</v>
+        <v>99.50459748545694</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5784524141094746</v>
+        <v>8.378352548852153</v>
       </c>
       <c r="G23" t="n">
-        <v>7.728912535686478</v>
+        <v>1.31948659270683</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5122600635424216</v>
+        <v>0.05492885738906</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45207</v>
+        <v>7906</v>
       </c>
       <c r="J23" t="n">
-        <v>24.46173600944801</v>
+        <v>19.10193873049559</v>
       </c>
       <c r="K23" t="n">
-        <v>9.606097094616972</v>
+        <v>19.06740855567788</v>
       </c>
       <c r="L23" t="n">
-        <v>14.68063260349559</v>
+        <v>23.24502393394037</v>
       </c>
       <c r="M23" t="n">
-        <v>11.95266483252204</v>
+        <v>20.11244339814313</v>
       </c>
       <c r="N23" t="n">
-        <v>58.34</v>
+        <v>9.81</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>3.91</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>4.21</v>
+        <v>2.82</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="R23" t="n">
-        <v>432472.71</v>
+        <v>2618348.58</v>
       </c>
       <c r="S23" t="n">
-        <v>899041</v>
+        <v>26645</v>
       </c>
       <c r="T23" t="n">
-        <v>47.06763083531943</v>
+        <v>43.7068962147807</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20.63992042440318</v>
+        <v>8.370767521615225</v>
       </c>
       <c r="C24" t="n">
-        <v>26.2827398165744</v>
+        <v>13.23404445637104</v>
       </c>
       <c r="D24" t="n">
-        <v>14.88611227356968</v>
+        <v>8.445007553238145</v>
       </c>
       <c r="E24" t="n">
-        <v>12.52466072816405</v>
+        <v>22.01647093221578</v>
       </c>
       <c r="F24" t="n">
-        <v>0.003232758620689655</v>
+        <v>0.07998840747717723</v>
       </c>
       <c r="G24" t="n">
-        <v>71.78431372549019</v>
+        <v>19.82558139534884</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9638144626908672</v>
+        <v>0.7348612354521038</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1536</v>
+        <v>1929</v>
       </c>
       <c r="J24" t="n">
-        <v>19.843289373664</v>
+        <v>14.80997180241832</v>
       </c>
       <c r="K24" t="n">
-        <v>6.717165240230294</v>
+        <v>10.32561591555659</v>
       </c>
       <c r="L24" t="n">
-        <v>9.275930793686072</v>
+        <v>11.2926552609119</v>
       </c>
       <c r="M24" t="n">
-        <v>9.261870727688626</v>
+        <v>10.67987982673917</v>
       </c>
       <c r="N24" t="n">
-        <v>58.43</v>
+        <v>25.87</v>
       </c>
       <c r="O24" t="n">
-        <v>6.47</v>
+        <v>1.21</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>4.23</v>
+        <v>3.2</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="R24" t="n">
-        <v>2599556.05</v>
+        <v>3154358.33</v>
       </c>
       <c r="S24" t="n">
-        <v>16727</v>
+        <v>20521</v>
       </c>
       <c r="T24" t="n">
-        <v>45.21496781773225</v>
+        <v>42.94800389990229</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17.06727541291795</v>
+        <v>20.63992042440318</v>
       </c>
       <c r="C25" t="n">
-        <v>22.0258064516129</v>
+        <v>26.2827398165744</v>
       </c>
       <c r="D25" t="n">
-        <v>6.837009144701453</v>
+        <v>14.88611227356968</v>
       </c>
       <c r="E25" t="n">
-        <v>10.11834319526627</v>
+        <v>12.52466072816405</v>
       </c>
       <c r="F25" t="n">
-        <v>0.040687525177924</v>
+        <v>0.003232758620689655</v>
       </c>
       <c r="G25" t="n">
-        <v>25.35714285714286</v>
+        <v>71.78431372549019</v>
       </c>
       <c r="H25" t="n">
-        <v>1.495214348910158</v>
+        <v>0.9638144626908672</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>335</v>
+        <v>1536</v>
       </c>
       <c r="J25" t="n">
-        <v>21.14089015706202</v>
+        <v>19.843289373664</v>
       </c>
       <c r="K25" t="n">
-        <v>13.03790793906312</v>
+        <v>6.717165240230294</v>
       </c>
       <c r="L25" t="n">
-        <v>10.03323122942004</v>
+        <v>9.275930793686072</v>
       </c>
       <c r="M25" t="n">
-        <v>8.997698704834534</v>
+        <v>9.261870727688626</v>
       </c>
       <c r="N25" t="n">
-        <v>45.41</v>
+        <v>58.43</v>
       </c>
       <c r="O25" t="n">
-        <v>14.08</v>
+        <v>6.47</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>2.6</v>
+        <v>4.23</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>44</v>
       </c>
       <c r="R25" t="n">
-        <v>2521508.87</v>
+        <v>2599556.05</v>
       </c>
       <c r="S25" t="n">
-        <v>18590</v>
+        <v>16727</v>
       </c>
       <c r="T25" t="n">
-        <v>42.0191990677735</v>
+        <v>38.77359464614575</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16.71605179468811</v>
+        <v>13.48039215686275</v>
       </c>
       <c r="C26" t="n">
-        <v>1.368070466573592</v>
+        <v>11.1011492379167</v>
       </c>
       <c r="D26" t="n">
-        <v>13.93516047014541</v>
+        <v>4.905818773282963</v>
       </c>
       <c r="E26" t="n">
-        <v>41.75390656810141</v>
+        <v>12.56099480560365</v>
       </c>
       <c r="F26" t="n">
-        <v>14.86741992554242</v>
+        <v>0.7688869665513264</v>
       </c>
       <c r="G26" t="n">
-        <v>1.610661174334986</v>
+        <v>5.565701559020044</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0719985042520674</v>
+        <v>1.138394457054115</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13296</v>
+        <v>383</v>
       </c>
       <c r="J26" t="n">
-        <v>16.30293930023252</v>
+        <v>21.75273635187671</v>
       </c>
       <c r="K26" t="n">
-        <v>18.17561078322378</v>
+        <v>14.66004260219314</v>
       </c>
       <c r="L26" t="n">
-        <v>85.7752850068174</v>
+        <v>36.13077689773863</v>
       </c>
       <c r="M26" t="n">
-        <v>53.4206382524911</v>
+        <v>29.95061094416296</v>
       </c>
       <c r="N26" t="n">
-        <v>36.74</v>
+        <v>47.72</v>
       </c>
       <c r="O26" t="n">
-        <v>12.61</v>
+        <v>7.68</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>3.81</v>
+        <v>3.22</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="R26" t="n">
-        <v>496415.88</v>
+        <v>1905622.43</v>
       </c>
       <c r="S26" t="n">
-        <v>110519</v>
+        <v>19059</v>
       </c>
       <c r="T26" t="n">
-        <v>41.24609119135111</v>
+        <v>38.44901577120161</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18.35596999797284</v>
+        <v>9.958650553699458</v>
       </c>
       <c r="C27" t="n">
-        <v>21.00436292404951</v>
+        <v>8.361624052274221</v>
       </c>
       <c r="D27" t="n">
-        <v>14.60012899064818</v>
+        <v>8.789365557299389</v>
       </c>
       <c r="E27" t="n">
-        <v>19.34859722670106</v>
+        <v>18.07459281612296</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1383539428339753</v>
+        <v>0.5784524141094746</v>
       </c>
       <c r="G27" t="n">
-        <v>23.24193548387097</v>
+        <v>7.728912535686478</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8205874569992061</v>
+        <v>0.5122600635424216</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1042</v>
+        <v>45207</v>
       </c>
       <c r="J27" t="n">
-        <v>9.061384362071356</v>
+        <v>24.46173600944801</v>
       </c>
       <c r="K27" t="n">
-        <v>7.814065037783324</v>
+        <v>9.606097094616972</v>
       </c>
       <c r="L27" t="n">
-        <v>4.604418961155621</v>
+        <v>14.68063260349559</v>
       </c>
       <c r="M27" t="n">
-        <v>4.563955259127317</v>
+        <v>11.95266483252204</v>
       </c>
       <c r="N27" t="n">
-        <v>50.95</v>
+        <v>58.34</v>
       </c>
       <c r="O27" t="n">
-        <v>13.59</v>
+        <v>3.25</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>3.42</v>
+        <v>4.21</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>56521.84</v>
+        <v>432472.71</v>
       </c>
       <c r="S27" t="n">
-        <v>12404</v>
+        <v>899041</v>
       </c>
       <c r="T27" t="n">
-        <v>40.42963673128816</v>
+        <v>36.88286583267566</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.370767521615225</v>
+        <v>6.908270142781061</v>
       </c>
       <c r="C28" t="n">
-        <v>13.23404445637104</v>
+        <v>4.859369705184683</v>
       </c>
       <c r="D28" t="n">
-        <v>8.445007553238145</v>
+        <v>42.38369379181578</v>
       </c>
       <c r="E28" t="n">
-        <v>22.01647093221578</v>
+        <v>33.04807841916913</v>
       </c>
       <c r="F28" t="n">
-        <v>0.07998840747717723</v>
+        <v>0.1225938982019223</v>
       </c>
       <c r="G28" t="n">
-        <v>19.82558139534884</v>
+        <v>7.457865168539326</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7348612354521038</v>
+        <v>0.1088049569147946</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1929</v>
+        <v>1010</v>
       </c>
       <c r="J28" t="n">
-        <v>14.80997180241832</v>
+        <v>5.883921200220743</v>
       </c>
       <c r="K28" t="n">
-        <v>10.32561591555659</v>
+        <v>-5.136730668466605</v>
       </c>
       <c r="L28" t="n">
-        <v>11.2926552609119</v>
+        <v>15.69706651383664</v>
       </c>
       <c r="M28" t="n">
-        <v>10.67987982673917</v>
+        <v>12.88813207301975</v>
       </c>
       <c r="N28" t="n">
-        <v>25.87</v>
+        <v>46.26</v>
       </c>
       <c r="O28" t="n">
-        <v>1.21</v>
+        <v>14.32</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="R28" t="n">
-        <v>3154358.33</v>
+        <v>1381712.03</v>
       </c>
       <c r="S28" t="n">
-        <v>20521</v>
+        <v>6427</v>
       </c>
       <c r="T28" t="n">
-        <v>39.93760869022043</v>
+        <v>36.59576409007721</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6.908270142781061</v>
+        <v>18.35596999797284</v>
       </c>
       <c r="C29" t="n">
-        <v>4.859369705184683</v>
+        <v>21.00436292404951</v>
       </c>
       <c r="D29" t="n">
-        <v>42.38369379181578</v>
+        <v>14.60012899064818</v>
       </c>
       <c r="E29" t="n">
-        <v>33.04807841916913</v>
+        <v>19.34859722670106</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1225938982019223</v>
+        <v>0.1383539428339753</v>
       </c>
       <c r="G29" t="n">
-        <v>7.457865168539326</v>
+        <v>23.24193548387097</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1088049569147946</v>
+        <v>0.8205874569992061</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1010</v>
+        <v>1042</v>
       </c>
       <c r="J29" t="n">
-        <v>5.883921200220743</v>
+        <v>9.061384362071356</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.136730668466605</v>
+        <v>7.814065037783324</v>
       </c>
       <c r="L29" t="n">
-        <v>15.69706651383664</v>
+        <v>4.604418961155621</v>
       </c>
       <c r="M29" t="n">
-        <v>12.88813207301975</v>
+        <v>4.563955259127317</v>
       </c>
       <c r="N29" t="n">
-        <v>46.26</v>
+        <v>50.95</v>
       </c>
       <c r="O29" t="n">
-        <v>14.32</v>
+        <v>13.59</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>2.58</v>
+        <v>3.42</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="R29" t="n">
-        <v>1381712.03</v>
+        <v>56521.84</v>
       </c>
       <c r="S29" t="n">
-        <v>6427</v>
+        <v>12404</v>
       </c>
       <c r="T29" t="n">
-        <v>36.59576409007721</v>
+        <v>35.0152353511284</v>
       </c>
     </row>
     <row r="30">
@@ -5771,7 +5771,7 @@
         <v>98692</v>
       </c>
       <c r="T30" t="n">
-        <v>33.91957992781828</v>
+        <v>23.02128544550119</v>
       </c>
     </row>
   </sheetData>
@@ -5915,129 +5915,129 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>32.46823465801568</v>
+        <v>20.78030212917806</v>
       </c>
       <c r="C2" t="n">
-        <v>42.78159703860391</v>
+        <v>27.06792581636136</v>
       </c>
       <c r="D2" t="n">
-        <v>20.53342451701145</v>
+        <v>14.10805136073649</v>
       </c>
       <c r="E2" t="n">
-        <v>24.84185330825782</v>
+        <v>21.86869094726642</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.02243849689105163</v>
+        <v>0.04543832520518615</v>
       </c>
       <c r="G2" t="n">
-        <v>141.75</v>
+        <v>54.33333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1263238975544</v>
+        <v>1.025422325273269</v>
       </c>
       <c r="I2" t="n">
-        <v>797</v>
+        <v>955</v>
       </c>
       <c r="J2" t="n">
-        <v>10.71372178938566</v>
+        <v>19.2998469335665</v>
       </c>
       <c r="K2" t="n">
-        <v>9.716101277290168</v>
+        <v>11.83637017589811</v>
       </c>
       <c r="L2" t="n">
-        <v>21.69314043381163</v>
+        <v>13.48774998597666</v>
       </c>
       <c r="M2" t="n">
-        <v>21.65851677781967</v>
+        <v>13.56415724960776</v>
       </c>
       <c r="N2" t="n">
-        <v>75.58</v>
+        <v>36.12</v>
       </c>
       <c r="O2" t="n">
-        <v>4.48</v>
+        <v>12.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="R2" t="n">
-        <v>1536236.24</v>
+        <v>162274.18</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>5849</v>
+        <v>12383</v>
       </c>
       <c r="T2" t="n">
-        <v>74.48393689046455</v>
+        <v>78.17546048834996</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>27.85107439569436</v>
+        <v>32.46823465801568</v>
       </c>
       <c r="C3" t="n">
-        <v>36.27857238337121</v>
+        <v>42.78159703860391</v>
       </c>
       <c r="D3" t="n">
-        <v>29.28202523071713</v>
+        <v>20.53342451701145</v>
       </c>
       <c r="E3" t="n">
-        <v>37.0177518132814</v>
+        <v>24.84185330825782</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.004066731984914169</v>
+        <v>0.02243849689105163</v>
       </c>
       <c r="G3" t="n">
-        <v>362.9625</v>
+        <v>141.75</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7723477995509732</v>
+        <v>1.1263238975544</v>
       </c>
       <c r="I3" t="n">
-        <v>18742</v>
+        <v>797</v>
       </c>
       <c r="J3" t="n">
-        <v>12.89030700491063</v>
+        <v>10.71372178938566</v>
       </c>
       <c r="K3" t="n">
-        <v>7.950896846254429</v>
+        <v>9.716101277290168</v>
       </c>
       <c r="L3" t="n">
-        <v>10.08340755831796</v>
+        <v>21.69314043381163</v>
       </c>
       <c r="M3" t="n">
-        <v>9.856054330611785</v>
+        <v>21.65851677781967</v>
       </c>
       <c r="N3" t="n">
-        <v>47.85</v>
+        <v>75.58</v>
       </c>
       <c r="O3" t="n">
-        <v>3.24</v>
+        <v>4.48</v>
       </c>
       <c r="P3" t="n">
-        <v>4.26</v>
+        <v>0.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="R3" t="n">
-        <v>332245.58</v>
+        <v>1536236.24</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>70866</v>
+        <v>5849</v>
       </c>
       <c r="T3" t="n">
-        <v>70.61348571152801</v>
+        <v>74.71367760204753</v>
       </c>
     </row>
     <row r="4">
@@ -6089,199 +6089,199 @@
         <v>22240</v>
       </c>
       <c r="T4" t="n">
-        <v>60.95287318676066</v>
+        <v>68.12570273895892</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>15.55455702838313</v>
+        <v>27.85107439569436</v>
       </c>
       <c r="C5" t="n">
-        <v>20.91325875664772</v>
+        <v>36.27857238337121</v>
       </c>
       <c r="D5" t="n">
-        <v>16.11701714906495</v>
+        <v>29.28202523071713</v>
       </c>
       <c r="E5" t="n">
-        <v>75.59168153953597</v>
+        <v>37.0177518132814</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.02093162585186849</v>
+        <v>0.004066731984914169</v>
       </c>
       <c r="G5" t="n">
-        <v>35.33876811594203</v>
+        <v>362.9625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7922417237881536</v>
+        <v>0.7723477995509732</v>
       </c>
       <c r="I5" t="n">
-        <v>1152</v>
+        <v>18742</v>
       </c>
       <c r="J5" t="n">
-        <v>10.38975593522793</v>
+        <v>12.89030700491063</v>
       </c>
       <c r="K5" t="n">
-        <v>9.513860126378049</v>
+        <v>7.950896846254429</v>
       </c>
       <c r="L5" t="n">
-        <v>22.72683484800089</v>
+        <v>10.08340755831796</v>
       </c>
       <c r="M5" t="n">
-        <v>21.83254460856599</v>
+        <v>9.856054330611785</v>
       </c>
       <c r="N5" t="n">
-        <v>59.75</v>
+        <v>47.85</v>
       </c>
       <c r="O5" t="n">
-        <v>5.93</v>
+        <v>3.24</v>
       </c>
       <c r="P5" t="n">
-        <v>0.12</v>
+        <v>4.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="R5" t="n">
-        <v>439803.15</v>
+        <v>332245.58</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>25774</v>
+        <v>70866</v>
       </c>
       <c r="T5" t="n">
-        <v>60.13315864117262</v>
+        <v>59.91275571721161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>20.78030212917806</v>
+        <v>15.55455702838313</v>
       </c>
       <c r="C6" t="n">
-        <v>27.06792581636136</v>
+        <v>20.91325875664772</v>
       </c>
       <c r="D6" t="n">
-        <v>14.10805136073649</v>
+        <v>16.11701714906495</v>
       </c>
       <c r="E6" t="n">
-        <v>21.86869094726642</v>
+        <v>75.59168153953597</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.04543832520518615</v>
+        <v>0.02093162585186849</v>
       </c>
       <c r="G6" t="n">
-        <v>54.33333333333334</v>
+        <v>35.33876811594203</v>
       </c>
       <c r="H6" t="n">
-        <v>1.025422325273269</v>
+        <v>0.7922417237881536</v>
       </c>
       <c r="I6" t="n">
-        <v>955</v>
+        <v>1152</v>
       </c>
       <c r="J6" t="n">
-        <v>19.2998469335665</v>
+        <v>10.38975593522793</v>
       </c>
       <c r="K6" t="n">
-        <v>11.83637017589811</v>
+        <v>9.513860126378049</v>
       </c>
       <c r="L6" t="n">
-        <v>13.48774998597666</v>
+        <v>22.72683484800089</v>
       </c>
       <c r="M6" t="n">
-        <v>13.56415724960776</v>
+        <v>21.83254460856599</v>
       </c>
       <c r="N6" t="n">
-        <v>36.12</v>
+        <v>59.75</v>
       </c>
       <c r="O6" t="n">
-        <v>12.3</v>
+        <v>5.93</v>
       </c>
       <c r="P6" t="n">
-        <v>1.01</v>
+        <v>0.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="R6" t="n">
-        <v>162274.18</v>
+        <v>439803.15</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>12383</v>
+        <v>25774</v>
       </c>
       <c r="T6" t="n">
-        <v>59.61651016619649</v>
+        <v>57.69180855467479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>13.56294790886726</v>
+        <v>20.07497364207896</v>
       </c>
       <c r="C7" t="n">
-        <v>17.9419388284085</v>
+        <v>26.42404462828735</v>
       </c>
       <c r="D7" t="n">
-        <v>4.993207190533383</v>
+        <v>16.61173581491534</v>
       </c>
       <c r="E7" t="n">
-        <v>8.084427730414067</v>
+        <v>76.31672482874498</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.03166114022890149</v>
+        <v>0.02897418876176344</v>
       </c>
       <c r="G7" t="n">
-        <v>73.29310344827586</v>
+        <v>57.8470012239902</v>
       </c>
       <c r="H7" t="n">
-        <v>2.398875873795579</v>
+        <v>0.7885945801322478</v>
       </c>
       <c r="I7" t="n">
-        <v>278</v>
+        <v>10145</v>
       </c>
       <c r="J7" t="n">
-        <v>28.1325519519273</v>
+        <v>9.589435897156351</v>
       </c>
       <c r="K7" t="n">
-        <v>20.48312440202782</v>
+        <v>9.504485244074123</v>
       </c>
       <c r="L7" t="n">
-        <v>22.96698996520703</v>
+        <v>11.15295043680342</v>
       </c>
       <c r="M7" t="n">
-        <v>22.74033782145131</v>
+        <v>9.460878422315755</v>
       </c>
       <c r="N7" t="n">
-        <v>72.53</v>
+        <v>34.51</v>
       </c>
       <c r="O7" t="n">
-        <v>11.71</v>
+        <v>11.88</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>4.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R7" t="n">
-        <v>3053088.97</v>
+        <v>548890.59</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>50789</v>
+        <v>61896</v>
       </c>
       <c r="T7" t="n">
-        <v>59.54233552850971</v>
+        <v>54.24287712632469</v>
       </c>
     </row>
     <row r="8">
@@ -6345,327 +6345,327 @@
         <v>16536</v>
       </c>
       <c r="T8" t="n">
-        <v>58.08734076782807</v>
+        <v>52.44066966339204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>20.07497364207896</v>
+        <v>13.56294790886726</v>
       </c>
       <c r="C9" t="n">
-        <v>26.42404462828735</v>
+        <v>17.9419388284085</v>
       </c>
       <c r="D9" t="n">
-        <v>16.61173581491534</v>
+        <v>4.993207190533383</v>
       </c>
       <c r="E9" t="n">
-        <v>76.31672482874498</v>
+        <v>8.084427730414067</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.02897418876176344</v>
+        <v>0.03166114022890149</v>
       </c>
       <c r="G9" t="n">
-        <v>57.8470012239902</v>
+        <v>73.29310344827586</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7885945801322478</v>
+        <v>2.398875873795579</v>
       </c>
       <c r="I9" t="n">
-        <v>10145</v>
+        <v>278</v>
       </c>
       <c r="J9" t="n">
-        <v>9.589435897156351</v>
+        <v>28.1325519519273</v>
       </c>
       <c r="K9" t="n">
-        <v>9.504485244074123</v>
+        <v>20.48312440202782</v>
       </c>
       <c r="L9" t="n">
-        <v>11.15295043680342</v>
+        <v>22.96698996520703</v>
       </c>
       <c r="M9" t="n">
-        <v>9.460878422315755</v>
+        <v>22.74033782145131</v>
       </c>
       <c r="N9" t="n">
-        <v>34.51</v>
+        <v>72.53</v>
       </c>
       <c r="O9" t="n">
-        <v>11.88</v>
+        <v>11.71</v>
       </c>
       <c r="P9" t="n">
-        <v>4.32</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>548890.59</v>
+        <v>3053088.97</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>61896</v>
+        <v>50789</v>
       </c>
       <c r="T9" t="n">
-        <v>55.16877298430498</v>
+        <v>49.2334625729186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>15.75038535195478</v>
+        <v>17.06727541291795</v>
       </c>
       <c r="C10" t="n">
-        <v>20.31834878432744</v>
+        <v>22.0258064516129</v>
       </c>
       <c r="D10" t="n">
-        <v>9.50809964894472</v>
+        <v>6.837009144701453</v>
       </c>
       <c r="E10" t="n">
-        <v>13.13003143989059</v>
+        <v>10.11834319526627</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.001389602503619973</v>
+        <v>0.040687525177924</v>
       </c>
       <c r="G10" t="n">
-        <v>117.9072164948454</v>
+        <v>25.35714285714286</v>
       </c>
       <c r="H10" t="n">
-        <v>1.230295566502463</v>
+        <v>1.495214348910158</v>
       </c>
       <c r="I10" t="n">
-        <v>4936</v>
+        <v>335</v>
       </c>
       <c r="J10" t="n">
-        <v>26.32364432616601</v>
+        <v>21.14089015706202</v>
       </c>
       <c r="K10" t="n">
-        <v>10.51021511264258</v>
+        <v>13.03790793906312</v>
       </c>
       <c r="L10" t="n">
-        <v>12.00718203930038</v>
+        <v>10.03323122942004</v>
       </c>
       <c r="M10" t="n">
-        <v>11.1392224868865</v>
+        <v>8.997698704834534</v>
       </c>
       <c r="N10" t="n">
-        <v>20.78</v>
+        <v>45.41</v>
       </c>
       <c r="O10" t="n">
-        <v>8.26</v>
+        <v>14.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="R10" t="n">
-        <v>1503863.63</v>
+        <v>2521508.87</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>141858</v>
+        <v>18590</v>
       </c>
       <c r="T10" t="n">
-        <v>49.23865164943381</v>
+        <v>48.75439737462181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>21.14243742584327</v>
+        <v>15.75038535195478</v>
       </c>
       <c r="C11" t="n">
-        <v>27.80661021578804</v>
+        <v>20.31834878432744</v>
       </c>
       <c r="D11" t="n">
-        <v>9.902352536452407</v>
+        <v>9.50809964894472</v>
       </c>
       <c r="E11" t="n">
-        <v>86.14676228532112</v>
+        <v>13.13003143989059</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.03423922255494661</v>
+        <v>0.001389602503619973</v>
       </c>
       <c r="G11" t="n">
-        <v>47.26850507982584</v>
+        <v>117.9072164948454</v>
       </c>
       <c r="H11" t="n">
-        <v>1.444920276832486</v>
+        <v>1.230295566502463</v>
       </c>
       <c r="I11" t="n">
-        <v>3095</v>
+        <v>4936</v>
       </c>
       <c r="J11" t="n">
-        <v>6.870906150291889</v>
+        <v>26.32364432616601</v>
       </c>
       <c r="K11" t="n">
-        <v>2.153067797054464</v>
+        <v>10.51021511264258</v>
       </c>
       <c r="L11" t="n">
-        <v>1.544181887188389</v>
+        <v>12.00718203930038</v>
       </c>
       <c r="M11" t="n">
-        <v>1.686343719746475</v>
+        <v>11.1392224868865</v>
       </c>
       <c r="N11" t="n">
-        <v>53.86</v>
+        <v>20.78</v>
       </c>
       <c r="O11" t="n">
-        <v>12.6</v>
+        <v>8.26</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="R11" t="n">
-        <v>1593400.88</v>
+        <v>1503863.63</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>37789</v>
+        <v>141858</v>
       </c>
       <c r="T11" t="n">
-        <v>46.37929264444782</v>
+        <v>42.2423881483173</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>20.63992042440318</v>
+        <v>21.14243742584327</v>
       </c>
       <c r="C12" t="n">
-        <v>26.2827398165744</v>
+        <v>27.80661021578804</v>
       </c>
       <c r="D12" t="n">
-        <v>14.88611227356968</v>
+        <v>9.902352536452407</v>
       </c>
       <c r="E12" t="n">
-        <v>12.52466072816405</v>
+        <v>86.14676228532112</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.003232758620689655</v>
+        <v>0.03423922255494661</v>
       </c>
       <c r="G12" t="n">
-        <v>71.78431372549019</v>
+        <v>47.26850507982584</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9638144626908672</v>
+        <v>1.444920276832486</v>
       </c>
       <c r="I12" t="n">
-        <v>1536</v>
+        <v>3095</v>
       </c>
       <c r="J12" t="n">
-        <v>19.843289373664</v>
+        <v>6.870906150291889</v>
       </c>
       <c r="K12" t="n">
-        <v>6.717165240230294</v>
+        <v>2.153067797054464</v>
       </c>
       <c r="L12" t="n">
-        <v>9.275930793686072</v>
+        <v>1.544181887188389</v>
       </c>
       <c r="M12" t="n">
-        <v>9.261870727688626</v>
+        <v>1.686343719746475</v>
       </c>
       <c r="N12" t="n">
-        <v>58.43</v>
+        <v>53.86</v>
       </c>
       <c r="O12" t="n">
-        <v>6.47</v>
+        <v>12.6</v>
       </c>
       <c r="P12" t="n">
-        <v>4.23</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="R12" t="n">
-        <v>2599556.05</v>
+        <v>1593400.88</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>16727</v>
+        <v>37789</v>
       </c>
       <c r="T12" t="n">
-        <v>45.21496781773225</v>
+        <v>40.95694729611733</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>17.06727541291795</v>
+        <v>20.63992042440318</v>
       </c>
       <c r="C13" t="n">
-        <v>22.0258064516129</v>
+        <v>26.2827398165744</v>
       </c>
       <c r="D13" t="n">
-        <v>6.837009144701453</v>
+        <v>14.88611227356968</v>
       </c>
       <c r="E13" t="n">
-        <v>10.11834319526627</v>
+        <v>12.52466072816405</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.040687525177924</v>
+        <v>0.003232758620689655</v>
       </c>
       <c r="G13" t="n">
-        <v>25.35714285714286</v>
+        <v>71.78431372549019</v>
       </c>
       <c r="H13" t="n">
-        <v>1.495214348910158</v>
+        <v>0.9638144626908672</v>
       </c>
       <c r="I13" t="n">
-        <v>335</v>
+        <v>1536</v>
       </c>
       <c r="J13" t="n">
-        <v>21.14089015706202</v>
+        <v>19.843289373664</v>
       </c>
       <c r="K13" t="n">
-        <v>13.03790793906312</v>
+        <v>6.717165240230294</v>
       </c>
       <c r="L13" t="n">
-        <v>10.03323122942004</v>
+        <v>9.275930793686072</v>
       </c>
       <c r="M13" t="n">
-        <v>8.997698704834534</v>
+        <v>9.261870727688626</v>
       </c>
       <c r="N13" t="n">
-        <v>45.41</v>
+        <v>58.43</v>
       </c>
       <c r="O13" t="n">
-        <v>14.08</v>
+        <v>6.47</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>4.23</v>
       </c>
       <c r="Q13" t="n">
         <v>44</v>
       </c>
       <c r="R13" t="n">
-        <v>2521508.87</v>
+        <v>2599556.05</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>18590</v>
+        <v>16727</v>
       </c>
       <c r="T13" t="n">
-        <v>42.0191990677735</v>
+        <v>38.77359464614575</v>
       </c>
     </row>
   </sheetData>
@@ -6867,638 +6867,641 @@
         <v>4270</v>
       </c>
       <c r="T2" t="n">
-        <v>85.75992272430739</v>
+        <v>79.94074387215829</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.30776794493609</v>
+        <v>48.27674122146251</v>
       </c>
       <c r="C3" t="n">
-        <v>33.00120254251846</v>
+        <v>26.73833927032831</v>
       </c>
       <c r="D3" t="n">
-        <v>11.93535353535353</v>
+        <v>41.36759945184802</v>
       </c>
       <c r="E3" t="n">
-        <v>15.92727272727273</v>
+        <v>36.20186292228556</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4309242871189774</v>
+        <v>0.8023177656738903</v>
       </c>
       <c r="G3" t="n">
-        <v>8.043478260869565</v>
+        <v>8.297225501770956</v>
       </c>
       <c r="H3" t="n">
-        <v>1.727869310248534</v>
+        <v>0.5472399439185297</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>841</v>
+        <v>17651</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>68.36335197744833</v>
+        <v>24.29479715622616</v>
       </c>
       <c r="K3" t="n">
-        <v>36.30691600183056</v>
-      </c>
-      <c r="L3" t="n">
-        <v>73.11367578503176</v>
-      </c>
-      <c r="M3" t="n">
-        <v>69.52182030724354</v>
+        <v>16.08609641044097</v>
       </c>
       <c r="N3" t="n">
-        <v>8.65</v>
+        <v>44.57</v>
       </c>
       <c r="O3" t="n">
-        <v>11.82</v>
+        <v>9.91</v>
       </c>
       <c r="P3" t="n">
-        <v>3.46</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>571322.04</v>
+        <v>1372183.55</v>
       </c>
       <c r="S3" t="n">
-        <v>12375</v>
+        <v>50351</v>
       </c>
       <c r="T3" t="n">
-        <v>81.23496652577464</v>
+        <v>79.79697482700455</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.27674122146251</v>
+        <v>20.78030212917806</v>
       </c>
       <c r="C4" t="n">
-        <v>26.73833927032831</v>
+        <v>27.06792581636136</v>
       </c>
       <c r="D4" t="n">
-        <v>41.36759945184802</v>
+        <v>14.10805136073649</v>
       </c>
       <c r="E4" t="n">
-        <v>36.20186292228556</v>
+        <v>21.86869094726642</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8023177656738903</v>
+        <v>0.04543832520518615</v>
       </c>
       <c r="G4" t="n">
-        <v>8.297225501770956</v>
+        <v>54.33333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5472399439185297</v>
+        <v>1.025422325273269</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17651</v>
+        <v>955</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>24.29479715622616</v>
+        <v>19.2998469335665</v>
       </c>
       <c r="K4" t="n">
-        <v>16.08609641044097</v>
+        <v>11.83637017589811</v>
+      </c>
+      <c r="L4" t="n">
+        <v>13.48774998597666</v>
+      </c>
+      <c r="M4" t="n">
+        <v>13.56415724960776</v>
       </c>
       <c r="N4" t="n">
-        <v>44.57</v>
+        <v>36.12</v>
       </c>
       <c r="O4" t="n">
-        <v>9.91</v>
+        <v>12.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="R4" t="n">
-        <v>1372183.55</v>
+        <v>162274.18</v>
       </c>
       <c r="S4" t="n">
-        <v>50351</v>
+        <v>12383</v>
       </c>
       <c r="T4" t="n">
-        <v>78.97373571732739</v>
+        <v>78.17546048834996</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.46823465801568</v>
+        <v>117.7544910179641</v>
       </c>
       <c r="C5" t="n">
-        <v>42.78159703860391</v>
+        <v>143.527815468114</v>
       </c>
       <c r="D5" t="n">
-        <v>20.53342451701145</v>
+        <v>16.12281708616873</v>
       </c>
       <c r="E5" t="n">
-        <v>24.84185330825782</v>
+        <v>23.82963023694351</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02243849689105163</v>
+        <v>0.1032934131736527</v>
       </c>
       <c r="G5" t="n">
-        <v>141.75</v>
+        <v>41.18620689655172</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1263238975544</v>
+        <v>2.318160220469448</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>797</v>
+        <v>2938</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10.71372178938566</v>
+        <v>18.28200866249903</v>
       </c>
       <c r="K5" t="n">
-        <v>9.716101277290168</v>
+        <v>14.54857371180267</v>
       </c>
       <c r="L5" t="n">
-        <v>21.69314043381163</v>
+        <v>14.85231951299384</v>
       </c>
       <c r="M5" t="n">
-        <v>21.65851677781967</v>
+        <v>15.43852585822143</v>
       </c>
       <c r="N5" t="n">
-        <v>75.58</v>
+        <v>54.96</v>
       </c>
       <c r="O5" t="n">
-        <v>4.48</v>
+        <v>14.34</v>
       </c>
       <c r="P5" t="n">
-        <v>0.96</v>
+        <v>3.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="R5" t="n">
-        <v>1536236.24</v>
+        <v>1677775.19</v>
       </c>
       <c r="S5" t="n">
-        <v>5849</v>
+        <v>24394</v>
       </c>
       <c r="T5" t="n">
-        <v>74.48393689046455</v>
+        <v>76.26865270052919</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.85107439569436</v>
+        <v>13.57678765646027</v>
       </c>
       <c r="C6" t="n">
-        <v>36.27857238337121</v>
+        <v>13.79672251887314</v>
       </c>
       <c r="D6" t="n">
-        <v>29.28202523071713</v>
+        <v>432.7262044653349</v>
       </c>
       <c r="E6" t="n">
-        <v>37.0177518132814</v>
+        <v>91.77438307873091</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004066731984914169</v>
+        <v>0.001161354544951794</v>
       </c>
       <c r="G6" t="n">
-        <v>362.9625</v>
+        <v>3764.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7723477995509732</v>
+        <v>0.02611991835607188</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18742</v>
+        <v>1469</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12.89030700491063</v>
+        <v>55.00574158769729</v>
       </c>
       <c r="K6" t="n">
-        <v>7.950896846254429</v>
+        <v>31.61229344896917</v>
       </c>
       <c r="L6" t="n">
-        <v>10.08340755831796</v>
+        <v>19.2975590637313</v>
       </c>
       <c r="M6" t="n">
-        <v>9.856054330611785</v>
+        <v>18.96864732798973</v>
       </c>
       <c r="N6" t="n">
-        <v>47.85</v>
+        <v>37.73</v>
       </c>
       <c r="O6" t="n">
-        <v>3.24</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>4.26</v>
+        <v>3.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="R6" t="n">
-        <v>332245.58</v>
+        <v>2191568.13</v>
       </c>
       <c r="S6" t="n">
-        <v>70866</v>
+        <v>1702</v>
       </c>
       <c r="T6" t="n">
-        <v>70.61348571152801</v>
+        <v>75.54487526078582</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.57678765646027</v>
+        <v>36.30776794493609</v>
       </c>
       <c r="C7" t="n">
-        <v>13.79672251887314</v>
+        <v>33.00120254251846</v>
       </c>
       <c r="D7" t="n">
-        <v>432.7262044653349</v>
+        <v>11.93535353535353</v>
       </c>
       <c r="E7" t="n">
-        <v>91.77438307873091</v>
+        <v>15.92727272727273</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001161354544951794</v>
+        <v>0.4309242871189774</v>
       </c>
       <c r="G7" t="n">
-        <v>3764.5</v>
+        <v>8.043478260869565</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02611991835607188</v>
+        <v>1.727869310248534</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1469</v>
+        <v>841</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>55.00574158769729</v>
+        <v>68.36335197744833</v>
       </c>
       <c r="K7" t="n">
-        <v>31.61229344896917</v>
+        <v>36.30691600183056</v>
       </c>
       <c r="L7" t="n">
-        <v>19.2975590637313</v>
+        <v>73.11367578503176</v>
       </c>
       <c r="M7" t="n">
-        <v>18.96864732798973</v>
+        <v>69.52182030724354</v>
       </c>
       <c r="N7" t="n">
-        <v>37.73</v>
+        <v>8.65</v>
       </c>
       <c r="O7" t="n">
-        <v>9.380000000000001</v>
+        <v>11.82</v>
       </c>
       <c r="P7" t="n">
-        <v>3.37</v>
+        <v>3.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>2191568.13</v>
+        <v>571322.04</v>
       </c>
       <c r="S7" t="n">
-        <v>1702</v>
+        <v>12375</v>
       </c>
       <c r="T7" t="n">
-        <v>67.8491262474583</v>
+        <v>74.759015326533</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>117.7544910179641</v>
+        <v>32.46823465801568</v>
       </c>
       <c r="C8" t="n">
-        <v>143.527815468114</v>
+        <v>42.78159703860391</v>
       </c>
       <c r="D8" t="n">
-        <v>16.12281708616873</v>
+        <v>20.53342451701145</v>
       </c>
       <c r="E8" t="n">
-        <v>23.82963023694351</v>
+        <v>24.84185330825782</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1032934131736527</v>
+        <v>0.02243849689105163</v>
       </c>
       <c r="G8" t="n">
-        <v>41.18620689655172</v>
+        <v>141.75</v>
       </c>
       <c r="H8" t="n">
-        <v>2.318160220469448</v>
+        <v>1.1263238975544</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2938</v>
+        <v>797</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.28200866249903</v>
+        <v>10.71372178938566</v>
       </c>
       <c r="K8" t="n">
-        <v>14.54857371180267</v>
+        <v>9.716101277290168</v>
       </c>
       <c r="L8" t="n">
-        <v>14.85231951299384</v>
+        <v>21.69314043381163</v>
       </c>
       <c r="M8" t="n">
-        <v>15.43852585822143</v>
+        <v>21.65851677781967</v>
       </c>
       <c r="N8" t="n">
-        <v>54.96</v>
+        <v>75.58</v>
       </c>
       <c r="O8" t="n">
-        <v>14.34</v>
+        <v>4.48</v>
       </c>
       <c r="P8" t="n">
-        <v>3.85</v>
+        <v>0.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="R8" t="n">
-        <v>1677775.19</v>
+        <v>1536236.24</v>
       </c>
       <c r="S8" t="n">
-        <v>24394</v>
+        <v>5849</v>
       </c>
       <c r="T8" t="n">
-        <v>66.8729916012617</v>
+        <v>74.71367760204753</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.51133734382231</v>
+        <v>15.3548827162833</v>
       </c>
       <c r="C9" t="n">
-        <v>27.7915137368122</v>
+        <v>9.427079258274</v>
       </c>
       <c r="D9" t="n">
-        <v>5.994201967046283</v>
+        <v>30.33956048070083</v>
       </c>
       <c r="E9" t="n">
-        <v>9.837909494446341</v>
+        <v>58.36172363445772</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7218747934157467</v>
+        <v>0.9373223691689719</v>
       </c>
       <c r="G9" t="n">
-        <v>11.35550735116896</v>
+        <v>5.949506037321624</v>
       </c>
       <c r="H9" t="n">
-        <v>2.213651947949293</v>
+        <v>0.2283010965905692</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25415</v>
+        <v>8250</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.86362936813233</v>
+        <v>28.63193631184944</v>
       </c>
       <c r="K9" t="n">
-        <v>8.483226324685255</v>
+        <v>19.57867595245697</v>
       </c>
       <c r="L9" t="n">
-        <v>25.79069872974655</v>
+        <v>14.90956518204163</v>
       </c>
       <c r="M9" t="n">
-        <v>28.06304880261565</v>
+        <v>14.86983549970351</v>
       </c>
       <c r="N9" t="n">
-        <v>68.15000000000001</v>
+        <v>48.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0.72</v>
+        <v>2.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="R9" t="n">
-        <v>468662.13</v>
+        <v>675598.01</v>
       </c>
       <c r="S9" t="n">
-        <v>448083</v>
+        <v>26711</v>
       </c>
       <c r="T9" t="n">
-        <v>65.88207685515766</v>
+        <v>64.60059842643911</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.3548827162833</v>
+        <v>35.51133734382231</v>
       </c>
       <c r="C10" t="n">
-        <v>9.427079258274</v>
+        <v>27.7915137368122</v>
       </c>
       <c r="D10" t="n">
-        <v>30.33956048070083</v>
+        <v>5.994201967046283</v>
       </c>
       <c r="E10" t="n">
-        <v>58.36172363445772</v>
+        <v>9.837909494446341</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9373223691689719</v>
+        <v>0.7218747934157467</v>
       </c>
       <c r="G10" t="n">
-        <v>5.949506037321624</v>
+        <v>11.35550735116896</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2283010965905692</v>
+        <v>2.213651947949293</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>8250</v>
+        <v>25415</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28.63193631184944</v>
+        <v>24.86362936813233</v>
       </c>
       <c r="K10" t="n">
-        <v>19.57867595245697</v>
+        <v>8.483226324685255</v>
       </c>
       <c r="L10" t="n">
-        <v>14.90956518204163</v>
+        <v>25.79069872974655</v>
       </c>
       <c r="M10" t="n">
-        <v>14.86983549970351</v>
+        <v>28.06304880261565</v>
       </c>
       <c r="N10" t="n">
-        <v>48.9</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>2.31</v>
+        <v>0.72</v>
       </c>
       <c r="P10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="R10" t="n">
-        <v>675598.01</v>
+        <v>468662.13</v>
       </c>
       <c r="S10" t="n">
-        <v>26711</v>
+        <v>448083</v>
       </c>
       <c r="T10" t="n">
-        <v>64.69131927823801</v>
+        <v>61.31382445684065</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.78800671841663</v>
+        <v>27.85107439569436</v>
       </c>
       <c r="C11" t="n">
-        <v>37.30292821974604</v>
+        <v>36.27857238337121</v>
       </c>
       <c r="D11" t="n">
-        <v>17.08075746730006</v>
+        <v>29.28202523071713</v>
       </c>
       <c r="E11" t="n">
-        <v>23.70339038198738</v>
+        <v>37.0177518132814</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09486358890553362</v>
+        <v>0.004066731984914169</v>
       </c>
       <c r="G11" t="n">
-        <v>87.52340425531915</v>
+        <v>362.9625</v>
       </c>
       <c r="H11" t="n">
-        <v>1.129760329363329</v>
+        <v>0.7723477995509732</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20117</v>
+        <v>18742</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15.21650079880636</v>
+        <v>12.89030700491063</v>
       </c>
       <c r="K11" t="n">
-        <v>13.19910093055623</v>
+        <v>7.950896846254429</v>
       </c>
       <c r="L11" t="n">
-        <v>11.23941998365794</v>
+        <v>10.08340755831796</v>
       </c>
       <c r="M11" t="n">
-        <v>12.47461131420948</v>
+        <v>9.856054330611785</v>
       </c>
       <c r="N11" t="n">
-        <v>35.99</v>
+        <v>47.85</v>
       </c>
       <c r="O11" t="n">
-        <v>8.970000000000001</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>4.1</v>
+        <v>4.26</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>84</v>
       </c>
       <c r="R11" t="n">
-        <v>1112279.92</v>
+        <v>332245.58</v>
       </c>
       <c r="S11" t="n">
-        <v>153670</v>
+        <v>70866</v>
       </c>
       <c r="T11" t="n">
-        <v>63.88370700777556</v>
+        <v>59.91275571721161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.09416181067115</v>
+        <v>15.7230643179025</v>
       </c>
       <c r="C12" t="n">
-        <v>16.56383979922618</v>
+        <v>20.87418300653595</v>
       </c>
       <c r="D12" t="n">
-        <v>19.81565870053818</v>
+        <v>9.366915605017816</v>
       </c>
       <c r="E12" t="n">
-        <v>26.84289749881436</v>
+        <v>87.42129155073948</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05142381453500244</v>
+        <v>0.002867677181482999</v>
       </c>
       <c r="G12" t="n">
-        <v>58.33193277310924</v>
+        <v>160.0267857142857</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5684929901064378</v>
+        <v>0.3236083907247109</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>11372</v>
+        <v>486</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13.12675558948349</v>
+        <v>18.98796206427069</v>
       </c>
       <c r="K12" t="n">
-        <v>10.78116321985565</v>
+        <v>12.91184100336258</v>
       </c>
       <c r="L12" t="n">
-        <v>24.53682964293125</v>
+        <v>12.83917371819816</v>
       </c>
       <c r="M12" t="n">
-        <v>29.45936165164078</v>
+        <v>11.1392224868865</v>
       </c>
       <c r="N12" t="n">
-        <v>37.9</v>
+        <v>49</v>
       </c>
       <c r="O12" t="n">
-        <v>6.71</v>
+        <v>7.86</v>
       </c>
       <c r="P12" t="n">
-        <v>3.88</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R12" t="n">
-        <v>1339586.09</v>
+        <v>1271789.21</v>
       </c>
       <c r="S12" t="n">
-        <v>48497</v>
+        <v>20487</v>
       </c>
       <c r="T12" t="n">
-        <v>62.40707534502386</v>
+        <v>59.23751631808607</v>
       </c>
     </row>
     <row r="13">
@@ -7562,321 +7565,321 @@
         <v>25774</v>
       </c>
       <c r="T13" t="n">
-        <v>60.13315864117262</v>
+        <v>57.69180855467479</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20.78030212917806</v>
+        <v>24.15402567094516</v>
       </c>
       <c r="C14" t="n">
-        <v>27.06792581636136</v>
+        <v>21.62162162162162</v>
       </c>
       <c r="D14" t="n">
-        <v>14.10805136073649</v>
+        <v>15.43624161073826</v>
       </c>
       <c r="E14" t="n">
-        <v>21.86869094726642</v>
+        <v>31.3944817300522</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04543832520518615</v>
+        <v>0.5866394399066511</v>
       </c>
       <c r="G14" t="n">
-        <v>54.33333333333334</v>
+        <v>9.926553672316384</v>
       </c>
       <c r="H14" t="n">
-        <v>1.025422325273269</v>
+        <v>0.7396070320579111</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>955</v>
+        <v>3106</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>19.2998469335665</v>
+        <v>10.25183069859263</v>
       </c>
       <c r="K14" t="n">
-        <v>11.83637017589811</v>
+        <v>6.932744476678732</v>
       </c>
       <c r="L14" t="n">
-        <v>13.48774998597666</v>
+        <v>30.59145740232785</v>
       </c>
       <c r="M14" t="n">
-        <v>13.56415724960776</v>
+        <v>30.39187954400138</v>
       </c>
       <c r="N14" t="n">
-        <v>36.12</v>
+        <v>46.4</v>
       </c>
       <c r="O14" t="n">
-        <v>12.3</v>
+        <v>6.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="R14" t="n">
-        <v>162274.18</v>
+        <v>1870170.39</v>
       </c>
       <c r="S14" t="n">
-        <v>12383</v>
+        <v>10728</v>
       </c>
       <c r="T14" t="n">
-        <v>59.61651016619649</v>
+        <v>55.90755671792368</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.56294790886726</v>
+        <v>17.99027109750765</v>
       </c>
       <c r="C15" t="n">
-        <v>17.9419388284085</v>
+        <v>3.168808778744431</v>
       </c>
       <c r="D15" t="n">
-        <v>4.993207190533383</v>
+        <v>28.8880112339828</v>
       </c>
       <c r="E15" t="n">
-        <v>8.084427730414067</v>
+        <v>62.41380175029464</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03166114022890149</v>
+        <v>6.445624336310825</v>
       </c>
       <c r="G15" t="n">
-        <v>73.29310344827586</v>
+        <v>1.300946133138182</v>
       </c>
       <c r="H15" t="n">
-        <v>2.398875873795579</v>
+        <v>0.06747535915921023</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>278</v>
+        <v>12547</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28.1325519519273</v>
+        <v>21.39660074377121</v>
       </c>
       <c r="K15" t="n">
-        <v>20.48312440202782</v>
+        <v>17.25086850260209</v>
       </c>
       <c r="L15" t="n">
-        <v>22.96698996520703</v>
+        <v>51.94877118224903</v>
       </c>
       <c r="M15" t="n">
-        <v>22.74033782145131</v>
+        <v>55.18455739153598</v>
       </c>
       <c r="N15" t="n">
-        <v>72.53</v>
+        <v>25.76</v>
       </c>
       <c r="O15" t="n">
-        <v>11.71</v>
+        <v>6.2</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>3.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>3053088.97</v>
+        <v>1319221.86</v>
       </c>
       <c r="S15" t="n">
-        <v>50789</v>
+        <v>159516</v>
       </c>
       <c r="T15" t="n">
-        <v>59.54233552850971</v>
+        <v>54.25483366558786</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>37.45613415294755</v>
+        <v>10.35839213740181</v>
       </c>
       <c r="C16" t="n">
-        <v>14.54625871578728</v>
+        <v>4.251687563503694</v>
       </c>
       <c r="D16" t="n">
-        <v>7.263066074788551</v>
+        <v>5.706018055499993</v>
       </c>
       <c r="E16" t="n">
-        <v>13.59538554282896</v>
+        <v>52.20093077836007</v>
       </c>
       <c r="F16" t="n">
-        <v>1.263124425916767</v>
+        <v>2.609472397390431</v>
       </c>
       <c r="G16" t="n">
-        <v>6.530242339274985</v>
+        <v>3.305545743553515</v>
       </c>
       <c r="H16" t="n">
-        <v>1.185123443593192</v>
+        <v>0.3393112060793767</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45133</v>
+        <v>27809</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20.57936456937097</v>
+        <v>14.23276725060496</v>
       </c>
       <c r="K16" t="n">
-        <v>7.720159538623927</v>
+        <v>13.17410230151459</v>
+      </c>
+      <c r="L16" t="n">
+        <v>38.35662769365473</v>
+      </c>
+      <c r="M16" t="n">
+        <v>67.02776523348103</v>
       </c>
       <c r="N16" t="n">
-        <v>67.06999999999999</v>
+        <v>63.78</v>
       </c>
       <c r="O16" t="n">
-        <v>0.93</v>
+        <v>6.28</v>
       </c>
       <c r="P16" t="n">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="R16" t="n">
-        <v>1504106.64</v>
+        <v>378605.83</v>
       </c>
       <c r="S16" t="n">
-        <v>437928</v>
+        <v>149982</v>
       </c>
       <c r="T16" t="n">
-        <v>58.76428095055527</v>
+        <v>52.69322977075988</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.7230643179025</v>
+        <v>37.45613415294755</v>
       </c>
       <c r="C17" t="n">
-        <v>20.87418300653595</v>
+        <v>14.54625871578728</v>
       </c>
       <c r="D17" t="n">
-        <v>9.366915605017816</v>
+        <v>7.263066074788551</v>
       </c>
       <c r="E17" t="n">
-        <v>87.42129155073948</v>
+        <v>13.59538554282896</v>
       </c>
       <c r="F17" t="n">
-        <v>0.002867677181482999</v>
+        <v>1.263124425916767</v>
       </c>
       <c r="G17" t="n">
-        <v>160.0267857142857</v>
+        <v>6.530242339274985</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3236083907247109</v>
+        <v>1.185123443593192</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>486</v>
+        <v>45133</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18.98796206427069</v>
+        <v>20.57936456937097</v>
       </c>
       <c r="K17" t="n">
-        <v>12.91184100336258</v>
-      </c>
-      <c r="L17" t="n">
-        <v>12.83917371819816</v>
-      </c>
-      <c r="M17" t="n">
-        <v>11.1392224868865</v>
+        <v>7.720159538623927</v>
       </c>
       <c r="N17" t="n">
-        <v>49</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>7.86</v>
+        <v>0.93</v>
       </c>
       <c r="P17" t="n">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1271789.21</v>
+        <v>1504106.64</v>
       </c>
       <c r="S17" t="n">
-        <v>20487</v>
+        <v>437928</v>
       </c>
       <c r="T17" t="n">
-        <v>58.37486301103623</v>
+        <v>51.6052090535713</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24.15402567094516</v>
+        <v>15.09416181067115</v>
       </c>
       <c r="C18" t="n">
-        <v>21.62162162162162</v>
+        <v>16.56383979922618</v>
       </c>
       <c r="D18" t="n">
-        <v>15.43624161073826</v>
+        <v>19.81565870053818</v>
       </c>
       <c r="E18" t="n">
-        <v>31.3944817300522</v>
+        <v>26.84289749881436</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5866394399066511</v>
+        <v>0.05142381453500244</v>
       </c>
       <c r="G18" t="n">
-        <v>9.926553672316384</v>
+        <v>58.33193277310924</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7396070320579111</v>
+        <v>0.5684929901064378</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3106</v>
+        <v>11372</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10.25183069859263</v>
+        <v>13.12675558948349</v>
       </c>
       <c r="K18" t="n">
-        <v>6.932744476678732</v>
+        <v>10.78116321985565</v>
       </c>
       <c r="L18" t="n">
-        <v>30.59145740232785</v>
+        <v>24.53682964293125</v>
       </c>
       <c r="M18" t="n">
-        <v>30.39187954400138</v>
+        <v>29.45936165164078</v>
       </c>
       <c r="N18" t="n">
-        <v>46.4</v>
+        <v>37.9</v>
       </c>
       <c r="O18" t="n">
-        <v>6.43</v>
+        <v>6.71</v>
       </c>
       <c r="P18" t="n">
-        <v>1.22</v>
+        <v>3.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="R18" t="n">
-        <v>1870170.39</v>
+        <v>1339586.09</v>
       </c>
       <c r="S18" t="n">
-        <v>10728</v>
+        <v>48497</v>
       </c>
       <c r="T18" t="n">
-        <v>58.29787713629067</v>
+        <v>51.37713526020612</v>
       </c>
     </row>
     <row r="19">
@@ -7940,775 +7943,772 @@
         <v>776352</v>
       </c>
       <c r="T19" t="n">
-        <v>55.28378884950389</v>
+        <v>51.28288911006975</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10.35839213740181</v>
+        <v>13.56294790886726</v>
       </c>
       <c r="C20" t="n">
-        <v>4.251687563503694</v>
+        <v>17.9419388284085</v>
       </c>
       <c r="D20" t="n">
-        <v>5.706018055499993</v>
+        <v>4.993207190533383</v>
       </c>
       <c r="E20" t="n">
-        <v>52.20093077836007</v>
+        <v>8.084427730414067</v>
       </c>
       <c r="F20" t="n">
-        <v>2.609472397390431</v>
+        <v>0.03166114022890149</v>
       </c>
       <c r="G20" t="n">
-        <v>3.305545743553515</v>
+        <v>73.29310344827586</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3393112060793767</v>
+        <v>2.398875873795579</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>27809</v>
+        <v>278</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14.23276725060496</v>
+        <v>28.1325519519273</v>
       </c>
       <c r="K20" t="n">
-        <v>13.17410230151459</v>
+        <v>20.48312440202782</v>
       </c>
       <c r="L20" t="n">
-        <v>38.35662769365473</v>
+        <v>22.96698996520703</v>
       </c>
       <c r="M20" t="n">
-        <v>67.02776523348103</v>
+        <v>22.74033782145131</v>
       </c>
       <c r="N20" t="n">
-        <v>63.78</v>
+        <v>72.53</v>
       </c>
       <c r="O20" t="n">
-        <v>6.28</v>
+        <v>11.71</v>
       </c>
       <c r="P20" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>378605.83</v>
+        <v>3053088.97</v>
       </c>
       <c r="S20" t="n">
-        <v>149982</v>
+        <v>50789</v>
       </c>
       <c r="T20" t="n">
-        <v>52.69322977075988</v>
+        <v>49.2334625729186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.0380853616381</v>
+        <v>14.33974005030719</v>
       </c>
       <c r="C21" t="n">
-        <v>1.390231951051347</v>
+        <v>2.148461558534627</v>
       </c>
       <c r="D21" t="n">
-        <v>24.0645524488647</v>
+        <v>23.07288232992184</v>
       </c>
       <c r="E21" t="n">
-        <v>99.50459748545694</v>
+        <v>61.41252040373843</v>
       </c>
       <c r="F21" t="n">
-        <v>8.378352548852153</v>
+        <v>6.808786667718385</v>
       </c>
       <c r="G21" t="n">
-        <v>1.31948659270683</v>
+        <v>1.400768822479211</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05492885738906</v>
+        <v>0.07038097917866981</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7906</v>
+        <v>35669</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19.10193873049559</v>
+        <v>30.18695614094877</v>
       </c>
       <c r="K21" t="n">
-        <v>19.06740855567788</v>
+        <v>21.95098428169122</v>
       </c>
       <c r="L21" t="n">
-        <v>23.24502393394037</v>
+        <v>23.86506357287907</v>
       </c>
       <c r="M21" t="n">
-        <v>20.11244339814313</v>
+        <v>15.42478808253083</v>
       </c>
       <c r="N21" t="n">
-        <v>9.81</v>
+        <v>49.42</v>
       </c>
       <c r="O21" t="n">
-        <v>3.91</v>
+        <v>4.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.82</v>
+        <v>4.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R21" t="n">
-        <v>2618348.58</v>
+        <v>808359.03</v>
       </c>
       <c r="S21" t="n">
-        <v>26645</v>
+        <v>283649</v>
       </c>
       <c r="T21" t="n">
-        <v>50.05123927590353</v>
+        <v>47.16364601771759</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17.99027109750765</v>
+        <v>16.71605179468811</v>
       </c>
       <c r="C22" t="n">
-        <v>3.168808778744431</v>
+        <v>1.368070466573592</v>
       </c>
       <c r="D22" t="n">
-        <v>28.8880112339828</v>
+        <v>13.93516047014541</v>
       </c>
       <c r="E22" t="n">
-        <v>62.41380175029464</v>
+        <v>41.75390656810141</v>
       </c>
       <c r="F22" t="n">
-        <v>6.445624336310825</v>
+        <v>14.86741992554242</v>
       </c>
       <c r="G22" t="n">
-        <v>1.300946133138182</v>
+        <v>1.610661174334986</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06747535915921023</v>
+        <v>0.0719985042520674</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>12547</v>
+        <v>13296</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>21.39660074377121</v>
+        <v>16.30293930023252</v>
       </c>
       <c r="K22" t="n">
-        <v>17.25086850260209</v>
+        <v>18.17561078322378</v>
       </c>
       <c r="L22" t="n">
-        <v>51.94877118224903</v>
+        <v>85.7752850068174</v>
       </c>
       <c r="M22" t="n">
-        <v>55.18455739153598</v>
+        <v>53.4206382524911</v>
       </c>
       <c r="N22" t="n">
-        <v>25.76</v>
+        <v>36.74</v>
       </c>
       <c r="O22" t="n">
-        <v>6.2</v>
+        <v>12.61</v>
       </c>
       <c r="P22" t="n">
-        <v>3.43</v>
+        <v>3.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>1319221.86</v>
+        <v>496415.88</v>
       </c>
       <c r="S22" t="n">
-        <v>159516</v>
+        <v>110519</v>
       </c>
       <c r="T22" t="n">
-        <v>49.77499869166721</v>
+        <v>46.09979877526326</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15.75038535195478</v>
+        <v>29.78800671841663</v>
       </c>
       <c r="C23" t="n">
-        <v>20.31834878432744</v>
+        <v>37.30292821974604</v>
       </c>
       <c r="D23" t="n">
-        <v>9.50809964894472</v>
+        <v>17.08075746730006</v>
       </c>
       <c r="E23" t="n">
-        <v>13.13003143989059</v>
+        <v>23.70339038198738</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001389602503619973</v>
+        <v>0.09486358890553362</v>
       </c>
       <c r="G23" t="n">
-        <v>117.9072164948454</v>
+        <v>87.52340425531915</v>
       </c>
       <c r="H23" t="n">
-        <v>1.230295566502463</v>
+        <v>1.129760329363329</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>4936</v>
+        <v>20117</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>26.32364432616601</v>
+        <v>15.21650079880636</v>
       </c>
       <c r="K23" t="n">
-        <v>10.51021511264258</v>
+        <v>13.19910093055623</v>
       </c>
       <c r="L23" t="n">
-        <v>12.00718203930038</v>
+        <v>11.23941998365794</v>
       </c>
       <c r="M23" t="n">
-        <v>11.1392224868865</v>
+        <v>12.47461131420948</v>
       </c>
       <c r="N23" t="n">
-        <v>20.78</v>
+        <v>35.99</v>
       </c>
       <c r="O23" t="n">
-        <v>8.26</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>29</v>
+        <v>4.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1503863.63</v>
+        <v>1112279.92</v>
       </c>
       <c r="S23" t="n">
-        <v>141858</v>
+        <v>153670</v>
       </c>
       <c r="T23" t="n">
-        <v>49.23865164943381</v>
+        <v>45.58342731354364</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14.33974005030719</v>
+        <v>13.0380853616381</v>
       </c>
       <c r="C24" t="n">
-        <v>2.148461558534627</v>
+        <v>1.390231951051347</v>
       </c>
       <c r="D24" t="n">
-        <v>23.07288232992184</v>
+        <v>24.0645524488647</v>
       </c>
       <c r="E24" t="n">
-        <v>61.41252040373843</v>
+        <v>99.50459748545694</v>
       </c>
       <c r="F24" t="n">
-        <v>6.808786667718385</v>
+        <v>8.378352548852153</v>
       </c>
       <c r="G24" t="n">
-        <v>1.400768822479211</v>
+        <v>1.31948659270683</v>
       </c>
       <c r="H24" t="n">
-        <v>0.07038097917866981</v>
+        <v>0.05492885738906</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>35669</v>
+        <v>7906</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>30.18695614094877</v>
+        <v>19.10193873049559</v>
       </c>
       <c r="K24" t="n">
-        <v>21.95098428169122</v>
+        <v>19.06740855567788</v>
       </c>
       <c r="L24" t="n">
-        <v>23.86506357287907</v>
+        <v>23.24502393394037</v>
       </c>
       <c r="M24" t="n">
-        <v>15.42478808253083</v>
+        <v>20.11244339814313</v>
       </c>
       <c r="N24" t="n">
-        <v>49.42</v>
+        <v>9.81</v>
       </c>
       <c r="O24" t="n">
-        <v>4.4</v>
+        <v>3.91</v>
       </c>
       <c r="P24" t="n">
-        <v>4.33</v>
+        <v>2.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="R24" t="n">
-        <v>808359.03</v>
+        <v>2618348.58</v>
       </c>
       <c r="S24" t="n">
-        <v>283649</v>
+        <v>26645</v>
       </c>
       <c r="T24" t="n">
-        <v>48.88959773887582</v>
+        <v>43.7068962147807</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.27359840706863</v>
+        <v>16.94039813688551</v>
       </c>
       <c r="C25" t="n">
-        <v>7.073680188819151</v>
+        <v>15.67768347234376</v>
       </c>
       <c r="D25" t="n">
-        <v>11.95063332978527</v>
+        <v>9.655290194725701</v>
       </c>
       <c r="E25" t="n">
-        <v>28.82672926202094</v>
+        <v>17.38851801500179</v>
       </c>
       <c r="F25" t="n">
-        <v>1.475521125007778</v>
+        <v>0.4544486308481918</v>
       </c>
       <c r="G25" t="n">
-        <v>4.604991464108609</v>
+        <v>11.361290955464</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3724372910920176</v>
+        <v>0.8332173339682772</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8644</v>
+        <v>42060</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>16.97193810203161</v>
+        <v>24.85526395727469</v>
       </c>
       <c r="K25" t="n">
-        <v>12.22230965433799</v>
+        <v>7.001683761214439</v>
       </c>
       <c r="L25" t="n">
-        <v>8.735165684951163</v>
+        <v>10.96639922553624</v>
       </c>
       <c r="M25" t="n">
-        <v>8.447177119769854</v>
+        <v>10.19722877214802</v>
       </c>
       <c r="N25" t="n">
-        <v>30.8</v>
+        <v>18.15</v>
       </c>
       <c r="O25" t="n">
-        <v>5.24</v>
+        <v>10.36</v>
       </c>
       <c r="P25" t="n">
-        <v>0.06</v>
+        <v>1.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="R25" t="n">
-        <v>907823.11</v>
+        <v>390111.05</v>
       </c>
       <c r="S25" t="n">
-        <v>178501</v>
+        <v>591396</v>
       </c>
       <c r="T25" t="n">
-        <v>47.99595327840979</v>
+        <v>43.29365313620517</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9.958650553699458</v>
+        <v>8.370767521615225</v>
       </c>
       <c r="C26" t="n">
-        <v>8.361624052274221</v>
+        <v>13.23404445637104</v>
       </c>
       <c r="D26" t="n">
-        <v>8.789365557299389</v>
+        <v>8.445007553238145</v>
       </c>
       <c r="E26" t="n">
-        <v>18.07459281612296</v>
+        <v>22.01647093221578</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5784524141094746</v>
+        <v>0.07998840747717723</v>
       </c>
       <c r="G26" t="n">
-        <v>7.728912535686478</v>
+        <v>19.82558139534884</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5122600635424216</v>
+        <v>0.7348612354521038</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45207</v>
+        <v>1929</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>24.46173600944801</v>
+        <v>14.80997180241832</v>
       </c>
       <c r="K26" t="n">
-        <v>9.606097094616972</v>
+        <v>10.32561591555659</v>
       </c>
       <c r="L26" t="n">
-        <v>14.68063260349559</v>
+        <v>11.2926552609119</v>
       </c>
       <c r="M26" t="n">
-        <v>11.95266483252204</v>
+        <v>10.67987982673917</v>
       </c>
       <c r="N26" t="n">
-        <v>58.34</v>
+        <v>25.87</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>1.21</v>
       </c>
       <c r="P26" t="n">
-        <v>4.21</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R26" t="n">
-        <v>432472.71</v>
+        <v>3154358.33</v>
       </c>
       <c r="S26" t="n">
-        <v>899041</v>
+        <v>20521</v>
       </c>
       <c r="T26" t="n">
-        <v>47.06763083531943</v>
+        <v>42.94800389990229</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.63992042440318</v>
+        <v>15.75038535195478</v>
       </c>
       <c r="C27" t="n">
-        <v>26.2827398165744</v>
+        <v>20.31834878432744</v>
       </c>
       <c r="D27" t="n">
-        <v>14.88611227356968</v>
+        <v>9.50809964894472</v>
       </c>
       <c r="E27" t="n">
-        <v>12.52466072816405</v>
+        <v>13.13003143989059</v>
       </c>
       <c r="F27" t="n">
-        <v>0.003232758620689655</v>
+        <v>0.001389602503619973</v>
       </c>
       <c r="G27" t="n">
-        <v>71.78431372549019</v>
+        <v>117.9072164948454</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9638144626908672</v>
+        <v>1.230295566502463</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1536</v>
+        <v>4936</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>19.843289373664</v>
+        <v>26.32364432616601</v>
       </c>
       <c r="K27" t="n">
-        <v>6.717165240230294</v>
+        <v>10.51021511264258</v>
       </c>
       <c r="L27" t="n">
-        <v>9.275930793686072</v>
+        <v>12.00718203930038</v>
       </c>
       <c r="M27" t="n">
-        <v>9.261870727688626</v>
+        <v>11.1392224868865</v>
       </c>
       <c r="N27" t="n">
-        <v>58.43</v>
+        <v>20.78</v>
       </c>
       <c r="O27" t="n">
-        <v>6.47</v>
+        <v>8.26</v>
       </c>
       <c r="P27" t="n">
-        <v>4.23</v>
+        <v>1.78</v>
       </c>
       <c r="Q27" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="R27" t="n">
-        <v>2599556.05</v>
+        <v>1503863.63</v>
       </c>
       <c r="S27" t="n">
-        <v>16727</v>
+        <v>141858</v>
       </c>
       <c r="T27" t="n">
-        <v>45.21496781773225</v>
+        <v>42.2423881483173</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16.94039813688551</v>
+        <v>9.567011474761177</v>
       </c>
       <c r="C28" t="n">
-        <v>15.67768347234376</v>
+        <v>8.622663105684854</v>
       </c>
       <c r="D28" t="n">
-        <v>9.655290194725701</v>
+        <v>4.702216130615571</v>
       </c>
       <c r="E28" t="n">
-        <v>17.38851801500179</v>
+        <v>88.94620349876368</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4544486308481918</v>
+        <v>0.5309290976579428</v>
       </c>
       <c r="G28" t="n">
-        <v>11.361290955464</v>
+        <v>126.4654377880184</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8332173339682772</v>
+        <v>0.9360228499109322</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>42060</v>
+        <v>9789</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>24.85526395727469</v>
+        <v>17.83085522343517</v>
       </c>
       <c r="K28" t="n">
-        <v>7.001683761214439</v>
+        <v>10.59243381898591</v>
       </c>
       <c r="L28" t="n">
-        <v>10.96639922553624</v>
+        <v>13.06871230695661</v>
       </c>
       <c r="M28" t="n">
-        <v>10.19722877214802</v>
+        <v>13.39665776330272</v>
       </c>
       <c r="N28" t="n">
-        <v>18.15</v>
+        <v>56.45</v>
       </c>
       <c r="O28" t="n">
-        <v>10.36</v>
+        <v>9.32</v>
       </c>
       <c r="P28" t="n">
-        <v>1.11</v>
+        <v>0.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="R28" t="n">
-        <v>390111.05</v>
+        <v>722281.1</v>
       </c>
       <c r="S28" t="n">
-        <v>591396</v>
+        <v>215962</v>
       </c>
       <c r="T28" t="n">
-        <v>43.63009417228872</v>
+        <v>41.67073140979862</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9.567011474761177</v>
+        <v>20.63992042440318</v>
       </c>
       <c r="C29" t="n">
-        <v>8.622663105684854</v>
+        <v>26.2827398165744</v>
       </c>
       <c r="D29" t="n">
-        <v>4.702216130615571</v>
+        <v>14.88611227356968</v>
       </c>
       <c r="E29" t="n">
-        <v>88.94620349876368</v>
+        <v>12.52466072816405</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5309290976579428</v>
+        <v>0.003232758620689655</v>
       </c>
       <c r="G29" t="n">
-        <v>126.4654377880184</v>
+        <v>71.78431372549019</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9360228499109322</v>
+        <v>0.9638144626908672</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>9789</v>
+        <v>1536</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>17.83085522343517</v>
+        <v>19.843289373664</v>
       </c>
       <c r="K29" t="n">
-        <v>10.59243381898591</v>
+        <v>6.717165240230294</v>
       </c>
       <c r="L29" t="n">
-        <v>13.06871230695661</v>
+        <v>9.275930793686072</v>
       </c>
       <c r="M29" t="n">
-        <v>13.39665776330272</v>
+        <v>9.261870727688626</v>
       </c>
       <c r="N29" t="n">
-        <v>56.45</v>
+        <v>58.43</v>
       </c>
       <c r="O29" t="n">
-        <v>9.32</v>
+        <v>6.47</v>
       </c>
       <c r="P29" t="n">
-        <v>0.98</v>
+        <v>4.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="R29" t="n">
-        <v>722281.1</v>
+        <v>2599556.05</v>
       </c>
       <c r="S29" t="n">
-        <v>215962</v>
+        <v>16727</v>
       </c>
       <c r="T29" t="n">
-        <v>41.51010973186696</v>
+        <v>38.77359464614575</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>16.71605179468811</v>
+        <v>9.958650553699458</v>
       </c>
       <c r="C30" t="n">
-        <v>1.368070466573592</v>
+        <v>8.361624052274221</v>
       </c>
       <c r="D30" t="n">
-        <v>13.93516047014541</v>
+        <v>8.789365557299389</v>
       </c>
       <c r="E30" t="n">
-        <v>41.75390656810141</v>
+        <v>18.07459281612296</v>
       </c>
       <c r="F30" t="n">
-        <v>14.86741992554242</v>
+        <v>0.5784524141094746</v>
       </c>
       <c r="G30" t="n">
-        <v>1.610661174334986</v>
+        <v>7.728912535686478</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0719985042520674</v>
+        <v>0.5122600635424216</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>13296</v>
+        <v>45207</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>16.30293930023252</v>
+        <v>24.46173600944801</v>
       </c>
       <c r="K30" t="n">
-        <v>18.17561078322378</v>
+        <v>9.606097094616972</v>
       </c>
       <c r="L30" t="n">
-        <v>85.7752850068174</v>
+        <v>14.68063260349559</v>
       </c>
       <c r="M30" t="n">
-        <v>53.4206382524911</v>
+        <v>11.95266483252204</v>
       </c>
       <c r="N30" t="n">
-        <v>36.74</v>
+        <v>58.34</v>
       </c>
       <c r="O30" t="n">
-        <v>12.61</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>3.81</v>
+        <v>4.21</v>
       </c>
       <c r="Q30" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R30" t="n">
-        <v>496415.88</v>
+        <v>432472.71</v>
       </c>
       <c r="S30" t="n">
-        <v>110519</v>
+        <v>899041</v>
       </c>
       <c r="T30" t="n">
-        <v>41.24609119135111</v>
+        <v>36.88286583267566</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8.370767521615225</v>
+        <v>13.27359840706863</v>
       </c>
       <c r="C31" t="n">
-        <v>13.23404445637104</v>
+        <v>7.073680188819151</v>
       </c>
       <c r="D31" t="n">
-        <v>8.445007553238145</v>
+        <v>11.95063332978527</v>
       </c>
       <c r="E31" t="n">
-        <v>22.01647093221578</v>
+        <v>28.82672926202094</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07998840747717723</v>
+        <v>1.475521125007778</v>
       </c>
       <c r="G31" t="n">
-        <v>19.82558139534884</v>
+        <v>4.604991464108609</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7348612354521038</v>
+        <v>0.3724372910920176</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1929</v>
+        <v>8644</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14.80997180241832</v>
+        <v>16.97193810203161</v>
       </c>
       <c r="K31" t="n">
-        <v>10.32561591555659</v>
+        <v>12.22230965433799</v>
       </c>
       <c r="L31" t="n">
-        <v>11.2926552609119</v>
+        <v>8.735165684951163</v>
       </c>
       <c r="M31" t="n">
-        <v>10.67987982673917</v>
+        <v>8.447177119769854</v>
       </c>
       <c r="N31" t="n">
-        <v>25.87</v>
+        <v>30.8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.21</v>
+        <v>5.24</v>
       </c>
       <c r="P31" t="n">
-        <v>3.2</v>
+        <v>0.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="R31" t="n">
-        <v>3154358.33</v>
+        <v>907823.11</v>
       </c>
       <c r="S31" t="n">
-        <v>20521</v>
+        <v>178501</v>
       </c>
       <c r="T31" t="n">
-        <v>39.93760869022043</v>
+        <v>30.6078239851872</v>
       </c>
     </row>
     <row r="32">
@@ -8772,7 +8772,7 @@
         <v>61449</v>
       </c>
       <c r="T32" t="n">
-        <v>38.41377147438534</v>
+        <v>28.93756947173712</v>
       </c>
     </row>
     <row r="33">
@@ -8836,7 +8836,7 @@
         <v>51996</v>
       </c>
       <c r="T33" t="n">
-        <v>38.39269885718054</v>
+        <v>27.43907441125606</v>
       </c>
     </row>
   </sheetData>

--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality Compounder" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value Pick" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth Accelerator" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dividend Champion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt-Free Blue Chip" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turnaround Watch" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Quality Compounder" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Value Pick" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Growth Accelerator" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dividend Champion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt-Free Blue Chip" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Turnaround Watch" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +45,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,10 +66,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -586,34 +593,34 @@
       <c r="I2" s="2" t="n">
         <v>3556</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>17.80103767695105</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>13.02966034945308</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>20.27736210195506</v>
       </c>
       <c r="M2" t="n">
         <v>20.97355268843126</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>73.37</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>2.42</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>58</v>
       </c>
       <c r="R2" t="n">
         <v>2126725.18</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="2" t="n">
         <v>35495</v>
       </c>
       <c r="T2" t="n">
@@ -650,34 +657,34 @@
       <c r="I3" s="2" t="n">
         <v>667</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>76.46921430165466</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>17.95524410389091</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="2" t="n">
         <v>29.16686408659448</v>
       </c>
       <c r="M3" t="n">
         <v>28.47351571234393</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="n">
         <v>60.44</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="3" t="n">
         <v>5.74</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="2" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>47</v>
       </c>
       <c r="R3" t="n">
         <v>1258520.29</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="3" t="n">
         <v>4270</v>
       </c>
       <c r="T3" t="n">
@@ -714,28 +721,28 @@
       <c r="I4" s="2" t="n">
         <v>17651</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="2" t="n">
         <v>24.29479715622616</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>16.08609641044097</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>44.57</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>9.91</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="2" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1372183.55</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="2" t="n">
         <v>50351</v>
       </c>
       <c r="T4" t="n">
@@ -772,34 +779,34 @@
       <c r="I5" s="2" t="n">
         <v>955</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="2" t="n">
         <v>19.2998469335665</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>11.83637017589811</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>13.48774998597666</v>
       </c>
       <c r="M5" t="n">
         <v>13.56415724960776</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>36.12</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="2" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="2" t="n">
         <v>47</v>
       </c>
       <c r="R5" t="n">
         <v>162274.18</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="2" t="n">
         <v>12383</v>
       </c>
       <c r="T5" t="n">
@@ -809,181 +816,181 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>117.7544910179641</v>
+        <v>17.69876929087712</v>
       </c>
       <c r="C6" t="n">
-        <v>143.527815468114</v>
+        <v>23.27321565617805</v>
       </c>
       <c r="D6" t="n">
-        <v>16.12281708616873</v>
+        <v>12.22122302158273</v>
       </c>
       <c r="E6" t="n">
-        <v>23.82963023694351</v>
+        <v>13.9568345323741</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.1032934131736527</v>
+        <v>0.01816761086149639</v>
       </c>
       <c r="G6" t="n">
-        <v>41.18620689655172</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>2.318160220469448</v>
+        <v>0.8790861298865568</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2938</v>
-      </c>
-      <c r="J6" t="n">
-        <v>18.28200866249903</v>
+        <v>1168</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>18.99870072744285</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>14.54857371180267</v>
-      </c>
-      <c r="L6" t="n">
-        <v>14.85231951299384</v>
+        <v>11.1933589020679</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>19.85339817550189</v>
       </c>
       <c r="M6" t="n">
-        <v>15.43852585822143</v>
-      </c>
-      <c r="N6" t="n">
-        <v>54.96</v>
-      </c>
-      <c r="O6" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>79</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1677775.19</v>
-      </c>
-      <c r="S6" t="n">
-        <v>24394</v>
+        <v>19.64385000375561</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>22240</v>
       </c>
       <c r="T6" t="n">
-        <v>76.26865270052919</v>
+        <v>77.08886610587359</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>36.30776794493609</v>
+        <v>117.7544910179641</v>
       </c>
       <c r="C7" t="n">
-        <v>33.00120254251846</v>
+        <v>143.527815468114</v>
       </c>
       <c r="D7" t="n">
-        <v>11.93535353535353</v>
+        <v>16.12281708616873</v>
       </c>
       <c r="E7" t="n">
-        <v>15.92727272727273</v>
+        <v>23.82963023694351</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.4309242871189774</v>
+        <v>0.1032934131736527</v>
       </c>
       <c r="G7" t="n">
-        <v>8.043478260869565</v>
+        <v>41.18620689655172</v>
       </c>
       <c r="H7" t="n">
-        <v>1.727869310248534</v>
+        <v>2.318160220469448</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>841</v>
-      </c>
-      <c r="J7" t="n">
-        <v>68.36335197744833</v>
+        <v>2938</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>18.28200866249903</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>36.30691600183056</v>
-      </c>
-      <c r="L7" t="n">
-        <v>73.11367578503176</v>
+        <v>14.54857371180267</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>14.85231951299384</v>
       </c>
       <c r="M7" t="n">
-        <v>69.52182030724354</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="O7" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>8</v>
+        <v>15.43852585822143</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>79</v>
       </c>
       <c r="R7" t="n">
-        <v>571322.04</v>
-      </c>
-      <c r="S7" t="n">
-        <v>12375</v>
+        <v>1677775.19</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>24394</v>
       </c>
       <c r="T7" t="n">
-        <v>74.759015326533</v>
+        <v>76.26865270052919</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>17.69876929087712</v>
+        <v>36.30776794493609</v>
       </c>
       <c r="C8" t="n">
-        <v>23.27321565617805</v>
+        <v>33.00120254251846</v>
       </c>
       <c r="D8" t="n">
-        <v>12.22122302158273</v>
+        <v>11.93535353535353</v>
       </c>
       <c r="E8" t="n">
-        <v>13.9568345323741</v>
+        <v>15.92727272727273</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.01816761086149639</v>
+        <v>0.4309242871189774</v>
       </c>
       <c r="G8" t="n">
-        <v>67.15000000000001</v>
+        <v>8.043478260869565</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8790861298865568</v>
+        <v>1.727869310248534</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1168</v>
-      </c>
-      <c r="J8" t="n">
-        <v>18.99870072744285</v>
+        <v>841</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>68.36335197744833</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>11.1933589020679</v>
-      </c>
-      <c r="L8" t="n">
-        <v>19.85339817550189</v>
+        <v>36.30691600183056</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>73.11367578503176</v>
       </c>
       <c r="M8" t="n">
-        <v>19.64385000375561</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>16</v>
-      </c>
-      <c r="S8" t="n">
-        <v>22240</v>
+        <v>69.52182030724354</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R8" t="n">
+        <v>571322.04</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>12375</v>
       </c>
       <c r="T8" t="n">
-        <v>68.12570273895892</v>
+        <v>74.759015326533</v>
       </c>
     </row>
     <row r="9">
@@ -1016,38 +1023,38 @@
       <c r="I9" s="2" t="n">
         <v>8250</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="2" t="n">
         <v>28.63193631184944</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>19.57867595245697</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="3" t="n">
         <v>14.90956518204163</v>
       </c>
       <c r="M9" t="n">
         <v>14.86983549970351</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>48.9</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="2" t="n">
         <v>2.31</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="2" t="n">
         <v>1.16</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="2" t="n">
         <v>16</v>
       </c>
       <c r="R9" t="n">
         <v>675598.01</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="2" t="n">
         <v>26711</v>
       </c>
       <c r="T9" t="n">
-        <v>64.60059842643911</v>
+        <v>70.30971582063562</v>
       </c>
     </row>
     <row r="10">
@@ -1080,34 +1087,34 @@
       <c r="I10" s="2" t="n">
         <v>50429</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="2" t="n">
         <v>13.63286455550641</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>10.4636148017166</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>7.871172131953608</v>
       </c>
       <c r="M10" t="n">
         <v>8.618771612987096</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>78.69</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="3" t="n">
         <v>6.08</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="2" t="n">
         <v>1.62</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="2" t="n">
         <v>58</v>
       </c>
       <c r="R10" t="n">
         <v>461188.15</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="2" t="n">
         <v>240893</v>
       </c>
       <c r="T10" t="n">
@@ -1117,129 +1124,129 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>19.74233736816026</v>
+        <v>15.7230643179025</v>
       </c>
       <c r="C11" t="n">
-        <v>23.8002379693284</v>
+        <v>20.87418300653595</v>
       </c>
       <c r="D11" t="n">
-        <v>19.9136053693192</v>
+        <v>9.366915605017816</v>
       </c>
       <c r="E11" t="n">
-        <v>28.32101674342223</v>
+        <v>87.42129155073948</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.07085722375592836</v>
+        <v>0.002867677181482999</v>
       </c>
       <c r="G11" t="n">
-        <v>51.70760233918129</v>
+        <v>160.0267857142857</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7223053120165034</v>
+        <v>0.3236083907247109</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>509</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13.71726615103832</v>
+        <v>486</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>18.98796206427069</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>12.63964434957199</v>
-      </c>
-      <c r="L11" t="n">
-        <v>23.39250464543747</v>
+        <v>12.91184100336258</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>12.83917371819816</v>
       </c>
       <c r="M11" t="n">
-        <v>23.84240955838754</v>
-      </c>
-      <c r="N11" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="O11" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>12</v>
+        <v>11.1392224868865</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>28</v>
       </c>
       <c r="R11" t="n">
-        <v>2441803.28</v>
-      </c>
-      <c r="S11" t="n">
-        <v>28011</v>
+        <v>1271789.21</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>20487</v>
       </c>
       <c r="T11" t="n">
-        <v>59.28443274332121</v>
+        <v>59.23751631808607</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>15.7230643179025</v>
+        <v>17.06727541291795</v>
       </c>
       <c r="C12" t="n">
-        <v>20.87418300653595</v>
+        <v>22.0258064516129</v>
       </c>
       <c r="D12" t="n">
-        <v>9.366915605017816</v>
+        <v>6.837009144701453</v>
       </c>
       <c r="E12" t="n">
-        <v>87.42129155073948</v>
+        <v>10.11834319526627</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.002867677181482999</v>
+        <v>0.040687525177924</v>
       </c>
       <c r="G12" t="n">
-        <v>160.0267857142857</v>
+        <v>25.35714285714286</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3236083907247109</v>
+        <v>1.495214348910158</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>486</v>
-      </c>
-      <c r="J12" t="n">
-        <v>18.98796206427069</v>
+        <v>335</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>21.14089015706202</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>12.91184100336258</v>
-      </c>
-      <c r="L12" t="n">
-        <v>12.83917371819816</v>
+        <v>13.03790793906312</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>10.03323122942004</v>
       </c>
       <c r="M12" t="n">
-        <v>11.1392224868865</v>
-      </c>
-      <c r="N12" t="n">
-        <v>49</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>28</v>
+        <v>8.997698704834534</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>44</v>
       </c>
       <c r="R12" t="n">
-        <v>1271789.21</v>
-      </c>
-      <c r="S12" t="n">
-        <v>20487</v>
+        <v>2521508.87</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>18590</v>
       </c>
       <c r="T12" t="n">
-        <v>59.23751631808607</v>
+        <v>58.15011682984635</v>
       </c>
     </row>
     <row r="13">
@@ -1272,34 +1279,34 @@
       <c r="I13" s="2" t="n">
         <v>15840</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="2" t="n">
         <v>13.39647732977698</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>12.71029997837341</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>9.194090295112023</v>
       </c>
       <c r="M13" t="n">
         <v>9.407036350794119</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="3" t="n">
         <v>63.63</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="3" t="n">
         <v>5.44</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" s="3" t="n">
         <v>90</v>
       </c>
       <c r="R13" t="n">
         <v>412593.29</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="2" t="n">
         <v>109913</v>
       </c>
       <c r="T13" t="n">
@@ -1336,34 +1343,34 @@
       <c r="I14" s="2" t="n">
         <v>1752</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="2" t="n">
         <v>42.13101535214459</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>30.32798083513346</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14" s="2" t="n">
         <v>24.775129058601</v>
       </c>
       <c r="M14" t="n">
         <v>12.24383304425547</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14" s="3" t="n">
         <v>64.52</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" s="2" t="n">
         <v>4.43</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14" s="2" t="n">
         <v>42</v>
       </c>
       <c r="R14" t="n">
         <v>1347046.9</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14" s="2" t="n">
         <v>35517</v>
       </c>
       <c r="T14" t="n">
@@ -1400,34 +1407,34 @@
       <c r="I15" s="2" t="n">
         <v>12547</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="2" t="n">
         <v>21.39660074377121</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>17.25086850260209</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="2" t="n">
         <v>51.94877118224903</v>
       </c>
       <c r="M15" t="n">
         <v>55.18455739153598</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="2" t="n">
         <v>25.76</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="2" t="n">
         <v>16</v>
       </c>
       <c r="R15" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="2" t="n">
         <v>159516</v>
       </c>
       <c r="T15" t="n">
@@ -1464,34 +1471,34 @@
       <c r="I16" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="2" t="n">
         <v>23.776441520116</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>11.03693649673969</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="3" t="n">
         <v>12.6758416653777</v>
       </c>
       <c r="M16" t="n">
         <v>12.50545162905032</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="2" t="n">
         <v>15.62</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="3" t="n">
         <v>13.61</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="2" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" s="2" t="n">
         <v>35</v>
       </c>
       <c r="R16" t="n">
         <v>222391.83</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16" s="2" t="n">
         <v>16536</v>
       </c>
       <c r="T16" t="n">
@@ -1501,65 +1508,65 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>15.09416181067115</v>
+        <v>19.74233736816026</v>
       </c>
       <c r="C17" t="n">
-        <v>16.56383979922618</v>
+        <v>23.8002379693284</v>
       </c>
       <c r="D17" t="n">
-        <v>19.81565870053818</v>
+        <v>19.9136053693192</v>
       </c>
       <c r="E17" t="n">
-        <v>26.84289749881436</v>
+        <v>28.32101674342223</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.05142381453500244</v>
+        <v>0.07085722375592836</v>
       </c>
       <c r="G17" t="n">
-        <v>58.33193277310924</v>
+        <v>51.70760233918129</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5684929901064378</v>
+        <v>0.7223053120165034</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>11372</v>
-      </c>
-      <c r="J17" t="n">
-        <v>13.12675558948349</v>
+        <v>509</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>13.71726615103832</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>10.78116321985565</v>
-      </c>
-      <c r="L17" t="n">
-        <v>24.53682964293125</v>
+        <v>12.63964434957199</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>23.39250464543747</v>
       </c>
       <c r="M17" t="n">
-        <v>29.45936165164078</v>
-      </c>
-      <c r="N17" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>34</v>
+        <v>23.84240955838754</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>1339586.09</v>
-      </c>
-      <c r="S17" t="n">
-        <v>48497</v>
+        <v>2441803.28</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>28011</v>
       </c>
       <c r="T17" t="n">
-        <v>51.37713526020612</v>
+        <v>50.25220217061991</v>
       </c>
     </row>
     <row r="18">
@@ -1592,34 +1599,34 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="2" t="n">
         <v>38.18335427451367</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>21.08864867789759</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="2" t="n">
         <v>23.8762916927858</v>
       </c>
       <c r="M18" t="n">
         <v>24.57309396155174</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="3" t="n">
         <v>56.96</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="3" t="n">
         <v>5.76</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18" s="2" t="n">
         <v>4</v>
       </c>
       <c r="R18" t="n">
         <v>1535602.41</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="3" t="n">
         <v>4475</v>
       </c>
       <c r="T18" t="n">
@@ -1629,65 +1636,65 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>17.06727541291795</v>
+        <v>15.09416181067115</v>
       </c>
       <c r="C19" t="n">
-        <v>22.0258064516129</v>
+        <v>16.56383979922618</v>
       </c>
       <c r="D19" t="n">
-        <v>6.837009144701453</v>
+        <v>19.81565870053818</v>
       </c>
       <c r="E19" t="n">
-        <v>10.11834319526627</v>
+        <v>26.84289749881436</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.040687525177924</v>
+        <v>0.05142381453500244</v>
       </c>
       <c r="G19" t="n">
-        <v>25.35714285714286</v>
+        <v>58.33193277310924</v>
       </c>
       <c r="H19" t="n">
-        <v>1.495214348910158</v>
+        <v>0.5684929901064378</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>335</v>
-      </c>
-      <c r="J19" t="n">
-        <v>21.14089015706202</v>
+        <v>11372</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>13.12675558948349</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>13.03790793906312</v>
-      </c>
-      <c r="L19" t="n">
-        <v>10.03323122942004</v>
+        <v>10.78116321985565</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>24.53682964293125</v>
       </c>
       <c r="M19" t="n">
-        <v>8.997698704834534</v>
-      </c>
-      <c r="N19" t="n">
-        <v>45.41</v>
-      </c>
-      <c r="O19" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>44</v>
+        <v>29.45936165164078</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>34</v>
       </c>
       <c r="R19" t="n">
-        <v>2521508.87</v>
-      </c>
-      <c r="S19" t="n">
-        <v>18590</v>
+        <v>1339586.09</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>48497</v>
       </c>
       <c r="T19" t="n">
-        <v>48.75439737462181</v>
+        <v>47.85970653156618</v>
       </c>
     </row>
     <row r="20">
@@ -1720,34 +1727,34 @@
       <c r="I20" s="2" t="n">
         <v>13296</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="2" t="n">
         <v>16.30293930023252</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>18.17561078322378</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="2" t="n">
         <v>85.7752850068174</v>
       </c>
       <c r="M20" t="n">
         <v>53.4206382524911</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="3" t="n">
         <v>36.74</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="3" t="n">
         <v>12.61</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="2" t="n">
         <v>3.81</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="R20" t="n">
         <v>496415.88</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S20" s="2" t="n">
         <v>110519</v>
       </c>
       <c r="T20" t="n">
@@ -1784,31 +1791,31 @@
       <c r="I21" s="2" t="n">
         <v>20117</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="2" t="n">
         <v>15.21650079880636</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>13.19910093055623</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>11.23941998365794</v>
       </c>
       <c r="M21" t="n">
         <v>12.47461131420948</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="3" t="n">
         <v>35.99</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="3" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="2" t="n">
         <v>4.1</v>
       </c>
       <c r="R21" t="n">
         <v>1112279.92</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21" s="2" t="n">
         <v>153670</v>
       </c>
       <c r="T21" t="n">
@@ -1845,34 +1852,34 @@
       <c r="I22" s="2" t="n">
         <v>4936</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="2" t="n">
         <v>26.32364432616601</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>10.51021511264258</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>12.00718203930038</v>
       </c>
       <c r="M22" t="n">
         <v>11.1392224868865</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="2" t="n">
         <v>20.78</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="3" t="n">
         <v>8.26</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="2" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="2" t="n">
         <v>29</v>
       </c>
       <c r="R22" t="n">
         <v>1503863.63</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="2" t="n">
         <v>141858</v>
       </c>
       <c r="T22" t="n">
@@ -2023,7 +2030,7 @@
           <t>IOC</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>23.53162465856491</v>
       </c>
       <c r="C2" t="n">
@@ -2044,16 +2051,16 @@
       <c r="H2" t="n">
         <v>1.608409660170339</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>39635</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>28.72779122527918</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="3" t="n">
         <v>8.008755667240486</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>20.09908996673164</v>
       </c>
       <c r="M2" t="n">
@@ -2068,13 +2075,13 @@
       <c r="P2" s="2" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>40</v>
       </c>
       <c r="R2" t="n">
         <v>1418164.33</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="2" t="n">
         <v>776352</v>
       </c>
       <c r="T2" t="n">
@@ -2087,7 +2094,7 @@
           <t>IRFC</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>13.0380853616381</v>
       </c>
       <c r="C3" t="n">
@@ -2108,16 +2115,16 @@
       <c r="H3" t="n">
         <v>0.05492885738906</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>7906</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>19.10193873049559</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="2" t="n">
         <v>19.06740855567788</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="2" t="n">
         <v>23.24502393394037</v>
       </c>
       <c r="M3" t="n">
@@ -2132,13 +2139,13 @@
       <c r="P3" s="2" t="n">
         <v>2.82</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>31</v>
       </c>
       <c r="R3" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="2" t="n">
         <v>26645</v>
       </c>
       <c r="T3" t="n">
@@ -2151,7 +2158,7 @@
           <t>SHREECEM</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>8.370767521615225</v>
       </c>
       <c r="C4" t="n">
@@ -2172,16 +2179,16 @@
       <c r="H4" t="n">
         <v>0.7348612354521038</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>1929</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="2" t="n">
         <v>14.80997180241832</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="2" t="n">
         <v>10.32561591555659</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>11.2926552609119</v>
       </c>
       <c r="M4" t="n">
@@ -2196,13 +2203,13 @@
       <c r="P4" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="2" t="n">
         <v>16</v>
       </c>
       <c r="R4" t="n">
         <v>3154358.33</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="2" t="n">
         <v>20521</v>
       </c>
       <c r="T4" t="n">
@@ -2215,7 +2222,7 @@
           <t>BANKBARODA</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="2" t="n">
         <v>15.7618637908999</v>
       </c>
       <c r="C5" t="n">
@@ -2236,16 +2243,16 @@
       <c r="H5" t="n">
         <v>0.07153782236255685</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>-7559</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="2" t="n">
         <v>16.78883948962531</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="2" t="n">
         <v>17.47729766589094</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="2" t="n">
         <v>74.50588066551305</v>
       </c>
       <c r="M5" t="n">
@@ -2260,13 +2267,13 @@
       <c r="P5" s="2" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="2" t="n">
         <v>21</v>
       </c>
       <c r="R5" t="n">
         <v>590971.02</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="2" t="n">
         <v>118379</v>
       </c>
       <c r="T5" t="n">
@@ -2279,7 +2286,7 @@
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>14.25227319776422</v>
       </c>
       <c r="C6" t="n">
@@ -2300,16 +2307,16 @@
       <c r="H6" t="n">
         <v>0.08884228106460039</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>-17468</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="2" t="n">
         <v>16.41029009859514</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="2" t="n">
         <v>15.49561308335803</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="2" t="n">
         <v>22.07746495394836</v>
       </c>
       <c r="M6" t="n">
@@ -2324,13 +2331,13 @@
       <c r="P6" s="2" t="n">
         <v>1.42</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="2" t="n">
         <v>14</v>
       </c>
       <c r="R6" t="n">
         <v>1807433.12</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="T6" t="n">
@@ -2343,7 +2350,7 @@
           <t>MOTHERSON</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>11.54654941693749</v>
       </c>
       <c r="C7" t="n">
@@ -2364,16 +2371,16 @@
       <c r="H7" t="n">
         <v>1.172420347359167</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="2" t="n">
         <v>925</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="2" t="n">
         <v>19.82084189180693</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>9.211957132942761</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>7.557399109099472</v>
       </c>
       <c r="M7" t="n">
@@ -2388,13 +2395,13 @@
       <c r="P7" s="2" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="2" t="n">
         <v>20</v>
       </c>
       <c r="R7" t="n">
         <v>146151.16</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="2" t="n">
         <v>98692</v>
       </c>
       <c r="T7" t="n">
@@ -2407,7 +2414,7 @@
           <t>M&amp;M</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2" t="n">
         <v>18.53754343556428</v>
       </c>
       <c r="C8" t="n">
@@ -2428,16 +2435,16 @@
       <c r="H8" t="n">
         <v>0.5925222177725139</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>-11245</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="2" t="n">
         <v>23.2535428740343</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>5.838805854237616</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>15.31688706104797</v>
       </c>
       <c r="M8" t="n">
@@ -2452,13 +2459,13 @@
       <c r="P8" s="2" t="n">
         <v>2.37</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="2" t="n">
         <v>21</v>
       </c>
       <c r="R8" t="n">
         <v>4173085.48</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="2" t="n">
         <v>139078</v>
       </c>
       <c r="T8" t="n">
@@ -2609,7 +2616,7 @@
           <t>IRCTC</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>34.39628482972136</v>
       </c>
       <c r="C2" t="n">
@@ -2630,10 +2637,10 @@
       <c r="H2" t="n">
         <v>0.7010343129207027</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>667</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>76.46921430165466</v>
       </c>
       <c r="K2" s="2" t="n">
@@ -2645,22 +2652,22 @@
       <c r="M2" t="n">
         <v>28.47351571234393</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>60.44</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="3" t="n">
         <v>5.74</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>47</v>
       </c>
       <c r="R2" t="n">
         <v>1258520.29</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="3" t="n">
         <v>4270</v>
       </c>
       <c r="T2" t="n">
@@ -2673,7 +2680,7 @@
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="2" t="n">
         <v>36.30776794493609</v>
       </c>
       <c r="C3" t="n">
@@ -2694,10 +2701,10 @@
       <c r="H3" t="n">
         <v>1.727869310248534</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>68.36335197744833</v>
       </c>
       <c r="K3" s="2" t="n">
@@ -2709,22 +2716,22 @@
       <c r="M3" t="n">
         <v>69.52182030724354</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="2" t="n">
         <v>8.65</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="3" t="n">
         <v>11.82</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="2" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>8</v>
       </c>
       <c r="R3" t="n">
         <v>571322.04</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="2" t="n">
         <v>12375</v>
       </c>
       <c r="T3" t="n">
@@ -2752,10 +2759,10 @@
       <c r="H4" t="n">
         <v>56.38625204582652</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>9424</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="2" t="n">
         <v>67.58091776468258</v>
       </c>
       <c r="K4" s="2" t="n">
@@ -2767,22 +2774,22 @@
       <c r="M4" t="n">
         <v>121.2356822276117</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>76.23</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>7.87</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="2" t="n">
         <v>4.27</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="2" t="n">
         <v>68904</v>
       </c>
       <c r="T4" t="n">
@@ -2795,7 +2802,7 @@
           <t>LTIM</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="2" t="n">
         <v>22.9043860525527</v>
       </c>
       <c r="C5" t="n">
@@ -2816,10 +2823,10 @@
       <c r="H5" t="n">
         <v>1.289464130119082</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>1752</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="2" t="n">
         <v>42.13101535214459</v>
       </c>
       <c r="K5" s="2" t="n">
@@ -2831,22 +2838,22 @@
       <c r="M5" t="n">
         <v>12.24383304425547</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>64.52</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="2" t="n">
         <v>2.38</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="2" t="n">
         <v>4.43</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="2" t="n">
         <v>42</v>
       </c>
       <c r="R5" t="n">
         <v>1347046.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="2" t="n">
         <v>35517</v>
       </c>
       <c r="T5" t="n">
@@ -2859,7 +2866,7 @@
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="2" t="n">
         <v>17.99027109750765</v>
       </c>
       <c r="C6" t="n">
@@ -2880,10 +2887,10 @@
       <c r="H6" t="n">
         <v>0.06747535915921023</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="2" t="n">
         <v>12547</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="2" t="n">
         <v>21.39660074377121</v>
       </c>
       <c r="K6" s="2" t="n">
@@ -2895,22 +2902,22 @@
       <c r="M6" t="n">
         <v>55.18455739153598</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="2" t="n">
         <v>25.76</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="2" t="n">
         <v>3.43</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="2" t="n">
         <v>16</v>
       </c>
       <c r="R6" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="2" t="n">
         <v>159516</v>
       </c>
       <c r="T6" t="n">
@@ -2923,7 +2930,7 @@
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="2" t="n">
         <v>37.2192057915469</v>
       </c>
       <c r="C7" t="n">
@@ -2944,10 +2951,10 @@
       <c r="H7" t="n">
         <v>1.619298190002219</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="2" t="n">
         <v>1506</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="2" t="n">
         <v>33.14221885428872</v>
       </c>
       <c r="K7" s="2" t="n">
@@ -2959,22 +2966,22 @@
       <c r="M7" t="n">
         <v>19.50578386760935</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="2" t="n">
         <v>10.13</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3" t="n">
         <v>10.51</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="2" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="2" t="n">
         <v>28</v>
       </c>
       <c r="R7" t="n">
         <v>1793769.72</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="2" t="n">
         <v>51084</v>
       </c>
       <c r="T7" t="n">
@@ -2987,7 +2994,7 @@
           <t>ATGL</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2" t="n">
         <v>18.65921787709497</v>
       </c>
       <c r="C8" t="n">
@@ -3008,10 +3015,10 @@
       <c r="H8" t="n">
         <v>0.6788531553398058</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="2" t="n">
         <v>38.18335427451367</v>
       </c>
       <c r="K8" s="2" t="n">
@@ -3023,22 +3030,22 @@
       <c r="M8" t="n">
         <v>24.57309396155174</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="n">
         <v>56.96</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="3" t="n">
         <v>5.76</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="R8" t="n">
         <v>1535602.41</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="3" t="n">
         <v>4475</v>
       </c>
       <c r="T8" t="n">
@@ -3051,7 +3058,7 @@
           <t>DMART</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>13.56294790886726</v>
       </c>
       <c r="C9" t="n">
@@ -3072,10 +3079,10 @@
       <c r="H9" t="n">
         <v>2.398875873795579</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="2" t="n">
         <v>278</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="2" t="n">
         <v>28.1325519519273</v>
       </c>
       <c r="K9" s="2" t="n">
@@ -3087,22 +3094,22 @@
       <c r="M9" t="n">
         <v>22.74033782145131</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>72.53</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="3" t="n">
         <v>11.71</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="2" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>3053088.97</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="2" t="n">
         <v>50789</v>
       </c>
       <c r="T9" t="n">
@@ -3115,7 +3122,7 @@
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>14.33974005030719</v>
       </c>
       <c r="C10" t="n">
@@ -3136,10 +3143,10 @@
       <c r="H10" t="n">
         <v>0.07038097917866981</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="2" t="n">
         <v>35669</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="2" t="n">
         <v>30.18695614094877</v>
       </c>
       <c r="K10" s="2" t="n">
@@ -3151,22 +3158,22 @@
       <c r="M10" t="n">
         <v>15.42478808253083</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>49.42</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="2" t="n">
         <v>23</v>
       </c>
       <c r="R10" t="n">
         <v>808359.03</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="2" t="n">
         <v>283649</v>
       </c>
       <c r="T10" t="n">
@@ -3179,7 +3186,7 @@
           <t>CANBK</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="2" t="n">
         <v>16.71605179468811</v>
       </c>
       <c r="C11" t="n">
@@ -3200,10 +3207,10 @@
       <c r="H11" t="n">
         <v>0.0719985042520674</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="2" t="n">
         <v>13296</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="2" t="n">
         <v>16.30293930023252</v>
       </c>
       <c r="K11" s="2" t="n">
@@ -3215,22 +3222,22 @@
       <c r="M11" t="n">
         <v>53.4206382524911</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3" t="n">
         <v>36.74</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="3" t="n">
         <v>12.61</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="2" t="n">
         <v>3.81</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="2" t="n">
         <v>19</v>
       </c>
       <c r="R11" t="n">
         <v>496415.88</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="2" t="n">
         <v>110519</v>
       </c>
       <c r="T11" t="n">
@@ -3240,193 +3247,193 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IRFC</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>13.0380853616381</v>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>8.534650424813185</v>
       </c>
       <c r="C12" t="n">
-        <v>1.390231951051347</v>
+        <v>4.719023623857606</v>
       </c>
       <c r="D12" t="n">
-        <v>24.0645524488647</v>
+        <v>3.458790097592848</v>
       </c>
       <c r="E12" t="n">
-        <v>99.50459748545694</v>
+        <v>11.79929683367731</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>8.378352548852153</v>
+        <v>1.671358378544375</v>
       </c>
       <c r="G12" t="n">
-        <v>1.31948659270683</v>
+        <v>2.749286498353458</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05492885738906</v>
-      </c>
-      <c r="I12" t="n">
-        <v>7906</v>
-      </c>
-      <c r="J12" t="n">
-        <v>19.10193873049559</v>
+        <v>0.6004321671876751</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>-8455</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>34.60338228109774</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>19.06740855567788</v>
+        <v>19.01541475308124</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>23.24502393394037</v>
+        <v>45.81058899665285</v>
       </c>
       <c r="M12" t="n">
-        <v>20.11244339814313</v>
-      </c>
-      <c r="N12" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>31</v>
+        <v>31.95079107728942</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>2618348.58</v>
-      </c>
-      <c r="S12" t="n">
-        <v>26645</v>
+        <v>187927.97</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>96421</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7068962147807</v>
+        <v>45.53113716311739</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>7.566793298872766</v>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>13.0380853616381</v>
       </c>
       <c r="C13" t="n">
-        <v>8.682297532507423</v>
+        <v>1.390231951051347</v>
       </c>
       <c r="D13" t="n">
-        <v>7.990266999868473</v>
+        <v>24.0645524488647</v>
       </c>
       <c r="E13" t="n">
-        <v>15.02038668946468</v>
+        <v>99.50459748545694</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.21654107242947</v>
+        <v>8.378352548852153</v>
       </c>
       <c r="G13" t="n">
-        <v>25.32183908045977</v>
+        <v>1.31948659270683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5454284586965099</v>
-      </c>
-      <c r="I13" t="n">
-        <v>26</v>
-      </c>
-      <c r="J13" t="n">
-        <v>9.436125385661253</v>
+        <v>0.05492885738906</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>7906</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>19.10193873049559</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>15.96086282879563</v>
+        <v>19.06740855567788</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>21.59956338772886</v>
+        <v>23.24502393394037</v>
       </c>
       <c r="M13" t="n">
-        <v>14.86983549970351</v>
-      </c>
-      <c r="N13" t="n">
-        <v>54.79</v>
-      </c>
-      <c r="O13" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>64</v>
+        <v>20.11244339814313</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>31</v>
       </c>
       <c r="R13" t="n">
-        <v>350543.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>15206</v>
+        <v>2618348.58</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>26645</v>
       </c>
       <c r="T13" t="n">
-        <v>43.51633606444935</v>
+        <v>43.7068962147807</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>8.534650424813185</v>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>7.566793298872766</v>
       </c>
       <c r="C14" t="n">
-        <v>4.719023623857606</v>
+        <v>8.682297532507423</v>
       </c>
       <c r="D14" t="n">
-        <v>3.458790097592848</v>
+        <v>7.990266999868473</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79929683367731</v>
+        <v>15.02038668946468</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.671358378544375</v>
+        <v>0.21654107242947</v>
       </c>
       <c r="G14" t="n">
-        <v>2.749286498353458</v>
+        <v>25.32183908045977</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6004321671876751</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-8455</v>
-      </c>
-      <c r="J14" t="n">
-        <v>34.60338228109774</v>
+        <v>0.5454284586965099</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>9.436125385661253</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>19.01541475308124</v>
+        <v>15.96086282879563</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>45.81058899665285</v>
+        <v>21.59956338772886</v>
       </c>
       <c r="M14" t="n">
-        <v>31.95079107728942</v>
-      </c>
-      <c r="N14" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="O14" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5</v>
+        <v>14.86983549970351</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>64</v>
       </c>
       <c r="R14" t="n">
-        <v>187927.97</v>
-      </c>
-      <c r="S14" t="n">
-        <v>96421</v>
+        <v>350543.35</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>15206</v>
       </c>
       <c r="T14" t="n">
-        <v>43.08380814902782</v>
+        <v>43.51633606444935</v>
       </c>
     </row>
     <row r="15">
@@ -3435,7 +3442,7 @@
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="2" t="n">
         <v>18.8419213518306</v>
       </c>
       <c r="C15" t="n">
@@ -3456,10 +3463,10 @@
       <c r="H15" t="n">
         <v>0.1463025160881669</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="3" t="n">
         <v>-79931</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="2" t="n">
         <v>27.25940575809531</v>
       </c>
       <c r="K15" s="2" t="n">
@@ -3471,22 +3478,22 @@
       <c r="M15" t="n">
         <v>27.5561392815338</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15" s="3" t="n">
         <v>69.2</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" s="2" t="n">
         <v>4.11</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="3" t="n">
         <v>0.27</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="2" t="n">
         <v>15</v>
       </c>
       <c r="R15" t="n">
         <v>2473271.58</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="2" t="n">
         <v>54972</v>
       </c>
       <c r="T15" t="n">
@@ -3499,7 +3506,7 @@
           <t>BAJAJFINSV</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="2" t="n">
         <v>25.85035141227954</v>
       </c>
       <c r="C16" t="n">
@@ -3520,10 +3527,10 @@
       <c r="H16" t="n">
         <v>0.2053943414307379</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="3" t="n">
         <v>-79634</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="2" t="n">
         <v>22.13149041552844</v>
       </c>
       <c r="K16" s="2" t="n">
@@ -3535,22 +3542,22 @@
       <c r="M16" t="n">
         <v>20.58909506066124</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16" s="2" t="n">
         <v>15.07</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" s="3" t="n">
         <v>6.08</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="2" t="n">
         <v>2.56</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" s="2" t="n">
         <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>1905112.17</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16" s="2" t="n">
         <v>110382</v>
       </c>
       <c r="T16" t="n">
@@ -3563,7 +3570,7 @@
           <t>BANKBARODA</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="2" t="n">
         <v>15.7618637908999</v>
       </c>
       <c r="C17" t="n">
@@ -3584,10 +3591,10 @@
       <c r="H17" t="n">
         <v>0.07153782236255685</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="3" t="n">
         <v>-7559</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="2" t="n">
         <v>16.78883948962531</v>
       </c>
       <c r="K17" s="2" t="n">
@@ -3599,22 +3606,22 @@
       <c r="M17" t="n">
         <v>55.18455739153598</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17" s="2" t="n">
         <v>16.89</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17" s="2" t="n">
         <v>4.15</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="2" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="2" t="n">
         <v>21</v>
       </c>
       <c r="R17" t="n">
         <v>590971.02</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17" s="2" t="n">
         <v>118379</v>
       </c>
       <c r="T17" t="n">
@@ -3627,7 +3634,7 @@
           <t>SHRIRAMFIN</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="2" t="n">
         <v>15.11635033812082</v>
       </c>
       <c r="C18" t="n">
@@ -3648,10 +3655,10 @@
       <c r="H18" t="n">
         <v>0.1465685998082702</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="3" t="n">
         <v>-31359</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="2" t="n">
         <v>27.82625310142639</v>
       </c>
       <c r="K18" s="2" t="n">
@@ -3663,22 +3670,22 @@
       <c r="M18" t="n">
         <v>14.28965514115608</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="3" t="n">
         <v>68.53</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="3" t="n">
         <v>7.91</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18" s="2" t="n">
         <v>23</v>
       </c>
       <c r="R18" t="n">
         <v>868933.47</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="2" t="n">
         <v>36388</v>
       </c>
       <c r="T18" t="n">
@@ -3691,7 +3698,7 @@
           <t>CHOLAFIN</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="2" t="n">
         <v>17.45521359669269</v>
       </c>
       <c r="C19" t="n">
@@ -3712,10 +3719,10 @@
       <c r="H19" t="n">
         <v>0.1223019286981607</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="3" t="n">
         <v>-38538</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="2" t="n">
         <v>25.98553091668698</v>
       </c>
       <c r="K19" s="2" t="n">
@@ -3727,22 +3734,22 @@
       <c r="M19" t="n">
         <v>22.27523876455795</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19" s="2" t="n">
         <v>16.79</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" s="3" t="n">
         <v>10.36</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" s="2" t="n">
         <v>2.83</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19" s="2" t="n">
         <v>5</v>
       </c>
       <c r="R19" t="n">
         <v>971931.96</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S19" s="2" t="n">
         <v>19163</v>
       </c>
       <c r="T19" t="n">
@@ -3755,7 +3762,7 @@
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>14.25227319776422</v>
       </c>
       <c r="C20" t="n">
@@ -3776,10 +3783,10 @@
       <c r="H20" t="n">
         <v>0.08884228106460039</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="3" t="n">
         <v>-17468</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="2" t="n">
         <v>16.41029009859514</v>
       </c>
       <c r="K20" s="2" t="n">
@@ -3791,22 +3798,22 @@
       <c r="M20" t="n">
         <v>15.89562187541786</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="2" t="n">
         <v>8.99</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20" s="2" t="n">
         <v>1.42</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20" s="2" t="n">
         <v>14</v>
       </c>
       <c r="R20" t="n">
         <v>1807433.12</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S20" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="T20" t="n">
@@ -3957,7 +3964,7 @@
           <t>ASIANPAINT</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>29.67748825288338</v>
       </c>
       <c r="C2" t="n">
@@ -3981,22 +3988,22 @@
       <c r="I2" s="2" t="n">
         <v>3556</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>17.80103767695105</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>13.02966034945308</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>20.27736210195506</v>
       </c>
       <c r="M2" t="n">
         <v>20.97355268843126</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>73.37</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="2" t="n">
         <v>3.9</v>
       </c>
       <c r="P2" s="2" t="n">
@@ -4008,7 +4015,7 @@
       <c r="R2" t="n">
         <v>2126725.18</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="2" t="n">
         <v>35495</v>
       </c>
       <c r="T2" t="n">
@@ -4039,22 +4046,22 @@
       <c r="I3" s="2" t="n">
         <v>1814</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>9.909701355201484</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>8.712548590236358</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="2" t="n">
         <v>26.48527056305299</v>
       </c>
       <c r="M3" t="n">
         <v>26.63896760913802</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="n">
         <v>71.89</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="2" t="n">
         <v>3.65</v>
       </c>
       <c r="P3" s="2" t="n">
@@ -4066,11 +4073,11 @@
       <c r="R3" t="n">
         <v>2643616.86</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="2" t="n">
         <v>30381</v>
       </c>
       <c r="T3" t="n">
-        <v>80.11686765708708</v>
+        <v>80.30328785369947</v>
       </c>
     </row>
     <row r="4">
@@ -4079,7 +4086,7 @@
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="2" t="n">
         <v>117.7544910179641</v>
       </c>
       <c r="C4" t="n">
@@ -4103,22 +4110,22 @@
       <c r="I4" s="2" t="n">
         <v>2938</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="2" t="n">
         <v>18.28200866249903</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="2" t="n">
         <v>14.54857371180267</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>14.85231951299384</v>
       </c>
       <c r="M4" t="n">
         <v>15.43852585822143</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>54.96</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>14.34</v>
       </c>
       <c r="P4" s="2" t="n">
@@ -4130,7 +4137,7 @@
       <c r="R4" t="n">
         <v>1677775.19</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="2" t="n">
         <v>24394</v>
       </c>
       <c r="T4" t="n">
@@ -4143,7 +4150,7 @@
           <t>BAJAJHLDNG</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>13.57678765646027</v>
       </c>
       <c r="C5" t="n">
@@ -4167,22 +4174,22 @@
       <c r="I5" s="2" t="n">
         <v>1469</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="2" t="n">
         <v>55.00574158769729</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="2" t="n">
         <v>31.61229344896917</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>19.2975590637313</v>
       </c>
       <c r="M5" t="n">
         <v>18.96864732798973</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>37.73</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="3" t="n">
         <v>9.380000000000001</v>
       </c>
       <c r="P5" s="2" t="n">
@@ -4194,7 +4201,7 @@
       <c r="R5" t="n">
         <v>2191568.13</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="3" t="n">
         <v>1702</v>
       </c>
       <c r="T5" t="n">
@@ -4207,7 +4214,7 @@
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="2" t="n">
         <v>36.30776794493609</v>
       </c>
       <c r="C6" t="n">
@@ -4231,22 +4238,22 @@
       <c r="I6" s="2" t="n">
         <v>841</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="2" t="n">
         <v>68.36335197744833</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="2" t="n">
         <v>36.30691600183056</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="2" t="n">
         <v>73.11367578503176</v>
       </c>
       <c r="M6" t="n">
         <v>69.52182030724354</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="2" t="n">
         <v>8.65</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="3" t="n">
         <v>11.82</v>
       </c>
       <c r="P6" s="2" t="n">
@@ -4258,7 +4265,7 @@
       <c r="R6" t="n">
         <v>571322.04</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="2" t="n">
         <v>12375</v>
       </c>
       <c r="T6" t="n">
@@ -4289,22 +4296,22 @@
       <c r="I7" s="2" t="n">
         <v>9424</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="2" t="n">
         <v>67.58091776468258</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="2" t="n">
         <v>19.31335512580617</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="2" t="n">
         <v>120.6925086746793</v>
       </c>
       <c r="M7" t="n">
         <v>121.2356822276117</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="n">
         <v>76.23</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3" t="n">
         <v>7.87</v>
       </c>
       <c r="P7" s="2" t="n">
@@ -4316,7 +4323,7 @@
       <c r="R7" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="2" t="n">
         <v>68904</v>
       </c>
       <c r="T7" t="n">
@@ -4329,7 +4336,7 @@
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="2" t="n">
         <v>45.16982956605826</v>
       </c>
       <c r="C8" t="n">
@@ -4353,22 +4360,22 @@
       <c r="I8" s="2" t="n">
         <v>13617</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="2" t="n">
         <v>16.49395652851666</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="3" t="n">
         <v>7.402890725901301</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>16.43231987118112</v>
       </c>
       <c r="M8" t="n">
         <v>16.85151856943003</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="n">
         <v>34.27</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="3" t="n">
         <v>14.75</v>
       </c>
       <c r="P8" s="2" t="n">
@@ -4380,7 +4387,7 @@
       <c r="R8" t="n">
         <v>454024.84</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="2" t="n">
         <v>142324</v>
       </c>
       <c r="T8" t="n">
@@ -4393,7 +4400,7 @@
           <t>LICI</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="2" t="n">
         <v>49.44710986501021</v>
       </c>
       <c r="C9" t="n">
@@ -4417,19 +4424,19 @@
       <c r="I9" s="2" t="n">
         <v>853</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="3" t="n">
         <v>6.981735429882496</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>8.15986061977938</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="2" t="n">
         <v>73.17556747076097</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="3" t="n">
         <v>30.67</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="P9" s="2" t="n">
@@ -4441,7 +4448,7 @@
       <c r="R9" t="n">
         <v>183583.67</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="2" t="n">
         <v>845966</v>
       </c>
       <c r="T9" t="n">
@@ -4454,7 +4461,7 @@
           <t>BAJAJ-AUTO</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="2" t="n">
         <v>26.61418410330778</v>
       </c>
       <c r="C10" t="n">
@@ -4478,22 +4485,22 @@
       <c r="I10" s="2" t="n">
         <v>6486</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="2" t="n">
         <v>17.38465261667195</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>8.127604751021389</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="3" t="n">
         <v>9.358917170384974</v>
       </c>
       <c r="M10" t="n">
         <v>10.17727634846559</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="2" t="n">
         <v>29.91</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="3" t="n">
         <v>9.83</v>
       </c>
       <c r="P10" s="2" t="n">
@@ -4505,7 +4512,7 @@
       <c r="R10" t="n">
         <v>653817.3</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="2" t="n">
         <v>44870</v>
       </c>
       <c r="T10" t="n">
@@ -4518,7 +4525,7 @@
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="2" t="n">
         <v>15.7230643179025</v>
       </c>
       <c r="C11" t="n">
@@ -4542,22 +4549,22 @@
       <c r="I11" s="2" t="n">
         <v>486</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="2" t="n">
         <v>18.98796206427069</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="2" t="n">
         <v>12.91184100336258</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>12.83917371819816</v>
       </c>
       <c r="M11" t="n">
         <v>11.1392224868865</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="3" t="n">
         <v>7.86</v>
       </c>
       <c r="P11" s="2" t="n">
@@ -4569,7 +4576,7 @@
       <c r="R11" t="n">
         <v>1271789.21</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="2" t="n">
         <v>20487</v>
       </c>
       <c r="T11" t="n">
@@ -4579,367 +4586,367 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.153456416595399</v>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>17.06727541291795</v>
       </c>
       <c r="C12" t="n">
-        <v>1.405707632934954</v>
+        <v>22.0258064516129</v>
       </c>
       <c r="D12" t="n">
-        <v>86.52291105121293</v>
+        <v>6.837009144701453</v>
       </c>
       <c r="E12" t="n">
-        <v>84.04312668463612</v>
+        <v>10.11834319526627</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.040687525177924</v>
       </c>
       <c r="G12" t="n">
-        <v>198.8</v>
+        <v>25.35714285714286</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0128052021565203</v>
+        <v>1.495214348910158</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>763</v>
-      </c>
-      <c r="N12" t="n">
-        <v>34.24</v>
-      </c>
-      <c r="O12" t="n">
-        <v>9.91</v>
+        <v>335</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>21.14089015706202</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>13.03790793906312</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>10.03323122942004</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8.997698704834534</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>14.08</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>3.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R12" t="n">
-        <v>1401774.99</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1855</v>
+        <v>2521508.87</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>18590</v>
       </c>
       <c r="T12" t="n">
-        <v>55.30519904723734</v>
+        <v>58.15011682984635</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LTIM</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>22.9043860525527</v>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>1.153456416595399</v>
       </c>
       <c r="C13" t="n">
-        <v>27.38467110326407</v>
+        <v>1.405707632934954</v>
       </c>
       <c r="D13" t="n">
-        <v>12.90931103415266</v>
+        <v>86.52291105121293</v>
       </c>
       <c r="E13" t="n">
-        <v>17.98293774812062</v>
+        <v>84.04312668463612</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1034568888000799</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>31.93243243243243</v>
+        <v>198.8</v>
       </c>
       <c r="H13" t="n">
-        <v>1.289464130119082</v>
+        <v>0.0128052021565203</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1752</v>
-      </c>
-      <c r="J13" t="n">
-        <v>42.13101535214459</v>
-      </c>
-      <c r="K13" t="n">
-        <v>30.32798083513346</v>
-      </c>
-      <c r="L13" t="n">
-        <v>24.775129058601</v>
-      </c>
-      <c r="M13" t="n">
-        <v>12.24383304425547</v>
-      </c>
-      <c r="N13" t="n">
-        <v>64.52</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.38</v>
+        <v>763</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>9.91</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>4.43</v>
+        <v>3.09</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1347046.9</v>
-      </c>
-      <c r="S13" t="n">
-        <v>35517</v>
+        <v>1401774.99</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>1855</v>
       </c>
       <c r="T13" t="n">
-        <v>54.82910568425711</v>
+        <v>55.30519904723734</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>17.99027109750765</v>
+          <t>LTIM</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>22.9043860525527</v>
       </c>
       <c r="C14" t="n">
-        <v>3.168808778744431</v>
+        <v>27.38467110326407</v>
       </c>
       <c r="D14" t="n">
-        <v>28.8880112339828</v>
+        <v>12.90931103415266</v>
       </c>
       <c r="E14" t="n">
-        <v>62.41380175029464</v>
+        <v>17.98293774812062</v>
       </c>
       <c r="F14" t="n">
-        <v>6.445624336310825</v>
+        <v>0.1034568888000799</v>
       </c>
       <c r="G14" t="n">
-        <v>1.300946133138182</v>
+        <v>31.93243243243243</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06747535915921023</v>
+        <v>1.289464130119082</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>12547</v>
-      </c>
-      <c r="J14" t="n">
-        <v>21.39660074377121</v>
-      </c>
-      <c r="K14" t="n">
-        <v>17.25086850260209</v>
-      </c>
-      <c r="L14" t="n">
-        <v>51.94877118224903</v>
+        <v>1752</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>42.13101535214459</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>30.32798083513346</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>24.775129058601</v>
       </c>
       <c r="M14" t="n">
-        <v>55.18455739153598</v>
-      </c>
-      <c r="N14" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="O14" t="n">
-        <v>6.2</v>
+        <v>12.24383304425547</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>2.38</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>3.43</v>
+        <v>4.43</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="R14" t="n">
-        <v>1319221.86</v>
-      </c>
-      <c r="S14" t="n">
-        <v>159516</v>
+        <v>1347046.9</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>35517</v>
       </c>
       <c r="T14" t="n">
-        <v>54.25483366558786</v>
+        <v>54.82910568425711</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>22.17234691050152</v>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>17.99027109750765</v>
       </c>
       <c r="C15" t="n">
-        <v>28.17374350086655</v>
+        <v>3.168808778744431</v>
       </c>
       <c r="D15" t="n">
-        <v>24.19569424286405</v>
+        <v>28.8880112339828</v>
       </c>
       <c r="E15" t="n">
-        <v>26.17924528301887</v>
+        <v>62.41380175029464</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02321972845663619</v>
+        <v>6.445624336310825</v>
       </c>
       <c r="G15" t="n">
-        <v>114.7058823529412</v>
+        <v>1.300946133138182</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7153796236210254</v>
+        <v>0.06747535915921023</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>890</v>
-      </c>
-      <c r="J15" t="n">
-        <v>23.776441520116</v>
-      </c>
-      <c r="K15" t="n">
-        <v>11.03693649673969</v>
-      </c>
-      <c r="L15" t="n">
-        <v>12.6758416653777</v>
+        <v>12547</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>21.39660074377121</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>17.25086850260209</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>51.94877118224903</v>
       </c>
       <c r="M15" t="n">
-        <v>12.50545162905032</v>
-      </c>
-      <c r="N15" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="O15" t="n">
-        <v>13.61</v>
+        <v>55.18455739153598</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>4.41</v>
+        <v>3.43</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="R15" t="n">
-        <v>222391.83</v>
-      </c>
-      <c r="S15" t="n">
-        <v>16536</v>
+        <v>1319221.86</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>159516</v>
       </c>
       <c r="T15" t="n">
-        <v>52.44066966339204</v>
+        <v>54.25483366558786</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>37.45613415294755</v>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>22.17234691050152</v>
       </c>
       <c r="C16" t="n">
-        <v>14.54625871578728</v>
+        <v>28.17374350086655</v>
       </c>
       <c r="D16" t="n">
-        <v>7.263066074788551</v>
+        <v>24.19569424286405</v>
       </c>
       <c r="E16" t="n">
-        <v>13.59538554282896</v>
+        <v>26.17924528301887</v>
       </c>
       <c r="F16" t="n">
-        <v>1.263124425916767</v>
+        <v>0.02321972845663619</v>
       </c>
       <c r="G16" t="n">
-        <v>6.530242339274985</v>
+        <v>114.7058823529412</v>
       </c>
       <c r="H16" t="n">
-        <v>1.185123443593192</v>
+        <v>0.7153796236210254</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45133</v>
-      </c>
-      <c r="J16" t="n">
-        <v>20.57936456937097</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7.720159538623927</v>
-      </c>
-      <c r="N16" t="n">
-        <v>67.06999999999999</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.93</v>
+        <v>890</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>23.776441520116</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>11.03693649673969</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>12.6758416653777</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12.50545162905032</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>13.61</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>3.65</v>
+        <v>4.41</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="R16" t="n">
-        <v>1504106.64</v>
-      </c>
-      <c r="S16" t="n">
-        <v>437928</v>
+        <v>222391.83</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>16536</v>
       </c>
       <c r="T16" t="n">
-        <v>51.6052090535713</v>
+        <v>52.44066966339204</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>15.09416181067115</v>
+          <t>TATAMOTORS</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>37.45613415294755</v>
       </c>
       <c r="C17" t="n">
-        <v>16.56383979922618</v>
+        <v>14.54625871578728</v>
       </c>
       <c r="D17" t="n">
-        <v>19.81565870053818</v>
+        <v>7.263066074788551</v>
       </c>
       <c r="E17" t="n">
-        <v>26.84289749881436</v>
+        <v>13.59538554282896</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05142381453500244</v>
+        <v>1.263124425916767</v>
       </c>
       <c r="G17" t="n">
-        <v>58.33193277310924</v>
+        <v>6.530242339274985</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5684929901064378</v>
+        <v>1.185123443593192</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>11372</v>
-      </c>
-      <c r="J17" t="n">
-        <v>13.12675558948349</v>
-      </c>
-      <c r="K17" t="n">
-        <v>10.78116321985565</v>
-      </c>
-      <c r="L17" t="n">
-        <v>24.53682964293125</v>
-      </c>
-      <c r="M17" t="n">
-        <v>29.45936165164078</v>
-      </c>
-      <c r="N17" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>6.71</v>
+        <v>45133</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>20.57936456937097</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>7.720159538623927</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>67.06999999999999</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.93</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1339586.09</v>
-      </c>
-      <c r="S17" t="n">
-        <v>48497</v>
+        <v>1504106.64</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>437928</v>
       </c>
       <c r="T17" t="n">
-        <v>51.37713526020612</v>
+        <v>51.6052090535713</v>
       </c>
     </row>
     <row r="18">
@@ -4948,7 +4955,7 @@
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="2" t="n">
         <v>37.2192057915469</v>
       </c>
       <c r="C18" t="n">
@@ -4972,22 +4979,22 @@
       <c r="I18" s="2" t="n">
         <v>1506</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="2" t="n">
         <v>33.14221885428872</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="2" t="n">
         <v>20.89716395312024</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18" s="2" t="n">
         <v>20.27457629679304</v>
       </c>
       <c r="M18" t="n">
         <v>19.50578386760935</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18" s="2" t="n">
         <v>10.13</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" s="3" t="n">
         <v>10.51</v>
       </c>
       <c r="P18" s="2" t="n">
@@ -4999,7 +5006,7 @@
       <c r="R18" t="n">
         <v>1793769.72</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18" s="2" t="n">
         <v>51084</v>
       </c>
       <c r="T18" t="n">
@@ -5009,65 +5016,65 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>17.06727541291795</v>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>15.09416181067115</v>
       </c>
       <c r="C19" t="n">
-        <v>22.0258064516129</v>
+        <v>16.56383979922618</v>
       </c>
       <c r="D19" t="n">
-        <v>6.837009144701453</v>
+        <v>19.81565870053818</v>
       </c>
       <c r="E19" t="n">
-        <v>10.11834319526627</v>
+        <v>26.84289749881436</v>
       </c>
       <c r="F19" t="n">
-        <v>0.040687525177924</v>
+        <v>0.05142381453500244</v>
       </c>
       <c r="G19" t="n">
-        <v>25.35714285714286</v>
+        <v>58.33193277310924</v>
       </c>
       <c r="H19" t="n">
-        <v>1.495214348910158</v>
+        <v>0.5684929901064378</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>335</v>
-      </c>
-      <c r="J19" t="n">
-        <v>21.14089015706202</v>
-      </c>
-      <c r="K19" t="n">
-        <v>13.03790793906312</v>
-      </c>
-      <c r="L19" t="n">
-        <v>10.03323122942004</v>
+        <v>11372</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>13.12675558948349</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>10.78116321985565</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>24.53682964293125</v>
       </c>
       <c r="M19" t="n">
-        <v>8.997698704834534</v>
-      </c>
-      <c r="N19" t="n">
-        <v>45.41</v>
-      </c>
-      <c r="O19" t="n">
-        <v>14.08</v>
+        <v>29.45936165164078</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>6.71</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>2.6</v>
+        <v>3.88</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="R19" t="n">
-        <v>2521508.87</v>
-      </c>
-      <c r="S19" t="n">
-        <v>18590</v>
+        <v>1339586.09</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>48497</v>
       </c>
       <c r="T19" t="n">
-        <v>48.75439737462181</v>
+        <v>47.85970653156618</v>
       </c>
     </row>
     <row r="20">
@@ -5076,7 +5083,7 @@
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>14.33974005030719</v>
       </c>
       <c r="C20" t="n">
@@ -5100,22 +5107,22 @@
       <c r="I20" s="2" t="n">
         <v>35669</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" s="2" t="n">
         <v>30.18695614094877</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20" s="2" t="n">
         <v>21.95098428169122</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20" s="2" t="n">
         <v>23.86506357287907</v>
       </c>
       <c r="M20" t="n">
         <v>15.42478808253083</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20" s="3" t="n">
         <v>49.42</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" s="2" t="n">
         <v>4.4</v>
       </c>
       <c r="P20" s="2" t="n">
@@ -5127,7 +5134,7 @@
       <c r="R20" t="n">
         <v>808359.03</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S20" s="2" t="n">
         <v>283649</v>
       </c>
       <c r="T20" t="n">
@@ -5140,7 +5147,7 @@
           <t>POWERGRID</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="2" t="n">
         <v>17.87001124549607</v>
       </c>
       <c r="C21" t="n">
@@ -5164,22 +5171,22 @@
       <c r="I21" s="2" t="n">
         <v>24176</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="3" t="n">
         <v>4.965471644662767</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="3" t="n">
         <v>5.510261937513361</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="3" t="n">
         <v>9.189188268434778</v>
       </c>
       <c r="M21" t="n">
         <v>9.096607850144967</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="3" t="n">
         <v>64.39</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="3" t="n">
         <v>5.1</v>
       </c>
       <c r="P21" s="2" t="n">
@@ -5191,7 +5198,7 @@
       <c r="R21" t="n">
         <v>372584.24</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21" s="2" t="n">
         <v>45843</v>
       </c>
       <c r="T21" t="n">
@@ -5204,7 +5211,7 @@
           <t>CANBK</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="2" t="n">
         <v>16.71605179468811</v>
       </c>
       <c r="C22" t="n">
@@ -5228,22 +5235,22 @@
       <c r="I22" s="2" t="n">
         <v>13296</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" s="2" t="n">
         <v>16.30293930023252</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="2" t="n">
         <v>18.17561078322378</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="2" t="n">
         <v>85.7752850068174</v>
       </c>
       <c r="M22" t="n">
         <v>53.4206382524911</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="3" t="n">
         <v>36.74</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="3" t="n">
         <v>12.61</v>
       </c>
       <c r="P22" s="2" t="n">
@@ -5255,7 +5262,7 @@
       <c r="R22" t="n">
         <v>496415.88</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="2" t="n">
         <v>110519</v>
       </c>
       <c r="T22" t="n">
@@ -5268,7 +5275,7 @@
           <t>IRFC</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="3" t="n">
         <v>13.0380853616381</v>
       </c>
       <c r="C23" t="n">
@@ -5292,22 +5299,22 @@
       <c r="I23" s="2" t="n">
         <v>7906</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="2" t="n">
         <v>19.10193873049559</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="2" t="n">
         <v>19.06740855567788</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="2" t="n">
         <v>23.24502393394037</v>
       </c>
       <c r="M23" t="n">
         <v>20.11244339814313</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="2" t="n">
         <v>9.81</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="2" t="n">
         <v>3.91</v>
       </c>
       <c r="P23" s="2" t="n">
@@ -5319,7 +5326,7 @@
       <c r="R23" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="2" t="n">
         <v>26645</v>
       </c>
       <c r="T23" t="n">
@@ -5332,7 +5339,7 @@
           <t>SHREECEM</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="3" t="n">
         <v>8.370767521615225</v>
       </c>
       <c r="C24" t="n">
@@ -5356,22 +5363,22 @@
       <c r="I24" s="2" t="n">
         <v>1929</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="2" t="n">
         <v>14.80997180241832</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="2" t="n">
         <v>10.32561591555659</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="3" t="n">
         <v>11.2926552609119</v>
       </c>
       <c r="M24" t="n">
         <v>10.67987982673917</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="2" t="n">
         <v>25.87</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="2" t="n">
         <v>1.21</v>
       </c>
       <c r="P24" s="2" t="n">
@@ -5383,7 +5390,7 @@
       <c r="R24" t="n">
         <v>3154358.33</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S24" s="2" t="n">
         <v>20521</v>
       </c>
       <c r="T24" t="n">
@@ -5396,7 +5403,7 @@
           <t>BOSCHLTD</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="2" t="n">
         <v>20.63992042440318</v>
       </c>
       <c r="C25" t="n">
@@ -5420,22 +5427,22 @@
       <c r="I25" s="2" t="n">
         <v>1536</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="2" t="n">
         <v>19.843289373664</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" s="3" t="n">
         <v>6.717165240230294</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>9.275930793686072</v>
       </c>
       <c r="M25" t="n">
         <v>9.261870727688626</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="3" t="n">
         <v>58.43</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" s="3" t="n">
         <v>6.47</v>
       </c>
       <c r="P25" s="2" t="n">
@@ -5447,7 +5454,7 @@
       <c r="R25" t="n">
         <v>2599556.05</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S25" s="2" t="n">
         <v>16727</v>
       </c>
       <c r="T25" t="n">
@@ -5460,7 +5467,7 @@
           <t>APOLLOHOSP</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="3" t="n">
         <v>13.48039215686275</v>
       </c>
       <c r="C26" t="n">
@@ -5484,22 +5491,22 @@
       <c r="I26" s="2" t="n">
         <v>383</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="2" t="n">
         <v>21.75273635187671</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" s="2" t="n">
         <v>14.66004260219314</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="2" t="n">
         <v>36.13077689773863</v>
       </c>
       <c r="M26" t="n">
         <v>29.95061094416296</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="3" t="n">
         <v>47.72</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" s="3" t="n">
         <v>7.68</v>
       </c>
       <c r="P26" s="2" t="n">
@@ -5511,11 +5518,11 @@
       <c r="R26" t="n">
         <v>1905622.43</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S26" s="2" t="n">
         <v>19059</v>
       </c>
       <c r="T26" t="n">
-        <v>38.44901577120161</v>
+        <v>37.67781723389874</v>
       </c>
     </row>
     <row r="27">
@@ -5524,7 +5531,7 @@
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="3" t="n">
         <v>9.958650553699458</v>
       </c>
       <c r="C27" t="n">
@@ -5548,22 +5555,22 @@
       <c r="I27" s="2" t="n">
         <v>45207</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="2" t="n">
         <v>24.46173600944801</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" s="3" t="n">
         <v>9.606097094616972</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>14.68063260349559</v>
       </c>
       <c r="M27" t="n">
         <v>11.95266483252204</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="3" t="n">
         <v>58.34</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" s="2" t="n">
         <v>3.25</v>
       </c>
       <c r="P27" s="2" t="n">
@@ -5575,7 +5582,7 @@
       <c r="R27" t="n">
         <v>432472.71</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S27" s="2" t="n">
         <v>899041</v>
       </c>
       <c r="T27" t="n">
@@ -5588,7 +5595,7 @@
           <t>DLF</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="3" t="n">
         <v>6.908270142781061</v>
       </c>
       <c r="C28" t="n">
@@ -5612,22 +5619,22 @@
       <c r="I28" s="2" t="n">
         <v>1010</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="3" t="n">
         <v>5.883921200220743</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28" s="3" t="n">
         <v>-5.136730668466605</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>15.69706651383664</v>
       </c>
       <c r="M28" t="n">
         <v>12.88813207301975</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="3" t="n">
         <v>46.26</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" s="3" t="n">
         <v>14.32</v>
       </c>
       <c r="P28" s="2" t="n">
@@ -5639,7 +5646,7 @@
       <c r="R28" t="n">
         <v>1381712.03</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S28" s="2" t="n">
         <v>6427</v>
       </c>
       <c r="T28" t="n">
@@ -5652,7 +5659,7 @@
           <t>DABUR</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="2" t="n">
         <v>18.35596999797284</v>
       </c>
       <c r="C29" t="n">
@@ -5676,22 +5683,22 @@
       <c r="I29" s="2" t="n">
         <v>1042</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="3" t="n">
         <v>9.061384362071356</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="3" t="n">
         <v>7.814065037783324</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="3" t="n">
         <v>4.604418961155621</v>
       </c>
       <c r="M29" t="n">
         <v>4.563955259127317</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="3" t="n">
         <v>50.95</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="3" t="n">
         <v>13.59</v>
       </c>
       <c r="P29" s="2" t="n">
@@ -5703,7 +5710,7 @@
       <c r="R29" t="n">
         <v>56521.84</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" s="2" t="n">
         <v>12404</v>
       </c>
       <c r="T29" t="n">
@@ -5716,7 +5723,7 @@
           <t>MOTHERSON</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="3" t="n">
         <v>11.54654941693749</v>
       </c>
       <c r="C30" t="n">
@@ -5740,22 +5747,22 @@
       <c r="I30" s="2" t="n">
         <v>925</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="2" t="n">
         <v>19.82084189180693</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="3" t="n">
         <v>9.211957132942761</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="3" t="n">
         <v>7.557399109099472</v>
       </c>
       <c r="M30" t="n">
         <v>5.922384104881218</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="2" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" s="2" t="n">
         <v>2.38</v>
       </c>
       <c r="P30" s="2" t="n">
@@ -5767,7 +5774,7 @@
       <c r="R30" t="n">
         <v>146151.16</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" s="2" t="n">
         <v>98692</v>
       </c>
       <c r="T30" t="n">
@@ -5939,31 +5946,31 @@
       <c r="H2" t="n">
         <v>1.025422325273269</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>955</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>19.2998469335665</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>11.83637017589811</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>13.48774998597666</v>
       </c>
       <c r="M2" t="n">
         <v>13.56415724960776</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>36.12</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>47</v>
       </c>
       <c r="R2" t="n">
@@ -5979,117 +5986,117 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>32.46823465801568</v>
+        <v>17.69876929087712</v>
       </c>
       <c r="C3" t="n">
-        <v>42.78159703860391</v>
+        <v>23.27321565617805</v>
       </c>
       <c r="D3" t="n">
-        <v>20.53342451701145</v>
+        <v>12.22122302158273</v>
       </c>
       <c r="E3" t="n">
-        <v>24.84185330825782</v>
+        <v>13.9568345323741</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.02243849689105163</v>
+        <v>0.01816761086149639</v>
       </c>
       <c r="G3" t="n">
-        <v>141.75</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1263238975544</v>
-      </c>
-      <c r="I3" t="n">
-        <v>797</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10.71372178938566</v>
-      </c>
-      <c r="K3" t="n">
-        <v>9.716101277290168</v>
-      </c>
-      <c r="L3" t="n">
-        <v>21.69314043381163</v>
+        <v>0.8790861298865568</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1168</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>18.99870072744285</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>11.1933589020679</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>19.85339817550189</v>
       </c>
       <c r="M3" t="n">
-        <v>21.65851677781967</v>
-      </c>
-      <c r="N3" t="n">
-        <v>75.58</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>73</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1536236.24</v>
+        <v>19.64385000375561</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>5849</v>
+        <v>22240</v>
       </c>
       <c r="T3" t="n">
-        <v>74.71367760204753</v>
+        <v>77.08886610587359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>17.69876929087712</v>
+        <v>32.46823465801568</v>
       </c>
       <c r="C4" t="n">
-        <v>23.27321565617805</v>
+        <v>42.78159703860391</v>
       </c>
       <c r="D4" t="n">
-        <v>12.22122302158273</v>
+        <v>20.53342451701145</v>
       </c>
       <c r="E4" t="n">
-        <v>13.9568345323741</v>
+        <v>24.84185330825782</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.01816761086149639</v>
+        <v>0.02243849689105163</v>
       </c>
       <c r="G4" t="n">
-        <v>67.15000000000001</v>
+        <v>141.75</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8790861298865568</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1168</v>
-      </c>
-      <c r="J4" t="n">
-        <v>18.99870072744285</v>
-      </c>
-      <c r="K4" t="n">
-        <v>11.1933589020679</v>
-      </c>
-      <c r="L4" t="n">
-        <v>19.85339817550189</v>
+        <v>1.1263238975544</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>797</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>10.71372178938566</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>9.716101277290168</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>21.69314043381163</v>
       </c>
       <c r="M4" t="n">
-        <v>19.64385000375561</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>16</v>
+        <v>21.65851677781967</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1536236.24</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>22240</v>
+        <v>5849</v>
       </c>
       <c r="T4" t="n">
-        <v>68.12570273895892</v>
+        <v>63.58350294739142</v>
       </c>
     </row>
     <row r="5">
@@ -6119,31 +6126,31 @@
       <c r="H5" t="n">
         <v>0.7723477995509732</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="2" t="n">
         <v>18742</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="2" t="n">
         <v>12.89030700491063</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="3" t="n">
         <v>7.950896846254429</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>10.08340755831796</v>
       </c>
       <c r="M5" t="n">
         <v>9.856054330611785</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>47.85</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="2" t="n">
         <v>3.24</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="2" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="3" t="n">
         <v>84</v>
       </c>
       <c r="R5" t="n">
@@ -6159,65 +6166,65 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>15.55455702838313</v>
+        <v>17.06727541291795</v>
       </c>
       <c r="C6" t="n">
-        <v>20.91325875664772</v>
+        <v>22.0258064516129</v>
       </c>
       <c r="D6" t="n">
-        <v>16.11701714906495</v>
+        <v>6.837009144701453</v>
       </c>
       <c r="E6" t="n">
-        <v>75.59168153953597</v>
+        <v>10.11834319526627</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.02093162585186849</v>
+        <v>0.040687525177924</v>
       </c>
       <c r="G6" t="n">
-        <v>35.33876811594203</v>
+        <v>25.35714285714286</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7922417237881536</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1152</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10.38975593522793</v>
-      </c>
-      <c r="K6" t="n">
-        <v>9.513860126378049</v>
-      </c>
-      <c r="L6" t="n">
-        <v>22.72683484800089</v>
+        <v>1.495214348910158</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>21.14089015706202</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>13.03790793906312</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>10.03323122942004</v>
       </c>
       <c r="M6" t="n">
-        <v>21.83254460856599</v>
-      </c>
-      <c r="N6" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>25</v>
+        <v>8.997698704834534</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>44</v>
       </c>
       <c r="R6" t="n">
-        <v>439803.15</v>
+        <v>2521508.87</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>25774</v>
+        <v>18590</v>
       </c>
       <c r="T6" t="n">
-        <v>57.69180855467479</v>
+        <v>58.15011682984635</v>
       </c>
     </row>
     <row r="7">
@@ -6247,31 +6254,31 @@
       <c r="H7" t="n">
         <v>0.7885945801322478</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="2" t="n">
         <v>10145</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="3" t="n">
         <v>9.589435897156351</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>9.504485244074123</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>11.15295043680342</v>
       </c>
       <c r="M7" t="n">
         <v>9.460878422315755</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="n">
         <v>34.51</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3" t="n">
         <v>11.88</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="2" t="n">
         <v>4.32</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="3" t="n">
         <v>96</v>
       </c>
       <c r="R7" t="n">
@@ -6311,31 +6318,31 @@
       <c r="H8" t="n">
         <v>0.7153796236210254</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="2" t="n">
         <v>890</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="2" t="n">
         <v>23.776441520116</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="2" t="n">
         <v>11.03693649673969</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="3" t="n">
         <v>12.6758416653777</v>
       </c>
       <c r="M8" t="n">
         <v>12.50545162905032</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="2" t="n">
         <v>15.62</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="3" t="n">
         <v>13.61</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="2" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="2" t="n">
         <v>35</v>
       </c>
       <c r="R8" t="n">
@@ -6351,129 +6358,129 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>13.56294790886726</v>
+        <v>15.55455702838313</v>
       </c>
       <c r="C9" t="n">
-        <v>17.9419388284085</v>
+        <v>20.91325875664772</v>
       </c>
       <c r="D9" t="n">
-        <v>4.993207190533383</v>
+        <v>16.11701714906495</v>
       </c>
       <c r="E9" t="n">
-        <v>8.084427730414067</v>
+        <v>75.59168153953597</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.03166114022890149</v>
+        <v>0.02093162585186849</v>
       </c>
       <c r="G9" t="n">
-        <v>73.29310344827586</v>
+        <v>35.33876811594203</v>
       </c>
       <c r="H9" t="n">
-        <v>2.398875873795579</v>
-      </c>
-      <c r="I9" t="n">
-        <v>278</v>
-      </c>
-      <c r="J9" t="n">
-        <v>28.1325519519273</v>
-      </c>
-      <c r="K9" t="n">
-        <v>20.48312440202782</v>
-      </c>
-      <c r="L9" t="n">
-        <v>22.96698996520703</v>
+        <v>0.7922417237881536</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1152</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>10.38975593522793</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>9.513860126378049</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>22.72683484800089</v>
       </c>
       <c r="M9" t="n">
-        <v>22.74033782145131</v>
-      </c>
-      <c r="N9" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="O9" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
+        <v>21.83254460856599</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>25</v>
       </c>
       <c r="R9" t="n">
-        <v>3053088.97</v>
+        <v>439803.15</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>50789</v>
+        <v>25774</v>
       </c>
       <c r="T9" t="n">
-        <v>49.2334625729186</v>
+        <v>50.57169744934144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>17.06727541291795</v>
+        <v>13.56294790886726</v>
       </c>
       <c r="C10" t="n">
-        <v>22.0258064516129</v>
+        <v>17.9419388284085</v>
       </c>
       <c r="D10" t="n">
-        <v>6.837009144701453</v>
+        <v>4.993207190533383</v>
       </c>
       <c r="E10" t="n">
-        <v>10.11834319526627</v>
+        <v>8.084427730414067</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.040687525177924</v>
+        <v>0.03166114022890149</v>
       </c>
       <c r="G10" t="n">
-        <v>25.35714285714286</v>
+        <v>73.29310344827586</v>
       </c>
       <c r="H10" t="n">
-        <v>1.495214348910158</v>
-      </c>
-      <c r="I10" t="n">
-        <v>335</v>
-      </c>
-      <c r="J10" t="n">
-        <v>21.14089015706202</v>
-      </c>
-      <c r="K10" t="n">
-        <v>13.03790793906312</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10.03323122942004</v>
+        <v>2.398875873795579</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>28.1325519519273</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>20.48312440202782</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>22.96698996520703</v>
       </c>
       <c r="M10" t="n">
-        <v>8.997698704834534</v>
-      </c>
-      <c r="N10" t="n">
-        <v>45.41</v>
-      </c>
-      <c r="O10" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>44</v>
+        <v>22.74033782145131</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2521508.87</v>
+        <v>3053088.97</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>18590</v>
+        <v>50789</v>
       </c>
       <c r="T10" t="n">
-        <v>48.75439737462181</v>
+        <v>49.2334625729186</v>
       </c>
     </row>
     <row r="11">
@@ -6503,31 +6510,31 @@
       <c r="H11" t="n">
         <v>1.230295566502463</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="2" t="n">
         <v>4936</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="2" t="n">
         <v>26.32364432616601</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="2" t="n">
         <v>10.51021511264258</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>12.00718203930038</v>
       </c>
       <c r="M11" t="n">
         <v>11.1392224868865</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="2" t="n">
         <v>20.78</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="3" t="n">
         <v>8.26</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="2" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="2" t="n">
         <v>29</v>
       </c>
       <c r="R11" t="n">
@@ -6567,31 +6574,31 @@
       <c r="H12" t="n">
         <v>1.444920276832486</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="2" t="n">
         <v>3095</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="3" t="n">
         <v>6.870906150291889</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="3" t="n">
         <v>2.153067797054464</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>1.544181887188389</v>
       </c>
       <c r="M12" t="n">
         <v>1.686343719746475</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="3" t="n">
         <v>53.86</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="2" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="2" t="n">
         <v>75</v>
       </c>
       <c r="R12" t="n">
@@ -6631,31 +6638,31 @@
       <c r="H13" t="n">
         <v>0.9638144626908672</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="2" t="n">
         <v>1536</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="2" t="n">
         <v>19.843289373664</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13" s="3" t="n">
         <v>6.717165240230294</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="3" t="n">
         <v>9.275930793686072</v>
       </c>
       <c r="M13" t="n">
         <v>9.261870727688626</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13" s="3" t="n">
         <v>58.43</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" s="3" t="n">
         <v>6.47</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" s="2" t="n">
         <v>4.23</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13" s="2" t="n">
         <v>44</v>
       </c>
       <c r="R13" t="n">
@@ -6812,7 +6819,7 @@
           <t>IRCTC</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>34.39628482972136</v>
       </c>
       <c r="C2" t="n">
@@ -6839,31 +6846,31 @@
       <c r="J2" s="2" t="n">
         <v>76.46921430165466</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>17.95524410389091</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>29.16686408659448</v>
       </c>
       <c r="M2" t="n">
         <v>28.47351571234393</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="n">
         <v>60.44</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="3" t="n">
         <v>5.74</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>47</v>
       </c>
       <c r="R2" t="n">
         <v>1258520.29</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="3" t="n">
         <v>4270</v>
       </c>
       <c r="T2" t="n">
@@ -6876,7 +6883,7 @@
           <t>ADANIPOWER</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="2" t="n">
         <v>48.27674122146251</v>
       </c>
       <c r="C3" t="n">
@@ -6903,25 +6910,25 @@
       <c r="J3" s="2" t="n">
         <v>24.29479715622616</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="2" t="n">
         <v>16.08609641044097</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="n">
         <v>44.57</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="3" t="n">
         <v>9.91</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="2" t="n">
         <v>1.65</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1372183.55</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="2" t="n">
         <v>50351</v>
       </c>
       <c r="T3" t="n">
@@ -6934,7 +6941,7 @@
           <t>PIDILITIND</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="2" t="n">
         <v>20.78030212917806</v>
       </c>
       <c r="C4" t="n">
@@ -6961,31 +6968,31 @@
       <c r="J4" s="2" t="n">
         <v>19.2998469335665</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="2" t="n">
         <v>11.83637017589811</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>13.48774998597666</v>
       </c>
       <c r="M4" t="n">
         <v>13.56415724960776</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="n">
         <v>36.12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="2" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="2" t="n">
         <v>47</v>
       </c>
       <c r="R4" t="n">
         <v>162274.18</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="2" t="n">
         <v>12383</v>
       </c>
       <c r="T4" t="n">
@@ -6998,7 +7005,7 @@
           <t>NESTLEIND</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="2" t="n">
         <v>117.7544910179641</v>
       </c>
       <c r="C5" t="n">
@@ -7025,31 +7032,31 @@
       <c r="J5" s="2" t="n">
         <v>18.28200866249903</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="2" t="n">
         <v>14.54857371180267</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>14.85231951299384</v>
       </c>
       <c r="M5" t="n">
         <v>15.43852585822143</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="n">
         <v>54.96</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="3" t="n">
         <v>14.34</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="2" t="n">
         <v>3.85</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="2" t="n">
         <v>79</v>
       </c>
       <c r="R5" t="n">
         <v>1677775.19</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="2" t="n">
         <v>24394</v>
       </c>
       <c r="T5" t="n">
@@ -7062,7 +7069,7 @@
           <t>BAJAJHLDNG</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>13.57678765646027</v>
       </c>
       <c r="C6" t="n">
@@ -7089,31 +7096,31 @@
       <c r="J6" s="2" t="n">
         <v>55.00574158769729</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="2" t="n">
         <v>31.61229344896917</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>19.2975590637313</v>
       </c>
       <c r="M6" t="n">
         <v>18.96864732798973</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="n">
         <v>37.73</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="3" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" s="2" t="n">
         <v>3.37</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="2" t="n">
         <v>20</v>
       </c>
       <c r="R6" t="n">
         <v>2191568.13</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="3" t="n">
         <v>1702</v>
       </c>
       <c r="T6" t="n">
@@ -7126,7 +7133,7 @@
           <t>TRENT</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="2" t="n">
         <v>36.30776794493609</v>
       </c>
       <c r="C7" t="n">
@@ -7153,31 +7160,31 @@
       <c r="J7" s="2" t="n">
         <v>68.36335197744833</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="2" t="n">
         <v>36.30691600183056</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="2" t="n">
         <v>73.11367578503176</v>
       </c>
       <c r="M7" t="n">
         <v>69.52182030724354</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="2" t="n">
         <v>8.65</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3" t="n">
         <v>11.82</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="2" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="2" t="n">
         <v>8</v>
       </c>
       <c r="R7" t="n">
         <v>571322.04</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="2" t="n">
         <v>12375</v>
       </c>
       <c r="T7" t="n">
@@ -7187,129 +7194,129 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>32.46823465801568</v>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>15.3548827162833</v>
       </c>
       <c r="C8" t="n">
-        <v>42.78159703860391</v>
+        <v>9.427079258274</v>
       </c>
       <c r="D8" t="n">
-        <v>20.53342451701145</v>
+        <v>30.33956048070083</v>
       </c>
       <c r="E8" t="n">
-        <v>24.84185330825782</v>
+        <v>58.36172363445772</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02243849689105163</v>
+        <v>0.9373223691689719</v>
       </c>
       <c r="G8" t="n">
-        <v>141.75</v>
+        <v>5.949506037321624</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1263238975544</v>
+        <v>0.2283010965905692</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>797</v>
+        <v>8250</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.71372178938566</v>
-      </c>
-      <c r="K8" t="n">
-        <v>9.716101277290168</v>
-      </c>
-      <c r="L8" t="n">
-        <v>21.69314043381163</v>
+        <v>28.63193631184944</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>19.57867595245697</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>14.90956518204163</v>
       </c>
       <c r="M8" t="n">
-        <v>21.65851677781967</v>
-      </c>
-      <c r="N8" t="n">
-        <v>75.58</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>73</v>
+        <v>14.86983549970351</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>1536236.24</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5849</v>
+        <v>675598.01</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>26711</v>
       </c>
       <c r="T8" t="n">
-        <v>74.71367760204753</v>
+        <v>70.30971582063562</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>15.3548827162833</v>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>32.46823465801568</v>
       </c>
       <c r="C9" t="n">
-        <v>9.427079258274</v>
+        <v>42.78159703860391</v>
       </c>
       <c r="D9" t="n">
-        <v>30.33956048070083</v>
+        <v>20.53342451701145</v>
       </c>
       <c r="E9" t="n">
-        <v>58.36172363445772</v>
+        <v>24.84185330825782</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9373223691689719</v>
+        <v>0.02243849689105163</v>
       </c>
       <c r="G9" t="n">
-        <v>5.949506037321624</v>
+        <v>141.75</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2283010965905692</v>
+        <v>1.1263238975544</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>8250</v>
+        <v>797</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>28.63193631184944</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19.57867595245697</v>
-      </c>
-      <c r="L9" t="n">
-        <v>14.90956518204163</v>
+        <v>10.71372178938566</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>9.716101277290168</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>21.69314043381163</v>
       </c>
       <c r="M9" t="n">
-        <v>14.86983549970351</v>
-      </c>
-      <c r="N9" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>16</v>
+        <v>21.65851677781967</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>73</v>
       </c>
       <c r="R9" t="n">
-        <v>675598.01</v>
-      </c>
-      <c r="S9" t="n">
-        <v>26711</v>
+        <v>1536236.24</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>5849</v>
       </c>
       <c r="T9" t="n">
-        <v>64.60059842643911</v>
+        <v>63.58350294739142</v>
       </c>
     </row>
     <row r="10">
@@ -7318,7 +7325,7 @@
           <t>BPCL</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="2" t="n">
         <v>35.51133734382231</v>
       </c>
       <c r="C10" t="n">
@@ -7345,31 +7352,31 @@
       <c r="J10" s="2" t="n">
         <v>24.86362936813233</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>8.483226324685255</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="2" t="n">
         <v>25.79069872974655</v>
       </c>
       <c r="M10" t="n">
         <v>28.06304880261565</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10" s="3" t="n">
         <v>68.15000000000001</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="2" t="n">
         <v>0.72</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="2" t="n">
         <v>1.15</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="2" t="n">
         <v>33</v>
       </c>
       <c r="R10" t="n">
         <v>468662.13</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10" s="2" t="n">
         <v>448083</v>
       </c>
       <c r="T10" t="n">
@@ -7382,7 +7389,7 @@
           <t>ITC</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="2" t="n">
         <v>27.85107439569436</v>
       </c>
       <c r="C11" t="n">
@@ -7409,31 +7416,31 @@
       <c r="J11" s="2" t="n">
         <v>12.89030700491063</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11" s="3" t="n">
         <v>7.950896846254429</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="3" t="n">
         <v>10.08340755831796</v>
       </c>
       <c r="M11" t="n">
         <v>9.856054330611785</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11" s="3" t="n">
         <v>47.85</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" s="2" t="n">
         <v>3.24</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" s="2" t="n">
         <v>4.26</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11" s="3" t="n">
         <v>84</v>
       </c>
       <c r="R11" t="n">
         <v>332245.58</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="2" t="n">
         <v>70866</v>
       </c>
       <c r="T11" t="n">
@@ -7446,7 +7453,7 @@
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="2" t="n">
         <v>15.7230643179025</v>
       </c>
       <c r="C12" t="n">
@@ -7473,31 +7480,31 @@
       <c r="J12" s="2" t="n">
         <v>18.98796206427069</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12" s="2" t="n">
         <v>12.91184100336258</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="3" t="n">
         <v>12.83917371819816</v>
       </c>
       <c r="M12" t="n">
         <v>11.1392224868865</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" s="3" t="n">
         <v>7.86</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" s="2" t="n">
         <v>3.46</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12" s="2" t="n">
         <v>28</v>
       </c>
       <c r="R12" t="n">
         <v>1271789.21</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12" s="2" t="n">
         <v>20487</v>
       </c>
       <c r="T12" t="n">
@@ -7507,507 +7514,507 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>15.55455702838313</v>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>17.99027109750765</v>
       </c>
       <c r="C13" t="n">
-        <v>20.91325875664772</v>
+        <v>3.168808778744431</v>
       </c>
       <c r="D13" t="n">
-        <v>16.11701714906495</v>
+        <v>28.8880112339828</v>
       </c>
       <c r="E13" t="n">
-        <v>75.59168153953597</v>
+        <v>62.41380175029464</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02093162585186849</v>
+        <v>6.445624336310825</v>
       </c>
       <c r="G13" t="n">
-        <v>35.33876811594203</v>
+        <v>1.300946133138182</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7922417237881536</v>
+        <v>0.06747535915921023</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1152</v>
+        <v>12547</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10.38975593522793</v>
-      </c>
-      <c r="K13" t="n">
-        <v>9.513860126378049</v>
-      </c>
-      <c r="L13" t="n">
-        <v>22.72683484800089</v>
+        <v>21.39660074377121</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>17.25086850260209</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>51.94877118224903</v>
       </c>
       <c r="M13" t="n">
-        <v>21.83254460856599</v>
-      </c>
-      <c r="N13" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="O13" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>25</v>
+        <v>55.18455739153598</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="R13" t="n">
-        <v>439803.15</v>
-      </c>
-      <c r="S13" t="n">
-        <v>25774</v>
+        <v>1319221.86</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>159516</v>
       </c>
       <c r="T13" t="n">
-        <v>57.69180855467479</v>
+        <v>54.25483366558786</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>24.15402567094516</v>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>10.35839213740181</v>
       </c>
       <c r="C14" t="n">
-        <v>21.62162162162162</v>
+        <v>4.251687563503694</v>
       </c>
       <c r="D14" t="n">
-        <v>15.43624161073826</v>
+        <v>5.706018055499993</v>
       </c>
       <c r="E14" t="n">
-        <v>31.3944817300522</v>
+        <v>52.20093077836007</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5866394399066511</v>
+        <v>2.609472397390431</v>
       </c>
       <c r="G14" t="n">
-        <v>9.926553672316384</v>
+        <v>3.305545743553515</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7396070320579111</v>
+        <v>0.3393112060793767</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3106</v>
+        <v>27809</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10.25183069859263</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6.932744476678732</v>
-      </c>
-      <c r="L14" t="n">
-        <v>30.59145740232785</v>
+        <v>14.23276725060496</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>13.17410230151459</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>38.35662769365473</v>
       </c>
       <c r="M14" t="n">
-        <v>30.39187954400138</v>
-      </c>
-      <c r="N14" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>57</v>
+        <v>67.02776523348103</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>63.78</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>62</v>
       </c>
       <c r="R14" t="n">
-        <v>1870170.39</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10728</v>
+        <v>378605.83</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>149982</v>
       </c>
       <c r="T14" t="n">
-        <v>55.90755671792368</v>
+        <v>52.69322977075988</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>17.99027109750765</v>
+          <t>TATAMOTORS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>37.45613415294755</v>
       </c>
       <c r="C15" t="n">
-        <v>3.168808778744431</v>
+        <v>14.54625871578728</v>
       </c>
       <c r="D15" t="n">
-        <v>28.8880112339828</v>
+        <v>7.263066074788551</v>
       </c>
       <c r="E15" t="n">
-        <v>62.41380175029464</v>
+        <v>13.59538554282896</v>
       </c>
       <c r="F15" t="n">
-        <v>6.445624336310825</v>
+        <v>1.263124425916767</v>
       </c>
       <c r="G15" t="n">
-        <v>1.300946133138182</v>
+        <v>6.530242339274985</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06747535915921023</v>
+        <v>1.185123443593192</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12547</v>
+        <v>45133</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21.39660074377121</v>
-      </c>
-      <c r="K15" t="n">
-        <v>17.25086850260209</v>
-      </c>
-      <c r="L15" t="n">
-        <v>51.94877118224903</v>
-      </c>
-      <c r="M15" t="n">
-        <v>55.18455739153598</v>
-      </c>
-      <c r="N15" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="O15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>16</v>
+        <v>20.57936456937097</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>7.720159538623927</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>67.06999999999999</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>1319221.86</v>
-      </c>
-      <c r="S15" t="n">
-        <v>159516</v>
+        <v>1504106.64</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>437928</v>
       </c>
       <c r="T15" t="n">
-        <v>54.25483366558786</v>
+        <v>51.6052090535713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>10.35839213740181</v>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>23.53162465856491</v>
       </c>
       <c r="C16" t="n">
-        <v>4.251687563503694</v>
+        <v>18.12653261402648</v>
       </c>
       <c r="D16" t="n">
-        <v>5.706018055499993</v>
+        <v>5.559462717942377</v>
       </c>
       <c r="E16" t="n">
-        <v>52.20093077836007</v>
+        <v>9.743776019125345</v>
       </c>
       <c r="F16" t="n">
-        <v>2.609472397390431</v>
+        <v>0.7230954600718581</v>
       </c>
       <c r="G16" t="n">
-        <v>3.305545743553515</v>
+        <v>10.28232457809923</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3393112060793767</v>
+        <v>1.608409660170339</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>27809</v>
+        <v>39635</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>14.23276725060496</v>
-      </c>
-      <c r="K16" t="n">
-        <v>13.17410230151459</v>
-      </c>
-      <c r="L16" t="n">
-        <v>38.35662769365473</v>
+        <v>28.72779122527918</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>8.008755667240486</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>20.09908996673164</v>
       </c>
       <c r="M16" t="n">
-        <v>67.02776523348103</v>
-      </c>
-      <c r="N16" t="n">
-        <v>63.78</v>
-      </c>
-      <c r="O16" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>62</v>
+        <v>20.11244339814313</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>40</v>
       </c>
       <c r="R16" t="n">
-        <v>378605.83</v>
-      </c>
-      <c r="S16" t="n">
-        <v>149982</v>
+        <v>1418164.33</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>776352</v>
       </c>
       <c r="T16" t="n">
-        <v>52.69322977075988</v>
+        <v>51.28288911006975</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>37.45613415294755</v>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>15.55455702838313</v>
       </c>
       <c r="C17" t="n">
-        <v>14.54625871578728</v>
+        <v>20.91325875664772</v>
       </c>
       <c r="D17" t="n">
-        <v>7.263066074788551</v>
+        <v>16.11701714906495</v>
       </c>
       <c r="E17" t="n">
-        <v>13.59538554282896</v>
+        <v>75.59168153953597</v>
       </c>
       <c r="F17" t="n">
-        <v>1.263124425916767</v>
+        <v>0.02093162585186849</v>
       </c>
       <c r="G17" t="n">
-        <v>6.530242339274985</v>
+        <v>35.33876811594203</v>
       </c>
       <c r="H17" t="n">
-        <v>1.185123443593192</v>
+        <v>0.7922417237881536</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45133</v>
+        <v>1152</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20.57936456937097</v>
-      </c>
-      <c r="K17" t="n">
-        <v>7.720159538623927</v>
-      </c>
-      <c r="N17" t="n">
-        <v>67.06999999999999</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>7</v>
+        <v>10.38975593522793</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>9.513860126378049</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>22.72683484800089</v>
+      </c>
+      <c r="M17" t="n">
+        <v>21.83254460856599</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>25</v>
       </c>
       <c r="R17" t="n">
-        <v>1504106.64</v>
-      </c>
-      <c r="S17" t="n">
-        <v>437928</v>
+        <v>439803.15</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>25774</v>
       </c>
       <c r="T17" t="n">
-        <v>51.6052090535713</v>
+        <v>50.57169744934144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>15.09416181067115</v>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>13.56294790886726</v>
       </c>
       <c r="C18" t="n">
-        <v>16.56383979922618</v>
+        <v>17.9419388284085</v>
       </c>
       <c r="D18" t="n">
-        <v>19.81565870053818</v>
+        <v>4.993207190533383</v>
       </c>
       <c r="E18" t="n">
-        <v>26.84289749881436</v>
+        <v>8.084427730414067</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05142381453500244</v>
+        <v>0.03166114022890149</v>
       </c>
       <c r="G18" t="n">
-        <v>58.33193277310924</v>
+        <v>73.29310344827586</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5684929901064378</v>
+        <v>2.398875873795579</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11372</v>
+        <v>278</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>13.12675558948349</v>
-      </c>
-      <c r="K18" t="n">
-        <v>10.78116321985565</v>
-      </c>
-      <c r="L18" t="n">
-        <v>24.53682964293125</v>
+        <v>28.1325519519273</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>20.48312440202782</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>22.96698996520703</v>
       </c>
       <c r="M18" t="n">
-        <v>29.45936165164078</v>
-      </c>
-      <c r="N18" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>34</v>
+        <v>22.74033782145131</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1339586.09</v>
-      </c>
-      <c r="S18" t="n">
-        <v>48497</v>
+        <v>3053088.97</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>50789</v>
       </c>
       <c r="T18" t="n">
-        <v>51.37713526020612</v>
+        <v>49.2334625729186</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>23.53162465856491</v>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>15.09416181067115</v>
       </c>
       <c r="C19" t="n">
-        <v>18.12653261402648</v>
+        <v>16.56383979922618</v>
       </c>
       <c r="D19" t="n">
-        <v>5.559462717942377</v>
+        <v>19.81565870053818</v>
       </c>
       <c r="E19" t="n">
-        <v>9.743776019125345</v>
+        <v>26.84289749881436</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7230954600718581</v>
+        <v>0.05142381453500244</v>
       </c>
       <c r="G19" t="n">
-        <v>10.28232457809923</v>
+        <v>58.33193277310924</v>
       </c>
       <c r="H19" t="n">
-        <v>1.608409660170339</v>
+        <v>0.5684929901064378</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>39635</v>
+        <v>11372</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28.72779122527918</v>
-      </c>
-      <c r="K19" t="n">
-        <v>8.008755667240486</v>
-      </c>
-      <c r="L19" t="n">
-        <v>20.09908996673164</v>
+        <v>13.12675558948349</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>10.78116321985565</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>24.53682964293125</v>
       </c>
       <c r="M19" t="n">
-        <v>20.11244339814313</v>
-      </c>
-      <c r="N19" t="n">
-        <v>28.61</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>40</v>
+        <v>29.45936165164078</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>34</v>
       </c>
       <c r="R19" t="n">
-        <v>1418164.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>776352</v>
+        <v>1339586.09</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>48497</v>
       </c>
       <c r="T19" t="n">
-        <v>51.28288911006975</v>
+        <v>47.85970653156618</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DMART</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>13.56294790886726</v>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>24.15402567094516</v>
       </c>
       <c r="C20" t="n">
-        <v>17.9419388284085</v>
+        <v>21.62162162162162</v>
       </c>
       <c r="D20" t="n">
-        <v>4.993207190533383</v>
+        <v>15.43624161073826</v>
       </c>
       <c r="E20" t="n">
-        <v>8.084427730414067</v>
+        <v>31.3944817300522</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03166114022890149</v>
+        <v>0.5866394399066511</v>
       </c>
       <c r="G20" t="n">
-        <v>73.29310344827586</v>
+        <v>9.926553672316384</v>
       </c>
       <c r="H20" t="n">
-        <v>2.398875873795579</v>
+        <v>0.7396070320579111</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>278</v>
+        <v>3106</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>28.1325519519273</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20.48312440202782</v>
-      </c>
-      <c r="L20" t="n">
-        <v>22.96698996520703</v>
+        <v>10.25183069859263</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>6.932744476678732</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>30.59145740232785</v>
       </c>
       <c r="M20" t="n">
-        <v>22.74033782145131</v>
-      </c>
-      <c r="N20" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="O20" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
+        <v>30.39187954400138</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>57</v>
       </c>
       <c r="R20" t="n">
-        <v>3053088.97</v>
-      </c>
-      <c r="S20" t="n">
-        <v>50789</v>
+        <v>1870170.39</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>10728</v>
       </c>
       <c r="T20" t="n">
-        <v>49.2334625729186</v>
+        <v>47.25405762233536</v>
       </c>
     </row>
     <row r="21">
@@ -8016,7 +8023,7 @@
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="3" t="n">
         <v>14.33974005030719</v>
       </c>
       <c r="C21" t="n">
@@ -8043,31 +8050,31 @@
       <c r="J21" s="2" t="n">
         <v>30.18695614094877</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21" s="2" t="n">
         <v>21.95098428169122</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21" s="2" t="n">
         <v>23.86506357287907</v>
       </c>
       <c r="M21" t="n">
         <v>15.42478808253083</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21" s="3" t="n">
         <v>49.42</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21" s="2" t="n">
         <v>4.33</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21" s="2" t="n">
         <v>23</v>
       </c>
       <c r="R21" t="n">
         <v>808359.03</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21" s="2" t="n">
         <v>283649</v>
       </c>
       <c r="T21" t="n">
@@ -8080,7 +8087,7 @@
           <t>CANBK</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="2" t="n">
         <v>16.71605179468811</v>
       </c>
       <c r="C22" t="n">
@@ -8107,31 +8114,31 @@
       <c r="J22" s="2" t="n">
         <v>16.30293930023252</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="2" t="n">
         <v>18.17561078322378</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="2" t="n">
         <v>85.7752850068174</v>
       </c>
       <c r="M22" t="n">
         <v>53.4206382524911</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22" s="3" t="n">
         <v>36.74</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" s="3" t="n">
         <v>12.61</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22" s="2" t="n">
         <v>3.81</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22" s="2" t="n">
         <v>19</v>
       </c>
       <c r="R22" t="n">
         <v>496415.88</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22" s="2" t="n">
         <v>110519</v>
       </c>
       <c r="T22" t="n">
@@ -8144,7 +8151,7 @@
           <t>INFY</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="2" t="n">
         <v>29.78800671841663</v>
       </c>
       <c r="C23" t="n">
@@ -8171,28 +8178,28 @@
       <c r="J23" s="2" t="n">
         <v>15.21650079880636</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23" s="2" t="n">
         <v>13.19910093055623</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23" s="3" t="n">
         <v>11.23941998365794</v>
       </c>
       <c r="M23" t="n">
         <v>12.47461131420948</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23" s="3" t="n">
         <v>35.99</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" s="3" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23" s="2" t="n">
         <v>4.1</v>
       </c>
       <c r="R23" t="n">
         <v>1112279.92</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23" s="2" t="n">
         <v>153670</v>
       </c>
       <c r="T23" t="n">
@@ -8205,7 +8212,7 @@
           <t>IRFC</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="3" t="n">
         <v>13.0380853616381</v>
       </c>
       <c r="C24" t="n">
@@ -8232,31 +8239,31 @@
       <c r="J24" s="2" t="n">
         <v>19.10193873049559</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24" s="2" t="n">
         <v>19.06740855567788</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24" s="2" t="n">
         <v>23.24502393394037</v>
       </c>
       <c r="M24" t="n">
         <v>20.11244339814313</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24" s="2" t="n">
         <v>9.81</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" s="2" t="n">
         <v>3.91</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24" s="2" t="n">
         <v>2.82</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24" s="2" t="n">
         <v>31</v>
       </c>
       <c r="R24" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S24" s="2" t="n">
         <v>26645</v>
       </c>
       <c r="T24" t="n">
@@ -8269,7 +8276,7 @@
           <t>ONGC</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="2" t="n">
         <v>16.94039813688551</v>
       </c>
       <c r="C25" t="n">
@@ -8296,31 +8303,31 @@
       <c r="J25" s="2" t="n">
         <v>24.85526395727469</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25" s="3" t="n">
         <v>7.001683761214439</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25" s="3" t="n">
         <v>10.96639922553624</v>
       </c>
       <c r="M25" t="n">
         <v>10.19722877214802</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25" s="2" t="n">
         <v>18.15</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" s="3" t="n">
         <v>10.36</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25" s="2" t="n">
         <v>1.11</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25" s="2" t="n">
         <v>31</v>
       </c>
       <c r="R25" t="n">
         <v>390111.05</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S25" s="2" t="n">
         <v>591396</v>
       </c>
       <c r="T25" t="n">
@@ -8333,7 +8340,7 @@
           <t>SHREECEM</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="3" t="n">
         <v>8.370767521615225</v>
       </c>
       <c r="C26" t="n">
@@ -8360,31 +8367,31 @@
       <c r="J26" s="2" t="n">
         <v>14.80997180241832</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26" s="2" t="n">
         <v>10.32561591555659</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26" s="3" t="n">
         <v>11.2926552609119</v>
       </c>
       <c r="M26" t="n">
         <v>10.67987982673917</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26" s="2" t="n">
         <v>25.87</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" s="2" t="n">
         <v>1.21</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26" s="2" t="n">
         <v>16</v>
       </c>
       <c r="R26" t="n">
         <v>3154358.33</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S26" s="2" t="n">
         <v>20521</v>
       </c>
       <c r="T26" t="n">
@@ -8397,7 +8404,7 @@
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="2" t="n">
         <v>15.75038535195478</v>
       </c>
       <c r="C27" t="n">
@@ -8424,31 +8431,31 @@
       <c r="J27" s="2" t="n">
         <v>26.32364432616601</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27" s="2" t="n">
         <v>10.51021511264258</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27" s="3" t="n">
         <v>12.00718203930038</v>
       </c>
       <c r="M27" t="n">
         <v>11.1392224868865</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27" s="2" t="n">
         <v>20.78</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" s="3" t="n">
         <v>8.26</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27" s="2" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27" s="2" t="n">
         <v>29</v>
       </c>
       <c r="R27" t="n">
         <v>1503863.63</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S27" s="2" t="n">
         <v>141858</v>
       </c>
       <c r="T27" t="n">
@@ -8461,7 +8468,7 @@
           <t>HINDALCO</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="3" t="n">
         <v>9.567011474761177</v>
       </c>
       <c r="C28" t="n">
@@ -8488,31 +8495,31 @@
       <c r="J28" s="2" t="n">
         <v>17.83085522343517</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28" s="2" t="n">
         <v>10.59243381898591</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28" s="3" t="n">
         <v>13.06871230695661</v>
       </c>
       <c r="M28" t="n">
         <v>13.39665776330272</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28" s="3" t="n">
         <v>56.45</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" s="3" t="n">
         <v>9.32</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28" s="2" t="n">
         <v>0.98</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28" s="2" t="n">
         <v>8</v>
       </c>
       <c r="R28" t="n">
         <v>722281.1</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S28" s="2" t="n">
         <v>215962</v>
       </c>
       <c r="T28" t="n">
@@ -8525,7 +8532,7 @@
           <t>BOSCHLTD</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="2" t="n">
         <v>20.63992042440318</v>
       </c>
       <c r="C29" t="n">
@@ -8552,31 +8559,31 @@
       <c r="J29" s="2" t="n">
         <v>19.843289373664</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29" s="3" t="n">
         <v>6.717165240230294</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29" s="3" t="n">
         <v>9.275930793686072</v>
       </c>
       <c r="M29" t="n">
         <v>9.261870727688626</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29" s="3" t="n">
         <v>58.43</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" s="3" t="n">
         <v>6.47</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29" s="2" t="n">
         <v>4.23</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29" s="2" t="n">
         <v>44</v>
       </c>
       <c r="R29" t="n">
         <v>2599556.05</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S29" s="2" t="n">
         <v>16727</v>
       </c>
       <c r="T29" t="n">
@@ -8589,7 +8596,7 @@
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="3" t="n">
         <v>9.958650553699458</v>
       </c>
       <c r="C30" t="n">
@@ -8616,31 +8623,31 @@
       <c r="J30" s="2" t="n">
         <v>24.46173600944801</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30" s="3" t="n">
         <v>9.606097094616972</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30" s="3" t="n">
         <v>14.68063260349559</v>
       </c>
       <c r="M30" t="n">
         <v>11.95266483252204</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30" s="3" t="n">
         <v>58.34</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" s="2" t="n">
         <v>3.25</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30" s="2" t="n">
         <v>4.21</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30" s="2" t="n">
         <v>10</v>
       </c>
       <c r="R30" t="n">
         <v>432472.71</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S30" s="2" t="n">
         <v>899041</v>
       </c>
       <c r="T30" t="n">
@@ -8653,7 +8660,7 @@
           <t>NTPC</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="3" t="n">
         <v>13.27359840706863</v>
       </c>
       <c r="C31" t="n">
@@ -8680,31 +8687,31 @@
       <c r="J31" s="2" t="n">
         <v>16.97193810203161</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31" s="2" t="n">
         <v>12.22230965433799</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31" s="3" t="n">
         <v>8.735165684951163</v>
       </c>
       <c r="M31" t="n">
         <v>8.447177119769854</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31" s="3" t="n">
         <v>5.24</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P31" s="3" t="n">
         <v>0.06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31" s="2" t="n">
         <v>36</v>
       </c>
       <c r="R31" t="n">
         <v>907823.11</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S31" s="2" t="n">
         <v>178501</v>
       </c>
       <c r="T31" t="n">
@@ -8717,7 +8724,7 @@
           <t>TATAPOWER</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="3" t="n">
         <v>13.22784027691927</v>
       </c>
       <c r="C32" t="n">
@@ -8744,31 +8751,31 @@
       <c r="J32" s="2" t="n">
         <v>23.39827114613831</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32" s="2" t="n">
         <v>15.51115820187641</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="3" t="n">
         <v>10.431728917459</v>
       </c>
       <c r="M32" t="n">
         <v>5.922384104881218</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" s="2" t="n">
         <v>3.48</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P32" s="3" t="n">
         <v>0.49</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q32" s="2" t="n">
         <v>17</v>
       </c>
       <c r="R32" t="n">
         <v>1647269.48</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S32" s="2" t="n">
         <v>61449</v>
       </c>
       <c r="T32" t="n">
@@ -8781,7 +8788,7 @@
           <t>TECHM</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="3" t="n">
         <v>8.987963553189097</v>
       </c>
       <c r="C33" t="n">
@@ -8808,31 +8815,31 @@
       <c r="J33" s="2" t="n">
         <v>11.16009131174764</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33" s="3" t="n">
         <v>8.398437919098868</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="3" t="n">
         <v>-10.98516368821859</v>
       </c>
       <c r="M33" t="n">
         <v>-11.41672896552428</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="3" t="n">
         <v>57.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" s="3" t="n">
         <v>7.43</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P33" s="2" t="n">
         <v>0.64</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33" s="3" t="n">
         <v>150</v>
       </c>
       <c r="R33" t="n">
         <v>3021095.64</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S33" s="2" t="n">
         <v>51996</v>
       </c>
       <c r="T33" t="n">

--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -6092,7 +6092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6228,12 +6228,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6242,56 +6242,65 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.08958669347562</v>
+        <v>69.67912335635215</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>61.32056519118731</v>
+        <v>49.44710986501021</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.05035832114759</v>
       </c>
       <c r="G2" t="n">
-        <v>8.395910695456838</v>
+        <v>4.836600998148862</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>3.684256345007701</v>
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>371.9375</v>
       </c>
       <c r="K2" t="n">
-        <v>15.90207600910603</v>
+        <v>8.15986061977938</v>
+      </c>
+      <c r="L2" t="n">
+        <v>73.17556747076097</v>
       </c>
       <c r="N2" t="n">
-        <v>-29445</v>
+        <v>853</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.612606778720886</v>
+        <v>0.4646382763782856</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Accrual Risk</t>
+          <t>High Quality</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>19.29</v>
+        <v>30.67</v>
       </c>
       <c r="R2" t="n">
-        <v>10.91</v>
+        <v>8.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.32</v>
+        <v>3.77</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>109065</v>
+        <v>845966</v>
       </c>
       <c r="U2" t="n">
-        <v>9157</v>
+        <v>40916</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
+          <t>SBI Life Insurance Company Ltd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6300,34 +6309,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69.67912335635215</v>
+        <v>43.41835827855824</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>49.44710986501021</v>
+        <v>12.70458814059566</v>
       </c>
       <c r="F3" t="n">
-        <v>39.05035832114759</v>
+        <v>1.140327341024953</v>
       </c>
       <c r="G3" t="n">
-        <v>4.836600998148862</v>
+        <v>1.434978937479165</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>371.9375</v>
+        <v>240.3333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>8.15986061977938</v>
+        <v>24.23161418236754</v>
       </c>
       <c r="L3" t="n">
-        <v>73.17556747076097</v>
+        <v>7.374662152227485</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.885244396237145</v>
       </c>
       <c r="N3" t="n">
-        <v>853</v>
+        <v>-2099</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4646382763782856</v>
+        <v>-0.2368813254240325</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -6335,1138 +6347,18 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>30.67</v>
+        <v>69.98</v>
       </c>
       <c r="R3" t="n">
-        <v>8.1</v>
+        <v>9.48</v>
       </c>
       <c r="S3" t="n">
-        <v>3.77</v>
+        <v>1.62</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>845966</v>
+        <v>131988</v>
       </c>
       <c r="U3" t="n">
-        <v>40916</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>PFC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Power Finance Corporation Ltd</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>27.43053836876541</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>26.1609340860332</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.480398875307857</v>
-      </c>
-      <c r="G4" t="n">
-        <v>28.91659745596014</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>8.521864217426122</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.5804147544943239</v>
-      </c>
-      <c r="K4" t="n">
-        <v>11.08175357755092</v>
-      </c>
-      <c r="L4" t="n">
-        <v>15.92359362270073</v>
-      </c>
-      <c r="M4" t="n">
-        <v>14.86983549970351</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-101229</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-5.031547988302576</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Accrual Risk</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>91508</v>
-      </c>
-      <c r="U4" t="n">
-        <v>26461</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BAJAJFINSV</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bajaj Finserv Ltd</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>25.75641163005052</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>25.85035141227954</v>
-      </c>
-      <c r="F5" t="n">
-        <v>11.44874463510097</v>
-      </c>
-      <c r="G5" t="n">
-        <v>14.12820930948886</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>4.789368120938867</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.197130112323319</v>
-      </c>
-      <c r="K5" t="n">
-        <v>20.97274568418761</v>
-      </c>
-      <c r="L5" t="n">
-        <v>23.74781614270227</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20.58909506066124</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-79634</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-4.180016339930263</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Accrual Risk</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>110382</v>
-      </c>
-      <c r="U5" t="n">
-        <v>15595</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>REC Ltd</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>26.85241957245974</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>20.39653929343908</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9.294489608054098</v>
-      </c>
-      <c r="G6" t="n">
-        <v>29.7682934528695</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>6.424917087238645</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.600474155202351</v>
-      </c>
-      <c r="K6" t="n">
-        <v>13.33804224786568</v>
-      </c>
-      <c r="L6" t="n">
-        <v>19.76311435023079</v>
-      </c>
-      <c r="M6" t="n">
-        <v>19.67245924901726</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-59554</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-20.40097504287343</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Accrual Risk</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>47517</v>
-      </c>
-      <c r="U6" t="n">
-        <v>14145</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BAJFINANCE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bajaj Finance Ltd</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>33.96649178512514</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>18.8419213518306</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4.166013587646808</v>
-      </c>
-      <c r="G7" t="n">
-        <v>26.28792839991269</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>3.824788776468134</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2689.166666666667</v>
-      </c>
-      <c r="K7" t="n">
-        <v>24.35264273954201</v>
-      </c>
-      <c r="L7" t="n">
-        <v>29.32313482597901</v>
-      </c>
-      <c r="M7" t="n">
-        <v>27.5561392815338</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-79931</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-3.231792280571145</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Accrual Risk</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T7" s="2" t="n">
-        <v>54972</v>
-      </c>
-      <c r="U7" t="n">
-        <v>14451</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ICICI Bank Ltd</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>55.78104939027111</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>17.99027109750765</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5.11888931768417</v>
-      </c>
-      <c r="G8" t="n">
-        <v>28.8880112339828</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>6.445624336310825</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.300946133138182</v>
-      </c>
-      <c r="K8" t="n">
-        <v>17.25086850260209</v>
-      </c>
-      <c r="L8" t="n">
-        <v>51.94877118224903</v>
-      </c>
-      <c r="M8" t="n">
-        <v>55.18455739153598</v>
-      </c>
-      <c r="N8" t="n">
-        <v>12547</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.9510909711578005</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>High Quality</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>159516</v>
-      </c>
-      <c r="U8" t="n">
-        <v>46081</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cholamandalam Investment &amp; Finance Company Ltd</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>26.94888984286409</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>17.45521359669269</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.366695225484851</v>
-      </c>
-      <c r="G9" t="n">
-        <v>17.84689244899024</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>6.863420609401317</v>
-      </c>
-      <c r="I9" t="n">
-        <v>21.21176470588235</v>
-      </c>
-      <c r="K9" t="n">
-        <v>21.93916480497526</v>
-      </c>
-      <c r="L9" t="n">
-        <v>23.36341725167208</v>
-      </c>
-      <c r="M9" t="n">
-        <v>22.27523876455795</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-38538</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-3.965092371280805</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Accrual Risk</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="R9" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>19163</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Canara Bank</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>50.01209731543244</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>16.71605179468811</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3.09484900948278</v>
-      </c>
-      <c r="G10" t="n">
-        <v>13.93516047014541</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>14.86741992554242</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.610661174334986</v>
-      </c>
-      <c r="K10" t="n">
-        <v>18.17561078322378</v>
-      </c>
-      <c r="L10" t="n">
-        <v>85.7752850068174</v>
-      </c>
-      <c r="M10" t="n">
-        <v>53.4206382524911</v>
-      </c>
-      <c r="N10" t="n">
-        <v>13296</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.678399409785198</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>High Quality</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="R10" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>110519</v>
-      </c>
-      <c r="U10" t="n">
-        <v>15401</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Axis Bank Ltd</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>34.78026684048123</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>15.83271240518905</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.520716781712082</v>
-      </c>
-      <c r="G11" t="n">
-        <v>22.73130411725443</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>8.249122739980766</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.691203992514036</v>
-      </c>
-      <c r="K11" t="n">
-        <v>14.74358712051438</v>
-      </c>
-      <c r="L11" t="n">
-        <v>39.67228711897934</v>
-      </c>
-      <c r="M11" t="n">
-        <v>35.09600385206135</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-14556</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-1.534037435719632</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>High Quality</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>38.14</v>
-      </c>
-      <c r="R11" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>109369</v>
-      </c>
-      <c r="U11" t="n">
-        <v>24861</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bank of Baroda</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>35.98148777373478</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>15.7618637908999</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.712278690337432</v>
-      </c>
-      <c r="G12" t="n">
-        <v>15.93948250956673</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>12.14371872728943</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.896747724261721</v>
-      </c>
-      <c r="K12" t="n">
-        <v>17.47729766589094</v>
-      </c>
-      <c r="L12" t="n">
-        <v>74.50588066551305</v>
-      </c>
-      <c r="M12" t="n">
-        <v>55.18455739153598</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-7559</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-1.279081332956056</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>High Quality</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>16.89</v>
-      </c>
-      <c r="R12" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>118379</v>
-      </c>
-      <c r="U12" t="n">
-        <v>18869</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ICICIGI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ICICI Lombard General Insurance Company Ltd</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>57.68825046529937</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>15.7230643179025</v>
-      </c>
-      <c r="F13" t="n">
-        <v>145.2287581699346</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9.366915605017816</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0.002867677181482999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>160.0267857142857</v>
-      </c>
-      <c r="K13" t="n">
-        <v>12.91184100336258</v>
-      </c>
-      <c r="L13" t="n">
-        <v>12.83917371819816</v>
-      </c>
-      <c r="M13" t="n">
-        <v>11.1392224868865</v>
-      </c>
-      <c r="N13" t="n">
-        <v>486</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.03821387979852416</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>High Quality</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>49</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>20487</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1919</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Shriram Finance Ltd</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>23.4037502831333</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>15.11635033812082</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4.064342198385718</v>
-      </c>
-      <c r="G14" t="n">
-        <v>20.33362647026492</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>3.994034363699512</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.6766743648960739</v>
-      </c>
-      <c r="K14" t="n">
-        <v>18.55607005277675</v>
-      </c>
-      <c r="L14" t="n">
-        <v>23.49387942502037</v>
-      </c>
-      <c r="M14" t="n">
-        <v>14.28965514115608</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-31359</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-3.608906905151208</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Accrual Risk</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>68.53</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>36388</v>
-      </c>
-      <c r="U14" t="n">
-        <v>7399</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>HDFC Bank Ltd</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>46.98858561535396</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>14.33974005030719</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4.801033923800871</v>
-      </c>
-      <c r="G15" t="n">
-        <v>23.07288232992184</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>6.808786667718385</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.400768822479211</v>
-      </c>
-      <c r="K15" t="n">
-        <v>21.95098428169122</v>
-      </c>
-      <c r="L15" t="n">
-        <v>23.86506357287907</v>
-      </c>
-      <c r="M15" t="n">
-        <v>15.42478808253083</v>
-      </c>
-      <c r="N15" t="n">
-        <v>35669</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4.412519521183551</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Accrual Risk</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="R15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T15" s="2" t="n">
-        <v>283649</v>
-      </c>
-      <c r="U15" t="n">
-        <v>65446</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>IndusInd Bank Ltd</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>28.76228908265894</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>14.25227319776422</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3.475962286021232</v>
-      </c>
-      <c r="G16" t="n">
-        <v>19.56369677362945</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>6.885742949503957</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.879527055815935</v>
-      </c>
-      <c r="K16" t="n">
-        <v>15.49561308335803</v>
-      </c>
-      <c r="L16" t="n">
-        <v>22.07746495394836</v>
-      </c>
-      <c r="M16" t="n">
-        <v>15.89562187541786</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-17468</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.9664534641259643</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>High Quality</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T16" s="2" t="n">
-        <v>45748</v>
-      </c>
-      <c r="U16" t="n">
-        <v>8950</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Kotak Mahindra Bank Ltd</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>45.85310679979926</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>14.01301818853291</v>
-      </c>
-      <c r="F17" t="n">
-        <v>7.113136699541475</v>
-      </c>
-      <c r="G17" t="n">
-        <v>32.38615146611662</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>4.003739266919029</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.236375108447038</v>
-      </c>
-      <c r="K17" t="n">
-        <v>13.51960376324537</v>
-      </c>
-      <c r="L17" t="n">
-        <v>20.38200065626572</v>
-      </c>
-      <c r="M17" t="n">
-        <v>19.34407044160125</v>
-      </c>
-      <c r="N17" t="n">
-        <v>6766</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.572670875827523</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>High Quality</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T17" s="2" t="n">
-        <v>56237</v>
-      </c>
-      <c r="U17" t="n">
-        <v>18213</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>IRFC</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Indian Railway Finance Corporation Ltd</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>37.27216186683776</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>13.0380853616381</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5.746523336036321</v>
-      </c>
-      <c r="G18" t="n">
-        <v>24.0645524488647</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>8.378352548852153</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.31948659270683</v>
-      </c>
-      <c r="K18" t="n">
-        <v>19.06740855567788</v>
-      </c>
-      <c r="L18" t="n">
-        <v>23.24502393394037</v>
-      </c>
-      <c r="M18" t="n">
-        <v>20.11244339814313</v>
-      </c>
-      <c r="N18" t="n">
-        <v>7906</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.3019460457018293</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Accrual Risk</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T18" s="2" t="n">
-        <v>26645</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6412</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SBILIFE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SBI Life Insurance Company Ltd</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>43.41835827855824</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>12.70458814059566</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.140327341024953</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.434978937479165</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>240.3333333333333</v>
-      </c>
-      <c r="K19" t="n">
-        <v>24.23161418236754</v>
-      </c>
-      <c r="L19" t="n">
-        <v>7.374662152227485</v>
-      </c>
-      <c r="M19" t="n">
-        <v>7.885244396237145</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-2099</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-0.2368813254240325</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>High Quality</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>69.98</v>
-      </c>
-      <c r="R19" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T19" s="2" t="n">
-        <v>131988</v>
-      </c>
-      <c r="U19" t="n">
         <v>1894</v>
       </c>
     </row>
